--- a/dashboard/data/Elite.xlsx
+++ b/dashboard/data/Elite.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PCS\Desktop\Python\Practice\dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CFF83FF-6A11-4C4A-9A15-E47B4F398E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C197B3D3-D8CC-4DC1-93FD-EA20A50F31EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C510DD15-1ECC-4C0C-BE9E-FD99F7348715}"/>
   </bookViews>
@@ -617,24 +617,12 @@
       <c r="A2" s="6">
         <v>46127</v>
       </c>
-      <c r="B2" s="13">
-        <v>1</v>
-      </c>
-      <c r="C2" s="13">
-        <v>1</v>
-      </c>
-      <c r="D2" s="13">
-        <v>1</v>
-      </c>
-      <c r="E2" s="13">
-        <v>1</v>
-      </c>
-      <c r="F2" s="13">
-        <v>1</v>
-      </c>
-      <c r="G2" s="13">
-        <v>3</v>
-      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>

--- a/dashboard/data/Elite.xlsx
+++ b/dashboard/data/Elite.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PCS\Desktop\Python\Practice\dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C197B3D3-D8CC-4DC1-93FD-EA20A50F31EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A24B0AA-D6C4-41A6-8749-84595B07FA59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C510DD15-1ECC-4C0C-BE9E-FD99F7348715}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C510DD15-1ECC-4C0C-BE9E-FD99F7348715}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -617,12 +617,24 @@
       <c r="A2" s="6">
         <v>46127</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
+      <c r="B2" s="13">
+        <v>0.84</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.43</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.85</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.66</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.81</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-1.28</v>
+      </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>

--- a/dashboard/data/Elite.xlsx
+++ b/dashboard/data/Elite.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PCS\Desktop\Python\Practice\dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A24B0AA-D6C4-41A6-8749-84595B07FA59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72AAEA64-AFC4-4217-A811-05BFA3E0ECB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C510DD15-1ECC-4C0C-BE9E-FD99F7348715}"/>
   </bookViews>
@@ -210,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -232,9 +232,6 @@
     </xf>
     <xf numFmtId="14" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -565,11 +562,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E436C2D-E939-47CC-A565-7B11CCD28B8F}">
-  <dimension ref="A1:Y1002"/>
+  <dimension ref="A1:Y949"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.5703125" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -617,22 +615,22 @@
       <c r="A2" s="6">
         <v>46127</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="12">
         <v>0.84</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>0.43</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="12">
         <v>0.85</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="12">
         <v>0.66</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="12">
         <v>-0.81</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="12">
         <v>-1.28</v>
       </c>
       <c r="H2" s="4"/>
@@ -658,22 +656,22 @@
       <c r="A3" s="6">
         <v>46125</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="8">
         <v>1.94</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>1.84</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="8">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="8">
         <v>2.0499999999999998</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="8">
         <v>-17.72</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="8">
         <v>0</v>
       </c>
       <c r="H3" s="4"/>
@@ -699,22 +697,22 @@
       <c r="A4" s="6">
         <v>46122</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <v>0</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="9">
         <v>0</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <v>0.44</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="9">
         <v>1.08</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <v>-0.19</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <v>-3.03</v>
       </c>
       <c r="H4" s="4"/>
@@ -740,22 +738,22 @@
       <c r="A5" s="6">
         <v>46121</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="10">
         <v>0.46</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <v>0.09</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>1.51</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="10">
         <v>1.72</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="10">
         <v>0.59</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="10">
         <v>2.02</v>
       </c>
       <c r="H5" s="4"/>
@@ -781,22 +779,22 @@
       <c r="A6" s="6">
         <v>46120</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="9">
         <v>-0.12</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <v>0.56000000000000005</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>-0.56999999999999995</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <v>0.94</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <v>0</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <v>0</v>
       </c>
       <c r="H6" s="4"/>
@@ -822,22 +820,22 @@
       <c r="A7" s="6">
         <v>46119</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="10">
         <v>0.95</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <v>0.4</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <v>-0.4</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="10">
         <v>0.39</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="10">
         <v>0</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="10">
         <v>1.1499999999999999</v>
       </c>
       <c r="H7" s="4"/>
@@ -863,22 +861,22 @@
       <c r="A8" s="6">
         <v>46118</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <v>-0.14000000000000001</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <v>-0.46</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>0</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="9">
         <v>0</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="9">
         <v>0.13</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="9">
         <v>4.22</v>
       </c>
       <c r="H8" s="4"/>
@@ -904,22 +902,22 @@
       <c r="A9" s="6">
         <v>46114</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="9">
         <v>1.22</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <v>0.1</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>1.07</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="9">
         <v>1.51</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <v>-0.52</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="9">
         <v>-1.5</v>
       </c>
       <c r="H9" s="4"/>
@@ -945,22 +943,22 @@
       <c r="A10" s="6">
         <v>46113</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="10">
         <v>-1.21</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="10">
         <v>-1.38</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="10">
         <v>-0.84</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="10">
         <v>-1.81</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="10">
         <v>-1.96</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="10">
         <v>-2.73</v>
       </c>
       <c r="H10" s="4"/>
@@ -986,22 +984,22 @@
       <c r="A11" s="6">
         <v>46111</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>-1.73</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="9">
         <v>0.13</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>1.21</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="9">
         <v>1.73</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="9">
         <v>0</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="9">
         <v>0</v>
       </c>
       <c r="H11" s="4"/>
@@ -1027,22 +1025,22 @@
       <c r="A12" s="6">
         <v>46108</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="10">
         <v>0</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="10">
         <v>0</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="10">
         <v>1.95</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="10">
         <v>1.94</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="10">
         <v>4.4400000000000004</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="10">
         <v>7.63</v>
       </c>
       <c r="H12" s="4"/>
@@ -1068,22 +1066,22 @@
       <c r="A13" s="6">
         <v>46106</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <v>0.93</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="9">
         <v>0.57999999999999996</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>0.16</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="9">
         <v>-0.41</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="9">
         <v>0</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="9">
         <v>2.29</v>
       </c>
       <c r="H13" s="4"/>
@@ -1109,22 +1107,22 @@
       <c r="A14" s="6">
         <v>46105</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="10">
         <v>0.19</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="10">
         <v>-1.29</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="10">
         <v>1.45</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="10">
         <v>0.33</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="10">
         <v>-3.09</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="10">
         <v>-0.61</v>
       </c>
       <c r="H14" s="4"/>
@@ -1150,22 +1148,22 @@
       <c r="A15" s="6">
         <v>46104</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <v>0.3</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="9">
         <v>0.31</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <v>1.03</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="9">
         <v>-1.97</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="9">
         <v>0</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="9">
         <v>4.28</v>
       </c>
       <c r="H15" s="4"/>
@@ -1191,22 +1189,22 @@
       <c r="A16" s="6">
         <v>46101</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="10">
         <v>0</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="10">
         <v>0</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="10">
         <v>-0.27</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="10">
         <v>-0.24</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="10">
         <v>-2.88</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="10">
         <v>-3.94</v>
       </c>
       <c r="H16" s="4"/>
@@ -1232,22 +1230,22 @@
       <c r="A17" s="6">
         <v>46100</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <v>1.35</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="9">
         <v>1.18</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <v>2</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <v>1.96</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="9">
         <v>2.85</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="9">
         <v>6.27</v>
       </c>
       <c r="H17" s="4"/>
@@ -1273,22 +1271,22 @@
       <c r="A18" s="6">
         <v>46099</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="10">
         <v>-1.93</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="10">
         <v>0.35</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="10">
         <v>0.36</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="10">
         <v>-2.0299999999999998</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="10">
         <v>0</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="10">
         <v>0.3</v>
       </c>
       <c r="H18" s="4"/>
@@ -1314,22 +1312,22 @@
       <c r="A19" s="6">
         <v>46098</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <v>0.03</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <v>0.11</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <v>-0.4</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="9">
         <v>-1.22</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="9">
         <v>0</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="9">
         <v>3.95</v>
       </c>
       <c r="H19" s="4"/>
@@ -1355,22 +1353,22 @@
       <c r="A20" s="6">
         <v>46097</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="10">
         <v>-1.46</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="10">
         <v>-2.2000000000000002</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="10">
         <v>-1.91</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="10">
         <v>-1.97</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="10">
         <v>2.64</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="10">
         <v>6.07</v>
       </c>
       <c r="H20" s="4"/>
@@ -1396,22 +1394,22 @@
       <c r="A21" s="6">
         <v>46094</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <v>0</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9">
         <v>0</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <v>-1.22</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="9">
         <v>-1.7</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="9">
         <v>0</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="9">
         <v>-0.15</v>
       </c>
       <c r="H21" s="4"/>
@@ -1437,22 +1435,22 @@
       <c r="A22" s="6">
         <v>46093</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="10">
         <v>-1.38</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="10">
         <v>-0.26</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="10">
         <v>-1.9</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="10">
         <v>-2.14</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="10">
         <v>0</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="10">
         <v>0.72</v>
       </c>
       <c r="H22" s="4"/>
@@ -1478,22 +1476,22 @@
       <c r="A23" s="6">
         <v>46092</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="9">
         <v>-1.56</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="9">
         <v>-0.6</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="9">
         <v>0.45</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="9">
         <v>-2.09</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="9">
         <v>1.76</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="9">
         <v>3.64</v>
       </c>
       <c r="H23" s="4"/>
@@ -1519,22 +1517,22 @@
       <c r="A24" s="6">
         <v>46091</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="10">
         <v>0.31</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="10">
         <v>1.1100000000000001</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="10">
         <v>-1.73</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="10">
         <v>0.96</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="10">
         <v>3.2</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="10">
         <v>7.06</v>
       </c>
       <c r="H24" s="4"/>
@@ -1560,22 +1558,22 @@
       <c r="A25" s="6">
         <v>46090</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="9">
         <v>0.82</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="9">
         <v>-0.37</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="9">
         <v>0.99</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="9">
         <v>1.28</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="9">
         <v>0</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="9">
         <v>5.85</v>
       </c>
       <c r="H25" s="4"/>
@@ -1601,22 +1599,22 @@
       <c r="A26" s="6">
         <v>46087</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="10">
         <v>0</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="10">
         <v>0</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="10">
         <v>-1.81</v>
       </c>
-      <c r="E26" s="11">
+      <c r="E26" s="10">
         <v>1.57</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F26" s="10">
         <v>-3.5</v>
       </c>
-      <c r="G26" s="11">
+      <c r="G26" s="10">
         <v>1.46</v>
       </c>
       <c r="H26" s="4"/>
@@ -1642,22 +1640,22 @@
       <c r="A27" s="6">
         <v>46086</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="9">
         <v>1.63</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="9">
         <v>0.3</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="9">
         <v>-0.47</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="9">
         <v>-0.08</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="9">
         <v>0</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="9">
         <v>3.79</v>
       </c>
       <c r="H27" s="4"/>
@@ -1683,22 +1681,22 @@
       <c r="A28" s="6">
         <v>46085</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="10">
         <v>0.5</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="10">
         <v>-1.2</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="10">
         <v>0.51</v>
       </c>
-      <c r="E28" s="11">
+      <c r="E28" s="10">
         <v>1.27</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="10">
         <v>-3.08</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="10">
         <v>-10.52</v>
       </c>
       <c r="H28" s="4"/>
@@ -1724,22 +1722,22 @@
       <c r="A29" s="6">
         <v>46083</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="9">
         <v>-1.08</v>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="9">
         <v>-0.78</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="9">
         <v>1.27</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="9">
         <v>-0.09</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="9">
         <v>0</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="9">
         <v>3.42</v>
       </c>
       <c r="H29" s="4"/>
@@ -1765,22 +1763,22 @@
       <c r="A30" s="6">
         <v>46080</v>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="10">
         <v>0</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="10">
         <v>0</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="10">
         <v>-1.83</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="10">
         <v>-0.04</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="10">
         <v>2.44</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="10">
         <v>0.63</v>
       </c>
       <c r="H30" s="4"/>
@@ -1806,22 +1804,22 @@
       <c r="A31" s="6">
         <v>46079</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="9">
         <v>-0.22</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="9">
         <v>0.05</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="9">
         <v>0.33</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="9">
         <v>-1.53</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="9">
         <v>0.48</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="9">
         <v>-2.42</v>
       </c>
       <c r="H31" s="4"/>
@@ -1847,22 +1845,22 @@
       <c r="A32" s="6">
         <v>46078</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="10">
         <v>-0.04</v>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="10">
         <v>0.47</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="10">
         <v>-0.21</v>
       </c>
-      <c r="E32" s="11">
+      <c r="E32" s="10">
         <v>0.01</v>
       </c>
-      <c r="F32" s="11">
+      <c r="F32" s="10">
         <v>-2.88</v>
       </c>
-      <c r="G32" s="11">
+      <c r="G32" s="10">
         <v>-5.39</v>
       </c>
       <c r="H32" s="4"/>
@@ -1888,22 +1886,22 @@
       <c r="A33" s="6">
         <v>46077</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="9">
         <v>0.05</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="9">
         <v>-0.28000000000000003</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="9">
         <v>-1.06</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="9">
         <v>-0.5</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="9">
         <v>0</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="9">
         <v>-1.24</v>
       </c>
       <c r="H33" s="4"/>
@@ -1929,22 +1927,22 @@
       <c r="A34" s="6">
         <v>46076</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="10">
         <v>0.38</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C34" s="10">
         <v>0.61</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="10">
         <v>0.26</v>
       </c>
-      <c r="E34" s="11">
+      <c r="E34" s="10">
         <v>0.41</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="10">
         <v>-4.07</v>
       </c>
-      <c r="G34" s="11">
+      <c r="G34" s="10">
         <v>4.2</v>
       </c>
       <c r="H34" s="4"/>
@@ -1970,22 +1968,22 @@
       <c r="A35" s="6">
         <v>46073</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="9">
         <v>0</v>
       </c>
-      <c r="C35" s="10">
+      <c r="C35" s="9">
         <v>0</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="9">
         <v>0.26</v>
       </c>
-      <c r="E35" s="10">
+      <c r="E35" s="9">
         <v>0</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="9">
         <v>0</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G35" s="9">
         <v>-2.13</v>
       </c>
       <c r="H35" s="4"/>
@@ -2011,22 +2009,22 @@
       <c r="A36" s="6">
         <v>46072</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="10">
         <v>-0.79</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="10">
         <v>-0.45</v>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="10">
         <v>0.74</v>
       </c>
-      <c r="E36" s="11">
+      <c r="E36" s="10">
         <v>0.95</v>
       </c>
-      <c r="F36" s="11">
+      <c r="F36" s="10">
         <v>3.44</v>
       </c>
-      <c r="G36" s="11">
+      <c r="G36" s="10">
         <v>2.97</v>
       </c>
       <c r="H36" s="4"/>
@@ -2052,22 +2050,22 @@
       <c r="A37" s="6">
         <v>46071</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="9">
         <v>0.63</v>
       </c>
-      <c r="C37" s="10">
+      <c r="C37" s="9">
         <v>0.11</v>
       </c>
-      <c r="D37" s="10">
+      <c r="D37" s="9">
         <v>0.46</v>
       </c>
-      <c r="E37" s="10">
+      <c r="E37" s="9">
         <v>-0.47</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F37" s="9">
         <v>0</v>
       </c>
-      <c r="G37" s="10">
+      <c r="G37" s="9">
         <v>-0.23</v>
       </c>
       <c r="H37" s="4"/>
@@ -2093,22 +2091,22 @@
       <c r="A38" s="6">
         <v>46070</v>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="10">
         <v>-0.38</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="10">
         <v>-0.28000000000000003</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="10">
         <v>-1.33</v>
       </c>
-      <c r="E38" s="11">
+      <c r="E38" s="10">
         <v>-1.44</v>
       </c>
-      <c r="F38" s="11">
+      <c r="F38" s="10">
         <v>0</v>
       </c>
-      <c r="G38" s="11">
+      <c r="G38" s="10">
         <v>2.3199999999999998</v>
       </c>
       <c r="H38" s="4"/>
@@ -2134,22 +2132,22 @@
       <c r="A39" s="6">
         <v>46069</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="9">
         <v>-1.58</v>
       </c>
-      <c r="C39" s="10">
+      <c r="C39" s="9">
         <v>-1.05</v>
       </c>
-      <c r="D39" s="10">
+      <c r="D39" s="9">
         <v>-1.56</v>
       </c>
-      <c r="E39" s="10">
+      <c r="E39" s="9">
         <v>0.09</v>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="9">
         <v>3.2</v>
       </c>
-      <c r="G39" s="10">
+      <c r="G39" s="9">
         <v>5.12</v>
       </c>
       <c r="H39" s="4"/>
@@ -2175,22 +2173,22 @@
       <c r="A40" s="6">
         <v>46066</v>
       </c>
-      <c r="B40" s="11">
+      <c r="B40" s="10">
         <v>0</v>
       </c>
-      <c r="C40" s="11">
+      <c r="C40" s="10">
         <v>0</v>
       </c>
-      <c r="D40" s="11">
+      <c r="D40" s="10">
         <v>-0.41</v>
       </c>
-      <c r="E40" s="11">
+      <c r="E40" s="10">
         <v>-0.41</v>
       </c>
-      <c r="F40" s="11">
+      <c r="F40" s="10">
         <v>3.94</v>
       </c>
-      <c r="G40" s="11">
+      <c r="G40" s="10">
         <v>2.5</v>
       </c>
       <c r="H40" s="4"/>
@@ -2216,22 +2214,22 @@
       <c r="A41" s="6">
         <v>46065</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="9">
         <v>0.26</v>
       </c>
-      <c r="C41" s="10">
+      <c r="C41" s="9">
         <v>0.18</v>
       </c>
-      <c r="D41" s="10">
+      <c r="D41" s="9">
         <v>0.36</v>
       </c>
-      <c r="E41" s="10">
+      <c r="E41" s="9">
         <v>0.52</v>
       </c>
-      <c r="F41" s="10">
+      <c r="F41" s="9">
         <v>1.1299999999999999</v>
       </c>
-      <c r="G41" s="10">
+      <c r="G41" s="9">
         <v>3.77</v>
       </c>
       <c r="H41" s="4"/>
@@ -2257,22 +2255,22 @@
       <c r="A42" s="6">
         <v>46064</v>
       </c>
-      <c r="B42" s="11">
+      <c r="B42" s="10">
         <v>0.25</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C42" s="10">
         <v>0.14000000000000001</v>
       </c>
-      <c r="D42" s="11">
+      <c r="D42" s="10">
         <v>0.4</v>
       </c>
-      <c r="E42" s="11">
+      <c r="E42" s="10">
         <v>0.43</v>
       </c>
-      <c r="F42" s="11">
+      <c r="F42" s="10">
         <v>0</v>
       </c>
-      <c r="G42" s="11">
+      <c r="G42" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="H42" s="4"/>
@@ -2298,22 +2296,22 @@
       <c r="A43" s="6">
         <v>46063</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="9">
         <v>1.03</v>
       </c>
-      <c r="C43" s="10">
+      <c r="C43" s="9">
         <v>0.39</v>
       </c>
-      <c r="D43" s="10">
+      <c r="D43" s="9">
         <v>0.28000000000000003</v>
       </c>
-      <c r="E43" s="10">
+      <c r="E43" s="9">
         <v>0.74</v>
       </c>
-      <c r="F43" s="10">
+      <c r="F43" s="9">
         <v>0</v>
       </c>
-      <c r="G43" s="10">
+      <c r="G43" s="9">
         <v>1.36</v>
       </c>
       <c r="H43" s="4"/>
@@ -2339,22 +2337,22 @@
       <c r="A44" s="6">
         <v>46062</v>
       </c>
-      <c r="B44" s="11">
+      <c r="B44" s="10">
         <v>0.72</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C44" s="10">
         <v>0.64</v>
       </c>
-      <c r="D44" s="11">
+      <c r="D44" s="10">
         <v>0.67</v>
       </c>
-      <c r="E44" s="11">
+      <c r="E44" s="10">
         <v>0.55000000000000004</v>
       </c>
-      <c r="F44" s="11">
+      <c r="F44" s="10">
         <v>3.59</v>
       </c>
-      <c r="G44" s="11">
+      <c r="G44" s="10">
         <v>4.92</v>
       </c>
       <c r="H44" s="4"/>
@@ -2380,22 +2378,22 @@
       <c r="A45" s="6">
         <v>46059</v>
       </c>
-      <c r="B45" s="10">
+      <c r="B45" s="9">
         <v>0</v>
       </c>
-      <c r="C45" s="10">
+      <c r="C45" s="9">
         <v>0</v>
       </c>
-      <c r="D45" s="10">
+      <c r="D45" s="9">
         <v>-0.94</v>
       </c>
-      <c r="E45" s="10">
+      <c r="E45" s="9">
         <v>0.06</v>
       </c>
-      <c r="F45" s="10">
+      <c r="F45" s="9">
         <v>3.23</v>
       </c>
-      <c r="G45" s="10">
+      <c r="G45" s="9">
         <v>3.24</v>
       </c>
       <c r="H45" s="4"/>
@@ -2421,22 +2419,22 @@
       <c r="A46" s="6">
         <v>46058</v>
       </c>
-      <c r="B46" s="11">
+      <c r="B46" s="10">
         <v>1.82</v>
       </c>
-      <c r="C46" s="11">
+      <c r="C46" s="10">
         <v>1.48</v>
       </c>
-      <c r="D46" s="11">
+      <c r="D46" s="10">
         <v>1.52</v>
       </c>
-      <c r="E46" s="11">
+      <c r="E46" s="10">
         <v>1.38</v>
       </c>
-      <c r="F46" s="11">
+      <c r="F46" s="10">
         <v>-2.68</v>
       </c>
-      <c r="G46" s="11">
+      <c r="G46" s="10">
         <v>3.31</v>
       </c>
       <c r="H46" s="4"/>
@@ -2462,22 +2460,22 @@
       <c r="A47" s="6">
         <v>46057</v>
       </c>
-      <c r="B47" s="10">
+      <c r="B47" s="9">
         <v>-0.13</v>
       </c>
-      <c r="C47" s="10">
+      <c r="C47" s="9">
         <v>0.22</v>
       </c>
-      <c r="D47" s="10">
+      <c r="D47" s="9">
         <v>1.51</v>
       </c>
-      <c r="E47" s="10">
+      <c r="E47" s="9">
         <v>0.87</v>
       </c>
-      <c r="F47" s="10">
+      <c r="F47" s="9">
         <v>0.25</v>
       </c>
-      <c r="G47" s="10">
+      <c r="G47" s="9">
         <v>4.21</v>
       </c>
       <c r="H47" s="4"/>
@@ -2503,22 +2501,22 @@
       <c r="A48" s="6">
         <v>46056</v>
       </c>
-      <c r="B48" s="11">
+      <c r="B48" s="10">
         <v>1.18</v>
       </c>
-      <c r="C48" s="11">
+      <c r="C48" s="10">
         <v>1.05</v>
       </c>
-      <c r="D48" s="11">
+      <c r="D48" s="10">
         <v>2.59</v>
       </c>
-      <c r="E48" s="11">
+      <c r="E48" s="10">
         <v>2.04</v>
       </c>
-      <c r="F48" s="11">
+      <c r="F48" s="10">
         <v>4.55</v>
       </c>
-      <c r="G48" s="11">
+      <c r="G48" s="10">
         <v>0</v>
       </c>
       <c r="H48" s="4"/>
@@ -2544,22 +2542,22 @@
       <c r="A49" s="6">
         <v>46055</v>
       </c>
-      <c r="B49" s="10">
+      <c r="B49" s="9">
         <v>1.6</v>
       </c>
-      <c r="C49" s="10">
+      <c r="C49" s="9">
         <v>1.7</v>
       </c>
-      <c r="D49" s="10">
+      <c r="D49" s="9">
         <v>1.82</v>
       </c>
-      <c r="E49" s="10">
+      <c r="E49" s="9">
         <v>1.05</v>
       </c>
-      <c r="F49" s="10">
+      <c r="F49" s="9">
         <v>-0.14000000000000001</v>
       </c>
-      <c r="G49" s="10">
+      <c r="G49" s="9">
         <v>4.97</v>
       </c>
       <c r="H49" s="4"/>
@@ -2585,22 +2583,22 @@
       <c r="A50" s="6">
         <v>46054</v>
       </c>
-      <c r="B50" s="11">
+      <c r="B50" s="10">
         <v>0</v>
       </c>
-      <c r="C50" s="11">
+      <c r="C50" s="10">
         <v>0</v>
       </c>
-      <c r="D50" s="11">
+      <c r="D50" s="10">
         <v>0</v>
       </c>
-      <c r="E50" s="11">
+      <c r="E50" s="10">
         <v>0</v>
       </c>
-      <c r="F50" s="11">
+      <c r="F50" s="10">
         <v>1.34</v>
       </c>
-      <c r="G50" s="11">
+      <c r="G50" s="10">
         <v>5.0599999999999996</v>
       </c>
       <c r="H50" s="4"/>
@@ -2626,22 +2624,22 @@
       <c r="A51" s="6">
         <v>46052</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B51" s="9">
         <v>0</v>
       </c>
-      <c r="C51" s="10">
+      <c r="C51" s="9">
         <v>0</v>
       </c>
-      <c r="D51" s="10">
+      <c r="D51" s="9">
         <v>-0.17</v>
       </c>
-      <c r="E51" s="10">
+      <c r="E51" s="9">
         <v>0.05</v>
       </c>
-      <c r="F51" s="10">
+      <c r="F51" s="9">
         <v>-1.07</v>
       </c>
-      <c r="G51" s="10">
+      <c r="G51" s="9">
         <v>-4</v>
       </c>
       <c r="H51" s="4"/>
@@ -2667,22 +2665,22 @@
       <c r="A52" s="6">
         <v>46051</v>
       </c>
-      <c r="B52" s="11">
+      <c r="B52" s="10">
         <v>-0.12</v>
       </c>
-      <c r="C52" s="11">
+      <c r="C52" s="10">
         <v>0.82</v>
       </c>
-      <c r="D52" s="11">
+      <c r="D52" s="10">
         <v>0.72</v>
       </c>
-      <c r="E52" s="11">
+      <c r="E52" s="10">
         <v>1.33</v>
       </c>
-      <c r="F52" s="11">
+      <c r="F52" s="10">
         <v>1.75</v>
       </c>
-      <c r="G52" s="11">
+      <c r="G52" s="10">
         <v>2</v>
       </c>
       <c r="H52" s="4"/>
@@ -2708,22 +2706,22 @@
       <c r="A53" s="7">
         <v>46050</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B53" s="9">
         <v>1.68</v>
       </c>
-      <c r="C53" s="10">
+      <c r="C53" s="9">
         <v>1.58</v>
       </c>
-      <c r="D53" s="10">
+      <c r="D53" s="9">
         <v>0.14000000000000001</v>
       </c>
-      <c r="E53" s="10">
+      <c r="E53" s="9">
         <v>1.36</v>
       </c>
-      <c r="F53" s="10">
+      <c r="F53" s="9">
         <v>1.32</v>
       </c>
-      <c r="G53" s="10">
+      <c r="G53" s="9">
         <v>1</v>
       </c>
       <c r="H53" s="4"/>
@@ -2749,22 +2747,22 @@
       <c r="A54" s="7">
         <v>46049</v>
       </c>
-      <c r="B54" s="11">
+      <c r="B54" s="10">
         <v>0.22</v>
       </c>
-      <c r="C54" s="11">
+      <c r="C54" s="10">
         <v>0.64</v>
       </c>
-      <c r="D54" s="11">
+      <c r="D54" s="10">
         <v>-1.7</v>
       </c>
-      <c r="E54" s="11">
+      <c r="E54" s="10">
         <v>-0.99</v>
       </c>
-      <c r="F54" s="11">
+      <c r="F54" s="10">
         <v>1.1200000000000001</v>
       </c>
-      <c r="G54" s="11">
+      <c r="G54" s="10">
         <v>5.08</v>
       </c>
       <c r="H54" s="4"/>
@@ -2790,22 +2788,22 @@
       <c r="A55" s="6">
         <v>46045</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="9">
         <v>0</v>
       </c>
-      <c r="C55" s="10">
+      <c r="C55" s="9">
         <v>0</v>
       </c>
-      <c r="D55" s="10">
+      <c r="D55" s="9">
         <v>0.3</v>
       </c>
-      <c r="E55" s="10">
+      <c r="E55" s="9">
         <v>0.37</v>
       </c>
-      <c r="F55" s="10">
+      <c r="F55" s="9">
         <v>-2.25</v>
       </c>
-      <c r="G55" s="10">
+      <c r="G55" s="9">
         <v>4.72</v>
       </c>
       <c r="H55" s="4"/>
@@ -2831,22 +2829,22 @@
       <c r="A56" s="6">
         <v>46044</v>
       </c>
-      <c r="B56" s="11">
+      <c r="B56" s="10">
         <v>-1.44</v>
       </c>
-      <c r="C56" s="11">
+      <c r="C56" s="10">
         <v>-2.2599999999999998</v>
       </c>
-      <c r="D56" s="11">
+      <c r="D56" s="10">
         <v>-1.26</v>
       </c>
-      <c r="E56" s="11">
+      <c r="E56" s="10">
         <v>-0.79</v>
       </c>
-      <c r="F56" s="11">
+      <c r="F56" s="10">
         <v>4.37</v>
       </c>
-      <c r="G56" s="11">
+      <c r="G56" s="10">
         <v>0</v>
       </c>
       <c r="H56" s="4"/>
@@ -2872,22 +2870,22 @@
       <c r="A57" s="6">
         <v>46043</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="9">
         <v>1.31</v>
       </c>
-      <c r="C57" s="10">
+      <c r="C57" s="9">
         <v>-0.9</v>
       </c>
-      <c r="D57" s="10">
+      <c r="D57" s="9">
         <v>-1.75</v>
       </c>
-      <c r="E57" s="10">
+      <c r="E57" s="9">
         <v>-2.0099999999999998</v>
       </c>
-      <c r="F57" s="10">
+      <c r="F57" s="9">
         <v>0.23</v>
       </c>
-      <c r="G57" s="10">
+      <c r="G57" s="9">
         <v>-3.64</v>
       </c>
       <c r="H57" s="4"/>
@@ -2913,16 +2911,16 @@
       <c r="A58" s="7">
         <v>46042</v>
       </c>
-      <c r="B58" s="11">
+      <c r="B58" s="10">
         <v>1.23</v>
       </c>
-      <c r="C58" s="11">
+      <c r="C58" s="10">
         <v>1.0900000000000001</v>
       </c>
-      <c r="D58" s="11">
+      <c r="D58" s="10">
         <v>0.43</v>
       </c>
-      <c r="E58" s="11">
+      <c r="E58" s="10">
         <v>-0.03</v>
       </c>
       <c r="F58" s="4"/>
@@ -2952,16 +2950,16 @@
       <c r="A59" s="6">
         <v>46041</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B59" s="9">
         <v>0.15</v>
       </c>
-      <c r="C59" s="10">
+      <c r="C59" s="9">
         <v>0.04</v>
       </c>
-      <c r="D59" s="10">
+      <c r="D59" s="9">
         <v>-0.16</v>
       </c>
-      <c r="E59" s="10">
+      <c r="E59" s="9">
         <v>0.03</v>
       </c>
       <c r="F59" s="4"/>
@@ -2991,16 +2989,16 @@
       <c r="A60" s="6">
         <v>46038</v>
       </c>
-      <c r="B60" s="11">
+      <c r="B60" s="10">
         <v>0</v>
       </c>
-      <c r="C60" s="11">
+      <c r="C60" s="10">
         <v>0</v>
       </c>
-      <c r="D60" s="11">
+      <c r="D60" s="10">
         <v>-0.73</v>
       </c>
-      <c r="E60" s="11">
+      <c r="E60" s="10">
         <v>-0.77</v>
       </c>
       <c r="F60" s="4"/>
@@ -3030,16 +3028,16 @@
       <c r="A61" s="6">
         <v>46036</v>
       </c>
-      <c r="B61" s="10">
+      <c r="B61" s="9">
         <v>-1.56</v>
       </c>
-      <c r="C61" s="10">
+      <c r="C61" s="9">
         <v>-0.98</v>
       </c>
-      <c r="D61" s="10">
+      <c r="D61" s="9">
         <v>-1.47</v>
       </c>
-      <c r="E61" s="10">
+      <c r="E61" s="9">
         <v>-0.86</v>
       </c>
       <c r="F61" s="4"/>
@@ -3069,16 +3067,16 @@
       <c r="A62" s="6">
         <v>46035</v>
       </c>
-      <c r="B62" s="11">
+      <c r="B62" s="10">
         <v>-1.78</v>
       </c>
-      <c r="C62" s="11">
+      <c r="C62" s="10">
         <v>-1.96</v>
       </c>
-      <c r="D62" s="11">
+      <c r="D62" s="10">
         <v>-1.91</v>
       </c>
-      <c r="E62" s="11">
+      <c r="E62" s="10">
         <v>-1.21</v>
       </c>
       <c r="F62" s="4"/>
@@ -3108,16 +3106,16 @@
       <c r="A63" s="7">
         <v>46034</v>
       </c>
-      <c r="B63" s="10">
+      <c r="B63" s="9">
         <v>-1.21</v>
       </c>
-      <c r="C63" s="10">
+      <c r="C63" s="9">
         <v>-1.64</v>
       </c>
-      <c r="D63" s="10">
+      <c r="D63" s="9">
         <v>-1.67</v>
       </c>
-      <c r="E63" s="10">
+      <c r="E63" s="9">
         <v>-1.06</v>
       </c>
       <c r="F63" s="4"/>
@@ -3147,16 +3145,16 @@
       <c r="A64" s="6">
         <v>46031</v>
       </c>
-      <c r="B64" s="11">
+      <c r="B64" s="10">
         <v>0</v>
       </c>
-      <c r="C64" s="11">
+      <c r="C64" s="10">
         <v>0</v>
       </c>
-      <c r="D64" s="11">
+      <c r="D64" s="10">
         <v>-0.2</v>
       </c>
-      <c r="E64" s="11">
+      <c r="E64" s="10">
         <v>-1.52</v>
       </c>
       <c r="F64" s="4"/>
@@ -3186,16 +3184,16 @@
       <c r="A65" s="6">
         <v>46030</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B65" s="9">
         <v>0.9</v>
       </c>
-      <c r="C65" s="10">
+      <c r="C65" s="9">
         <v>0.88</v>
       </c>
-      <c r="D65" s="10">
+      <c r="D65" s="9">
         <v>1.1100000000000001</v>
       </c>
-      <c r="E65" s="10">
+      <c r="E65" s="9">
         <v>0.99</v>
       </c>
       <c r="F65" s="4"/>
@@ -3225,16 +3223,16 @@
       <c r="A66" s="6">
         <v>46029</v>
       </c>
-      <c r="B66" s="11">
+      <c r="B66" s="10">
         <v>-0.06</v>
       </c>
-      <c r="C66" s="11">
+      <c r="C66" s="10">
         <v>-0.11</v>
       </c>
-      <c r="D66" s="11">
+      <c r="D66" s="10">
         <v>-1.03</v>
       </c>
-      <c r="E66" s="11">
+      <c r="E66" s="10">
         <v>0.18</v>
       </c>
       <c r="F66" s="4"/>
@@ -3264,16 +3262,16 @@
       <c r="A67" s="6">
         <v>46028</v>
       </c>
-      <c r="B67" s="10">
+      <c r="B67" s="9">
         <v>-0.78</v>
       </c>
-      <c r="C67" s="10">
+      <c r="C67" s="9">
         <v>0.84</v>
       </c>
-      <c r="D67" s="10">
+      <c r="D67" s="9">
         <v>1.1499999999999999</v>
       </c>
-      <c r="E67" s="10">
+      <c r="E67" s="9">
         <v>0.12</v>
       </c>
       <c r="F67" s="4"/>
@@ -3303,16 +3301,16 @@
       <c r="A68" s="7">
         <v>46027</v>
       </c>
-      <c r="B68" s="11">
+      <c r="B68" s="10">
         <v>0</v>
       </c>
-      <c r="C68" s="11">
+      <c r="C68" s="10">
         <v>-0.25</v>
       </c>
-      <c r="D68" s="11">
+      <c r="D68" s="10">
         <v>0.09</v>
       </c>
-      <c r="E68" s="11">
+      <c r="E68" s="10">
         <v>0</v>
       </c>
       <c r="F68" s="4"/>
@@ -3342,16 +3340,16 @@
       <c r="A69" s="6">
         <v>46024</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="9">
         <v>0</v>
       </c>
-      <c r="C69" s="10">
+      <c r="C69" s="9">
         <v>0</v>
       </c>
-      <c r="D69" s="10">
+      <c r="D69" s="9">
         <v>0.1</v>
       </c>
-      <c r="E69" s="10">
+      <c r="E69" s="9">
         <v>-0.02</v>
       </c>
       <c r="F69" s="4"/>
@@ -3381,16 +3379,16 @@
       <c r="A70" s="6">
         <v>46023</v>
       </c>
-      <c r="B70" s="11">
+      <c r="B70" s="10">
         <v>1.18</v>
       </c>
-      <c r="C70" s="11">
+      <c r="C70" s="10">
         <v>1.17</v>
       </c>
-      <c r="D70" s="11">
+      <c r="D70" s="10">
         <v>1.52</v>
       </c>
-      <c r="E70" s="11">
+      <c r="E70" s="10">
         <v>0.36</v>
       </c>
       <c r="F70" s="4"/>
@@ -3420,16 +3418,16 @@
       <c r="A71" s="6">
         <v>46022</v>
       </c>
-      <c r="B71" s="10">
+      <c r="B71" s="9">
         <v>-1.1399999999999999</v>
       </c>
-      <c r="C71" s="10">
+      <c r="C71" s="9">
         <v>-0.42</v>
       </c>
-      <c r="D71" s="10">
+      <c r="D71" s="9">
         <v>0.28000000000000003</v>
       </c>
-      <c r="E71" s="10">
+      <c r="E71" s="9">
         <v>0.03</v>
       </c>
       <c r="F71" s="4"/>
@@ -3459,16 +3457,16 @@
       <c r="A72" s="6">
         <v>46021</v>
       </c>
-      <c r="B72" s="11">
+      <c r="B72" s="10">
         <v>1.19</v>
       </c>
-      <c r="C72" s="11">
+      <c r="C72" s="10">
         <v>1.25</v>
       </c>
-      <c r="D72" s="11">
+      <c r="D72" s="10">
         <v>0.12</v>
       </c>
-      <c r="E72" s="11">
+      <c r="E72" s="10">
         <v>1.04</v>
       </c>
       <c r="F72" s="4"/>
@@ -3498,16 +3496,16 @@
       <c r="A73" s="7">
         <v>46020</v>
       </c>
-      <c r="B73" s="10">
+      <c r="B73" s="9">
         <v>0.12</v>
       </c>
-      <c r="C73" s="10">
+      <c r="C73" s="9">
         <v>0.12</v>
       </c>
-      <c r="D73" s="10">
+      <c r="D73" s="9">
         <v>0.73</v>
       </c>
-      <c r="E73" s="10">
+      <c r="E73" s="9">
         <v>-0.1</v>
       </c>
       <c r="F73" s="4"/>
@@ -3537,16 +3535,16 @@
       <c r="A74" s="6">
         <v>46017</v>
       </c>
-      <c r="B74" s="11">
+      <c r="B74" s="10">
         <v>0</v>
       </c>
-      <c r="C74" s="11">
+      <c r="C74" s="10">
         <v>0</v>
       </c>
-      <c r="D74" s="11">
+      <c r="D74" s="10">
         <v>0.42</v>
       </c>
-      <c r="E74" s="11">
+      <c r="E74" s="10">
         <v>0.66</v>
       </c>
       <c r="F74" s="4"/>
@@ -3576,16 +3574,16 @@
       <c r="A75" s="6">
         <v>46015</v>
       </c>
-      <c r="B75" s="10">
+      <c r="B75" s="9">
         <v>1.17</v>
       </c>
-      <c r="C75" s="10">
+      <c r="C75" s="9">
         <v>0.94</v>
       </c>
-      <c r="D75" s="10">
+      <c r="D75" s="9">
         <v>0.95</v>
       </c>
-      <c r="E75" s="10">
+      <c r="E75" s="9">
         <v>1.51</v>
       </c>
       <c r="F75" s="4"/>
@@ -3615,16 +3613,16 @@
       <c r="A76" s="6">
         <v>46014</v>
       </c>
-      <c r="B76" s="11">
+      <c r="B76" s="10">
         <v>0.52</v>
       </c>
-      <c r="C76" s="11">
+      <c r="C76" s="10">
         <v>0.4</v>
       </c>
-      <c r="D76" s="11">
+      <c r="D76" s="10">
         <v>0.2</v>
       </c>
-      <c r="E76" s="11">
+      <c r="E76" s="10">
         <v>0.34</v>
       </c>
       <c r="F76" s="4"/>
@@ -3654,16 +3652,16 @@
       <c r="A77" s="6">
         <v>46013</v>
       </c>
-      <c r="B77" s="10">
+      <c r="B77" s="9">
         <v>0.79</v>
       </c>
-      <c r="C77" s="10">
+      <c r="C77" s="9">
         <v>0.73</v>
       </c>
-      <c r="D77" s="10">
+      <c r="D77" s="9">
         <v>0.83</v>
       </c>
-      <c r="E77" s="10">
+      <c r="E77" s="9">
         <v>0.74</v>
       </c>
       <c r="F77" s="4"/>
@@ -3693,16 +3691,16 @@
       <c r="A78" s="7">
         <v>46010</v>
       </c>
-      <c r="B78" s="11">
+      <c r="B78" s="10">
         <v>0</v>
       </c>
-      <c r="C78" s="11">
+      <c r="C78" s="10">
         <v>0</v>
       </c>
-      <c r="D78" s="11">
+      <c r="D78" s="10">
         <v>1.1100000000000001</v>
       </c>
-      <c r="E78" s="11">
+      <c r="E78" s="10">
         <v>0.97</v>
       </c>
       <c r="F78" s="4"/>
@@ -3732,16 +3730,16 @@
       <c r="A79" s="6">
         <v>46009</v>
       </c>
-      <c r="B79" s="10">
+      <c r="B79" s="9">
         <v>1.1100000000000001</v>
       </c>
-      <c r="C79" s="10">
+      <c r="C79" s="9">
         <v>1.3</v>
       </c>
-      <c r="D79" s="10">
+      <c r="D79" s="9">
         <v>0.67</v>
       </c>
-      <c r="E79" s="10">
+      <c r="E79" s="9">
         <v>1.1200000000000001</v>
       </c>
       <c r="F79" s="4"/>
@@ -3771,16 +3769,16 @@
       <c r="A80" s="6">
         <v>46008</v>
       </c>
-      <c r="B80" s="11">
+      <c r="B80" s="10">
         <v>0.2</v>
       </c>
-      <c r="C80" s="11">
+      <c r="C80" s="10">
         <v>0.87</v>
       </c>
-      <c r="D80" s="11">
+      <c r="D80" s="10">
         <v>0.42</v>
       </c>
-      <c r="E80" s="11">
+      <c r="E80" s="10">
         <v>0.33</v>
       </c>
       <c r="F80" s="4"/>
@@ -3810,16 +3808,16 @@
       <c r="A81" s="6">
         <v>46007</v>
       </c>
-      <c r="B81" s="10">
+      <c r="B81" s="9">
         <v>0.56000000000000005</v>
       </c>
-      <c r="C81" s="10">
+      <c r="C81" s="9">
         <v>1.9</v>
       </c>
-      <c r="D81" s="10">
+      <c r="D81" s="9">
         <v>1.1100000000000001</v>
       </c>
-      <c r="E81" s="10">
+      <c r="E81" s="9">
         <v>0.71</v>
       </c>
       <c r="F81" s="4"/>
@@ -3849,16 +3847,16 @@
       <c r="A82" s="6">
         <v>46006</v>
       </c>
-      <c r="B82" s="11">
+      <c r="B82" s="10">
         <v>0.51</v>
       </c>
-      <c r="C82" s="11">
+      <c r="C82" s="10">
         <v>0.43</v>
       </c>
-      <c r="D82" s="11">
+      <c r="D82" s="10">
         <v>1.08</v>
       </c>
-      <c r="E82" s="11">
+      <c r="E82" s="10">
         <v>0.27</v>
       </c>
       <c r="F82" s="4"/>
@@ -3888,16 +3886,16 @@
       <c r="A83" s="6">
         <v>46003</v>
       </c>
-      <c r="B83" s="10">
+      <c r="B83" s="9">
         <v>0</v>
       </c>
-      <c r="C83" s="10">
+      <c r="C83" s="9">
         <v>0</v>
       </c>
-      <c r="D83" s="10">
+      <c r="D83" s="9">
         <v>1.03</v>
       </c>
-      <c r="E83" s="10">
+      <c r="E83" s="9">
         <v>1.1200000000000001</v>
       </c>
       <c r="F83" s="4"/>
@@ -3927,16 +3925,16 @@
       <c r="A84" s="6">
         <v>46002</v>
       </c>
-      <c r="B84" s="11">
+      <c r="B84" s="10">
         <v>-1.38</v>
       </c>
-      <c r="C84" s="11">
+      <c r="C84" s="10">
         <v>-1.21</v>
       </c>
-      <c r="D84" s="11">
+      <c r="D84" s="10">
         <v>-1.6</v>
       </c>
-      <c r="E84" s="11">
+      <c r="E84" s="10">
         <v>-1.69</v>
       </c>
       <c r="F84" s="4"/>
@@ -3966,16 +3964,16 @@
       <c r="A85" s="6">
         <v>46001</v>
       </c>
-      <c r="B85" s="10">
+      <c r="B85" s="9">
         <v>-0.14000000000000001</v>
       </c>
-      <c r="C85" s="10">
+      <c r="C85" s="9">
         <v>-0.23</v>
       </c>
-      <c r="D85" s="10">
+      <c r="D85" s="9">
         <v>-0.71</v>
       </c>
-      <c r="E85" s="10">
+      <c r="E85" s="9">
         <v>-0.06</v>
       </c>
       <c r="F85" s="4"/>
@@ -4005,16 +4003,16 @@
       <c r="A86" s="6">
         <v>46000</v>
       </c>
-      <c r="B86" s="11">
+      <c r="B86" s="10">
         <v>-1.87</v>
       </c>
-      <c r="C86" s="11">
+      <c r="C86" s="10">
         <v>0.98</v>
       </c>
-      <c r="D86" s="11">
+      <c r="D86" s="10">
         <v>0.6</v>
       </c>
-      <c r="E86" s="11">
+      <c r="E86" s="10">
         <v>1.39</v>
       </c>
       <c r="F86" s="4"/>
@@ -4044,16 +4042,16 @@
       <c r="A87" s="6">
         <v>45999</v>
       </c>
-      <c r="B87" s="10">
+      <c r="B87" s="9">
         <v>-0.36</v>
       </c>
-      <c r="C87" s="10">
+      <c r="C87" s="9">
         <v>-0.36</v>
       </c>
-      <c r="D87" s="10">
+      <c r="D87" s="9">
         <v>-0.03</v>
       </c>
-      <c r="E87" s="10">
+      <c r="E87" s="9">
         <v>0.68</v>
       </c>
       <c r="F87" s="4"/>
@@ -4083,16 +4081,16 @@
       <c r="A88" s="6">
         <v>45996</v>
       </c>
-      <c r="B88" s="11">
+      <c r="B88" s="10">
         <v>0</v>
       </c>
-      <c r="C88" s="11">
+      <c r="C88" s="10">
         <v>0</v>
       </c>
-      <c r="D88" s="11">
+      <c r="D88" s="10">
         <v>0.33</v>
       </c>
-      <c r="E88" s="11">
+      <c r="E88" s="10">
         <v>-1.53</v>
       </c>
       <c r="F88" s="4"/>
@@ -4122,16 +4120,16 @@
       <c r="A89" s="6">
         <v>45995</v>
       </c>
-      <c r="B89" s="10">
+      <c r="B89" s="9">
         <v>-0.7</v>
       </c>
-      <c r="C89" s="10">
+      <c r="C89" s="9">
         <v>-0.7</v>
       </c>
-      <c r="D89" s="10">
+      <c r="D89" s="9">
         <v>1.43</v>
       </c>
-      <c r="E89" s="10">
+      <c r="E89" s="9">
         <v>1.06</v>
       </c>
       <c r="F89" s="4"/>
@@ -4161,16 +4159,16 @@
       <c r="A90" s="6">
         <v>45994</v>
       </c>
-      <c r="B90" s="11">
+      <c r="B90" s="10">
         <v>0.06</v>
       </c>
-      <c r="C90" s="11">
+      <c r="C90" s="10">
         <v>0.06</v>
       </c>
-      <c r="D90" s="10">
+      <c r="D90" s="9">
         <v>0.09</v>
       </c>
-      <c r="E90" s="11">
+      <c r="E90" s="10">
         <v>-0.16</v>
       </c>
       <c r="F90" s="4"/>
@@ -4200,16 +4198,16 @@
       <c r="A91" s="6">
         <v>45993</v>
       </c>
-      <c r="B91" s="10">
+      <c r="B91" s="9">
         <v>1.28</v>
       </c>
-      <c r="C91" s="11">
+      <c r="C91" s="10">
         <v>1.18</v>
       </c>
-      <c r="D91" s="10">
+      <c r="D91" s="9">
         <v>0.82</v>
       </c>
-      <c r="E91" s="11">
+      <c r="E91" s="10">
         <v>0.68</v>
       </c>
       <c r="F91" s="4"/>
@@ -4239,16 +4237,16 @@
       <c r="A92" s="6">
         <v>45992</v>
       </c>
-      <c r="B92" s="11">
+      <c r="B92" s="10">
         <v>0.76</v>
       </c>
-      <c r="C92" s="11">
+      <c r="C92" s="10">
         <v>0.65</v>
       </c>
-      <c r="D92" s="11">
+      <c r="D92" s="10">
         <v>0.74</v>
       </c>
-      <c r="E92" s="10">
+      <c r="E92" s="9">
         <v>-0.38</v>
       </c>
       <c r="F92" s="4"/>
@@ -4278,16 +4276,16 @@
       <c r="A93" s="6">
         <v>45989</v>
       </c>
-      <c r="B93" s="11">
+      <c r="B93" s="10">
         <v>0</v>
       </c>
-      <c r="C93" s="11">
+      <c r="C93" s="10">
         <v>0</v>
       </c>
-      <c r="D93" s="11">
+      <c r="D93" s="10">
         <v>0.97</v>
       </c>
-      <c r="E93" s="10">
+      <c r="E93" s="9">
         <v>0.98</v>
       </c>
       <c r="F93" s="4"/>
@@ -4317,16 +4315,16 @@
       <c r="A94" s="6">
         <v>45988</v>
       </c>
-      <c r="B94" s="11">
+      <c r="B94" s="10">
         <v>-1.1599999999999999</v>
       </c>
-      <c r="C94" s="11">
+      <c r="C94" s="10">
         <v>-1.41</v>
       </c>
-      <c r="D94" s="11">
+      <c r="D94" s="10">
         <v>-1.88</v>
       </c>
-      <c r="E94" s="10">
+      <c r="E94" s="9">
         <v>-1.31</v>
       </c>
       <c r="F94" s="4"/>
@@ -4356,16 +4354,16 @@
       <c r="A95" s="6">
         <v>45987</v>
       </c>
-      <c r="B95" s="11">
+      <c r="B95" s="10">
         <v>-1.1399999999999999</v>
       </c>
-      <c r="C95" s="11">
+      <c r="C95" s="10">
         <v>-1.06</v>
       </c>
-      <c r="D95" s="11">
+      <c r="D95" s="10">
         <v>-0.32</v>
       </c>
-      <c r="E95" s="10">
+      <c r="E95" s="9">
         <v>-0.42</v>
       </c>
       <c r="F95" s="4"/>
@@ -4395,16 +4393,16 @@
       <c r="A96" s="6">
         <v>45986</v>
       </c>
-      <c r="B96" s="11">
+      <c r="B96" s="10">
         <v>1.79</v>
       </c>
-      <c r="C96" s="11">
+      <c r="C96" s="10">
         <v>1.26</v>
       </c>
-      <c r="D96" s="11">
+      <c r="D96" s="10">
         <v>1.31</v>
       </c>
-      <c r="E96" s="10">
+      <c r="E96" s="9">
         <v>0.56999999999999995</v>
       </c>
       <c r="F96" s="4"/>
@@ -4434,16 +4432,16 @@
       <c r="A97" s="6">
         <v>45985</v>
       </c>
-      <c r="B97" s="11">
+      <c r="B97" s="10">
         <v>0.23</v>
       </c>
-      <c r="C97" s="11">
+      <c r="C97" s="10">
         <v>1.33</v>
       </c>
-      <c r="D97" s="11">
+      <c r="D97" s="10">
         <v>0.54</v>
       </c>
-      <c r="E97" s="10">
+      <c r="E97" s="9">
         <v>0.42</v>
       </c>
       <c r="F97" s="4"/>
@@ -4473,16 +4471,16 @@
       <c r="A98" s="6">
         <v>45982</v>
       </c>
-      <c r="B98" s="11">
+      <c r="B98" s="10">
         <v>0</v>
       </c>
-      <c r="C98" s="11">
+      <c r="C98" s="10">
         <v>0</v>
       </c>
-      <c r="D98" s="11">
+      <c r="D98" s="10">
         <v>-1.3</v>
       </c>
-      <c r="E98" s="10">
+      <c r="E98" s="9">
         <v>-0.93</v>
       </c>
       <c r="F98" s="4"/>
@@ -4512,16 +4510,16 @@
       <c r="A99" s="6">
         <v>45981</v>
       </c>
-      <c r="B99" s="11">
+      <c r="B99" s="10">
         <v>0.5</v>
       </c>
-      <c r="C99" s="11">
+      <c r="C99" s="10">
         <v>0.86</v>
       </c>
-      <c r="D99" s="11">
+      <c r="D99" s="10">
         <v>1.06</v>
       </c>
-      <c r="E99" s="10">
+      <c r="E99" s="9">
         <v>-0.17</v>
       </c>
       <c r="F99" s="4"/>
@@ -4551,16 +4549,16 @@
       <c r="A100" s="6">
         <v>45980</v>
       </c>
-      <c r="B100" s="11">
+      <c r="B100" s="10">
         <v>-0.66</v>
       </c>
-      <c r="C100" s="11">
+      <c r="C100" s="10">
         <v>-0.15</v>
       </c>
-      <c r="D100" s="11">
+      <c r="D100" s="10">
         <v>-0.5</v>
       </c>
-      <c r="E100" s="10">
+      <c r="E100" s="9">
         <v>0.01</v>
       </c>
       <c r="F100" s="4"/>
@@ -4590,16 +4588,16 @@
       <c r="A101" s="6">
         <v>45979</v>
       </c>
-      <c r="B101" s="11">
+      <c r="B101" s="10">
         <v>1.62</v>
       </c>
-      <c r="C101" s="11">
+      <c r="C101" s="10">
         <v>1.9</v>
       </c>
-      <c r="D101" s="11">
+      <c r="D101" s="10">
         <v>1.75</v>
       </c>
-      <c r="E101" s="10">
+      <c r="E101" s="9">
         <v>0.6</v>
       </c>
       <c r="F101" s="4"/>
@@ -4629,16 +4627,16 @@
       <c r="A102" s="6">
         <v>45978</v>
       </c>
-      <c r="B102" s="11">
+      <c r="B102" s="10">
         <v>-0.12</v>
       </c>
-      <c r="C102" s="11">
+      <c r="C102" s="10">
         <v>-0.1</v>
       </c>
-      <c r="D102" s="11">
+      <c r="D102" s="10">
         <v>1.04</v>
       </c>
-      <c r="E102" s="10">
+      <c r="E102" s="9">
         <v>0.91</v>
       </c>
       <c r="F102" s="4"/>
@@ -4668,16 +4666,16 @@
       <c r="A103" s="6">
         <v>45975</v>
       </c>
-      <c r="B103" s="11">
+      <c r="B103" s="10">
         <v>0</v>
       </c>
-      <c r="C103" s="11">
+      <c r="C103" s="10">
         <v>0</v>
       </c>
-      <c r="D103" s="11">
+      <c r="D103" s="10">
         <v>0.12</v>
       </c>
-      <c r="E103" s="10">
+      <c r="E103" s="9">
         <v>0.45</v>
       </c>
       <c r="F103" s="4"/>
@@ -4707,16 +4705,16 @@
       <c r="A104" s="6">
         <v>45974</v>
       </c>
-      <c r="B104" s="11">
+      <c r="B104" s="10">
         <v>-0.86</v>
       </c>
-      <c r="C104" s="11">
+      <c r="C104" s="10">
         <v>-0.86</v>
       </c>
-      <c r="D104" s="11">
+      <c r="D104" s="10">
         <v>-0.51</v>
       </c>
-      <c r="E104" s="11">
+      <c r="E104" s="10">
         <v>-1.79</v>
       </c>
       <c r="F104" s="4"/>
@@ -4746,16 +4744,16 @@
       <c r="A105" s="6">
         <v>45973</v>
       </c>
-      <c r="B105" s="11">
+      <c r="B105" s="10">
         <v>0.42</v>
       </c>
-      <c r="C105" s="11">
+      <c r="C105" s="10">
         <v>0.27</v>
       </c>
-      <c r="D105" s="11">
+      <c r="D105" s="10">
         <v>0.75</v>
       </c>
-      <c r="E105" s="10">
+      <c r="E105" s="9">
         <v>0.74</v>
       </c>
       <c r="F105" s="4"/>
@@ -4785,16 +4783,16 @@
       <c r="A106" s="6">
         <v>45972</v>
       </c>
-      <c r="B106" s="11">
+      <c r="B106" s="10">
         <v>-0.67</v>
       </c>
-      <c r="C106" s="11">
+      <c r="C106" s="10">
         <v>-0.55000000000000004</v>
       </c>
-      <c r="D106" s="11">
+      <c r="D106" s="10">
         <v>1.42</v>
       </c>
-      <c r="E106" s="11">
+      <c r="E106" s="10">
         <v>2.6</v>
       </c>
       <c r="F106" s="4"/>
@@ -4824,16 +4822,16 @@
       <c r="A107" s="6">
         <v>45971</v>
       </c>
-      <c r="B107" s="11">
+      <c r="B107" s="10">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C107" s="11">
+      <c r="C107" s="10">
         <v>-0.65</v>
       </c>
-      <c r="D107" s="11">
+      <c r="D107" s="10">
         <v>0.52</v>
       </c>
-      <c r="E107" s="11">
+      <c r="E107" s="10">
         <v>0.26</v>
       </c>
       <c r="F107" s="4"/>
@@ -4863,16 +4861,16 @@
       <c r="A108" s="7">
         <v>45968</v>
       </c>
-      <c r="B108" s="10">
+      <c r="B108" s="9">
         <v>0</v>
       </c>
-      <c r="C108" s="11">
+      <c r="C108" s="10">
         <v>0</v>
       </c>
-      <c r="D108" s="11">
+      <c r="D108" s="10">
         <v>0.28999999999999998</v>
       </c>
-      <c r="E108" s="11">
+      <c r="E108" s="10">
         <v>-0.32</v>
       </c>
       <c r="F108" s="4"/>
@@ -4902,16 +4900,16 @@
       <c r="A109" s="6">
         <v>45967</v>
       </c>
-      <c r="B109" s="11">
+      <c r="B109" s="10">
         <v>0.2</v>
       </c>
-      <c r="C109" s="10">
+      <c r="C109" s="9">
         <v>1.08</v>
       </c>
-      <c r="D109" s="11">
+      <c r="D109" s="10">
         <v>0.25</v>
       </c>
-      <c r="E109" s="11">
+      <c r="E109" s="10">
         <v>-0.35</v>
       </c>
       <c r="F109" s="4"/>
@@ -4941,14 +4939,14 @@
       <c r="A110" s="7">
         <v>45965</v>
       </c>
-      <c r="B110" s="10">
+      <c r="B110" s="9">
         <v>1.79</v>
       </c>
-      <c r="C110" s="10">
+      <c r="C110" s="9">
         <v>1.98</v>
       </c>
-      <c r="D110" s="12"/>
-      <c r="E110" s="11">
+      <c r="D110" s="11"/>
+      <c r="E110" s="10">
         <v>1.68</v>
       </c>
       <c r="F110" s="4"/>
@@ -4978,14 +4976,14 @@
       <c r="A111" s="6">
         <v>45964</v>
       </c>
-      <c r="B111" s="11">
+      <c r="B111" s="10">
         <v>0.34</v>
       </c>
-      <c r="C111" s="11">
+      <c r="C111" s="10">
         <v>0.63</v>
       </c>
-      <c r="D111" s="12"/>
-      <c r="E111" s="11">
+      <c r="D111" s="11"/>
+      <c r="E111" s="10">
         <v>1.38</v>
       </c>
       <c r="F111" s="4"/>
@@ -5015,10 +5013,10 @@
       <c r="A112" s="6">
         <v>45961</v>
       </c>
-      <c r="B112" s="11">
+      <c r="B112" s="10">
         <v>-1.99</v>
       </c>
-      <c r="C112" s="11">
+      <c r="C112" s="10">
         <v>-1.1000000000000001</v>
       </c>
       <c r="D112" s="4"/>
@@ -5050,10 +5048,10 @@
       <c r="A113" s="7">
         <v>45960</v>
       </c>
-      <c r="B113" s="10">
+      <c r="B113" s="9">
         <v>1.84</v>
       </c>
-      <c r="C113" s="11">
+      <c r="C113" s="10">
         <v>1.33</v>
       </c>
       <c r="D113" s="4"/>
@@ -5085,10 +5083,10 @@
       <c r="A114" s="6">
         <v>45959</v>
       </c>
-      <c r="B114" s="11">
+      <c r="B114" s="10">
         <v>0.46</v>
       </c>
-      <c r="C114" s="10">
+      <c r="C114" s="9">
         <v>0.27</v>
       </c>
       <c r="D114" s="4"/>
@@ -5120,10 +5118,10 @@
       <c r="A115" s="6">
         <v>45958</v>
       </c>
-      <c r="B115" s="11">
+      <c r="B115" s="10">
         <v>0.97</v>
       </c>
-      <c r="C115" s="11">
+      <c r="C115" s="10">
         <v>0.54</v>
       </c>
       <c r="D115" s="4"/>
@@ -5155,10 +5153,10 @@
       <c r="A116" s="6">
         <v>45957</v>
       </c>
-      <c r="B116" s="11">
+      <c r="B116" s="10">
         <v>-1.95</v>
       </c>
-      <c r="C116" s="11">
+      <c r="C116" s="10">
         <v>-1.24</v>
       </c>
       <c r="D116" s="4"/>
@@ -5190,10 +5188,10 @@
       <c r="A117" s="7">
         <v>45954</v>
       </c>
-      <c r="B117" s="10">
+      <c r="B117" s="9">
         <v>0.65</v>
       </c>
-      <c r="C117" s="10">
+      <c r="C117" s="9">
         <v>0.56000000000000005</v>
       </c>
       <c r="D117" s="4"/>
@@ -5225,10 +5223,10 @@
       <c r="A118" s="6">
         <v>45953</v>
       </c>
-      <c r="B118" s="11">
+      <c r="B118" s="10">
         <v>1.73</v>
       </c>
-      <c r="C118" s="11">
+      <c r="C118" s="10">
         <v>1.4</v>
       </c>
       <c r="D118" s="4"/>
@@ -5260,10 +5258,10 @@
       <c r="A119" s="6">
         <v>45951</v>
       </c>
-      <c r="B119" s="11">
+      <c r="B119" s="10">
         <v>0.01</v>
       </c>
-      <c r="C119" s="11">
+      <c r="C119" s="10">
         <v>0.01</v>
       </c>
       <c r="D119" s="4"/>
@@ -5295,10 +5293,10 @@
       <c r="A120" s="7">
         <v>45950</v>
       </c>
-      <c r="B120" s="10">
+      <c r="B120" s="9">
         <v>-1.85</v>
       </c>
-      <c r="C120" s="11">
+      <c r="C120" s="10">
         <v>0.51</v>
       </c>
       <c r="D120" s="4"/>
@@ -5330,10 +5328,10 @@
       <c r="A121" s="6">
         <v>45947</v>
       </c>
-      <c r="B121" s="11">
+      <c r="B121" s="10">
         <v>-1.61</v>
       </c>
-      <c r="C121" s="10">
+      <c r="C121" s="9">
         <v>-1.76</v>
       </c>
       <c r="D121" s="4"/>
@@ -5365,10 +5363,10 @@
       <c r="A122" s="6">
         <v>45946</v>
       </c>
-      <c r="B122" s="11">
+      <c r="B122" s="10">
         <v>2</v>
       </c>
-      <c r="C122" s="11">
+      <c r="C122" s="10">
         <v>1.02</v>
       </c>
       <c r="D122" s="4"/>
@@ -5400,10 +5398,10 @@
       <c r="A123" s="6">
         <v>45945</v>
       </c>
-      <c r="B123" s="11">
+      <c r="B123" s="10">
         <v>0.57999999999999996</v>
       </c>
-      <c r="C123" s="11">
+      <c r="C123" s="10">
         <v>0.41</v>
       </c>
       <c r="D123" s="4"/>
@@ -5435,10 +5433,10 @@
       <c r="A124" s="7">
         <v>45944</v>
       </c>
-      <c r="B124" s="10">
+      <c r="B124" s="9">
         <v>-0.2</v>
       </c>
-      <c r="C124" s="10">
+      <c r="C124" s="9">
         <v>0.38</v>
       </c>
       <c r="D124" s="4"/>
@@ -5470,10 +5468,10 @@
       <c r="A125" s="6">
         <v>45943</v>
       </c>
-      <c r="B125" s="11">
+      <c r="B125" s="10">
         <v>1</v>
       </c>
-      <c r="C125" s="11">
+      <c r="C125" s="10">
         <v>1</v>
       </c>
       <c r="D125" s="4"/>
@@ -5505,10 +5503,10 @@
       <c r="A126" s="6">
         <v>45940</v>
       </c>
-      <c r="B126" s="11">
+      <c r="B126" s="10">
         <v>-2</v>
       </c>
-      <c r="C126" s="11">
+      <c r="C126" s="10">
         <v>-1.22</v>
       </c>
       <c r="D126" s="4"/>
@@ -5540,10 +5538,10 @@
       <c r="A127" s="7">
         <v>45939</v>
       </c>
-      <c r="B127" s="10">
+      <c r="B127" s="9">
         <v>0.75</v>
       </c>
-      <c r="C127" s="11">
+      <c r="C127" s="10">
         <v>0.75</v>
       </c>
       <c r="D127" s="4"/>
@@ -5575,10 +5573,10 @@
       <c r="A128" s="6">
         <v>45938</v>
       </c>
-      <c r="B128" s="11">
+      <c r="B128" s="10">
         <v>-0.26</v>
       </c>
-      <c r="C128" s="10">
+      <c r="C128" s="9">
         <v>-0.26</v>
       </c>
       <c r="D128" s="4"/>
@@ -5610,10 +5608,10 @@
       <c r="A129" s="6">
         <v>45937</v>
       </c>
-      <c r="B129" s="11">
+      <c r="B129" s="10">
         <v>-0.2</v>
       </c>
-      <c r="C129" s="11">
+      <c r="C129" s="10">
         <v>-0.2</v>
       </c>
       <c r="D129" s="4"/>
@@ -5645,10 +5643,10 @@
       <c r="A130" s="6">
         <v>45936</v>
       </c>
-      <c r="B130" s="11">
+      <c r="B130" s="10">
         <v>-0.43</v>
       </c>
-      <c r="C130" s="11">
+      <c r="C130" s="10">
         <v>-0.43</v>
       </c>
       <c r="D130" s="4"/>
@@ -5680,10 +5678,10 @@
       <c r="A131" s="7">
         <v>45933</v>
       </c>
-      <c r="B131" s="10">
+      <c r="B131" s="9">
         <v>0.4</v>
       </c>
-      <c r="C131" s="10">
+      <c r="C131" s="9">
         <v>0.4</v>
       </c>
       <c r="D131" s="4"/>
@@ -5715,10 +5713,10 @@
       <c r="A132" s="6">
         <v>45931</v>
       </c>
-      <c r="B132" s="11">
+      <c r="B132" s="10">
         <v>0.49</v>
       </c>
-      <c r="C132" s="11">
+      <c r="C132" s="10">
         <v>0.49</v>
       </c>
       <c r="D132" s="4"/>
@@ -5750,10 +5748,10 @@
       <c r="A133" s="7">
         <v>45930</v>
       </c>
-      <c r="B133" s="10">
+      <c r="B133" s="9">
         <v>0.08</v>
       </c>
-      <c r="C133" s="11">
+      <c r="C133" s="10">
         <v>0.08</v>
       </c>
       <c r="D133" s="4"/>
@@ -5785,10 +5783,10 @@
       <c r="A134" s="6">
         <v>45929</v>
       </c>
-      <c r="B134" s="11">
+      <c r="B134" s="10">
         <v>0.27</v>
       </c>
-      <c r="C134" s="11">
+      <c r="C134" s="10">
         <v>0.27</v>
       </c>
       <c r="D134" s="4"/>
@@ -5820,10 +5818,10 @@
       <c r="A135" s="6">
         <v>45926</v>
       </c>
-      <c r="B135" s="11">
+      <c r="B135" s="10">
         <v>1.31</v>
       </c>
-      <c r="C135" s="11">
+      <c r="C135" s="10">
         <v>1.31</v>
       </c>
       <c r="D135" s="4"/>
@@ -5855,10 +5853,10 @@
       <c r="A136" s="6">
         <v>45925</v>
       </c>
-      <c r="B136" s="11">
+      <c r="B136" s="10">
         <v>0.97</v>
       </c>
-      <c r="C136" s="10">
+      <c r="C136" s="9">
         <v>0.97</v>
       </c>
       <c r="D136" s="4"/>
@@ -5890,10 +5888,10 @@
       <c r="A137" s="6">
         <v>45924</v>
       </c>
-      <c r="B137" s="11">
+      <c r="B137" s="10">
         <v>0.96</v>
       </c>
-      <c r="C137" s="11">
+      <c r="C137" s="10">
         <v>0.96</v>
       </c>
       <c r="D137" s="4"/>
@@ -5925,10 +5923,10 @@
       <c r="A138" s="7">
         <v>45923</v>
       </c>
-      <c r="B138" s="10">
+      <c r="B138" s="9">
         <v>-0.08</v>
       </c>
-      <c r="C138" s="10">
+      <c r="C138" s="9">
         <v>-0.08</v>
       </c>
       <c r="D138" s="4"/>
@@ -5960,10 +5958,10 @@
       <c r="A139" s="6">
         <v>45922</v>
       </c>
-      <c r="B139" s="11">
+      <c r="B139" s="10">
         <v>0.96</v>
       </c>
-      <c r="C139" s="11">
+      <c r="C139" s="10">
         <v>0.96</v>
       </c>
       <c r="D139" s="4"/>
@@ -5995,10 +5993,10 @@
       <c r="A140" s="7">
         <v>45919</v>
       </c>
-      <c r="B140" s="10">
+      <c r="B140" s="9">
         <v>-0.53</v>
       </c>
-      <c r="C140" s="11">
+      <c r="C140" s="10">
         <v>-0.53</v>
       </c>
       <c r="D140" s="4"/>
@@ -6030,10 +6028,10 @@
       <c r="A141" s="6">
         <v>45918</v>
       </c>
-      <c r="B141" s="11">
+      <c r="B141" s="10">
         <v>1.98</v>
       </c>
-      <c r="C141" s="11">
+      <c r="C141" s="10">
         <v>1.98</v>
       </c>
       <c r="D141" s="4"/>
@@ -6065,10 +6063,10 @@
       <c r="A142" s="6">
         <v>45917</v>
       </c>
-      <c r="B142" s="11">
+      <c r="B142" s="10">
         <v>0.28000000000000003</v>
       </c>
-      <c r="C142" s="11">
+      <c r="C142" s="10">
         <v>0.28000000000000003</v>
       </c>
       <c r="D142" s="4"/>
@@ -6100,10 +6098,10 @@
       <c r="A143" s="6">
         <v>45916</v>
       </c>
-      <c r="B143" s="11">
+      <c r="B143" s="10">
         <v>-0.13</v>
       </c>
-      <c r="C143" s="10">
+      <c r="C143" s="9">
         <v>-0.13</v>
       </c>
       <c r="D143" s="4"/>
@@ -6135,10 +6133,10 @@
       <c r="A144" s="6">
         <v>45915</v>
       </c>
-      <c r="B144" s="11">
+      <c r="B144" s="10">
         <v>0.42</v>
       </c>
-      <c r="C144" s="11">
+      <c r="C144" s="10">
         <v>0.42</v>
       </c>
       <c r="D144" s="4"/>
@@ -6170,10 +6168,10 @@
       <c r="A145" s="6">
         <v>45912</v>
       </c>
-      <c r="B145" s="11">
+      <c r="B145" s="10">
         <v>-0.15</v>
       </c>
-      <c r="C145" s="11">
+      <c r="C145" s="10">
         <v>-0.15</v>
       </c>
       <c r="D145" s="4"/>
@@ -6205,10 +6203,10 @@
       <c r="A146" s="6">
         <v>45911</v>
       </c>
-      <c r="B146" s="11">
+      <c r="B146" s="10">
         <v>1.36</v>
       </c>
-      <c r="C146" s="10">
+      <c r="C146" s="9">
         <v>1.36</v>
       </c>
       <c r="D146" s="4"/>
@@ -6240,10 +6238,10 @@
       <c r="A147" s="6">
         <v>45910</v>
       </c>
-      <c r="B147" s="11">
+      <c r="B147" s="10">
         <v>0.46</v>
       </c>
-      <c r="C147" s="11">
+      <c r="C147" s="10">
         <v>0.46</v>
       </c>
       <c r="D147" s="4"/>
@@ -6275,10 +6273,10 @@
       <c r="A148" s="6">
         <v>45909</v>
       </c>
-      <c r="B148" s="11">
+      <c r="B148" s="10">
         <v>1.8</v>
       </c>
-      <c r="C148" s="11">
+      <c r="C148" s="10">
         <v>1.8</v>
       </c>
       <c r="D148" s="4"/>
@@ -6310,10 +6308,10 @@
       <c r="A149" s="6">
         <v>45908</v>
       </c>
-      <c r="B149" s="11">
+      <c r="B149" s="10">
         <v>-0.11</v>
       </c>
-      <c r="C149" s="10">
+      <c r="C149" s="9">
         <v>-0.11</v>
       </c>
       <c r="D149" s="4"/>
@@ -6345,10 +6343,10 @@
       <c r="A150" s="6">
         <v>45905</v>
       </c>
-      <c r="B150" s="11">
+      <c r="B150" s="10">
         <v>-1.8</v>
       </c>
-      <c r="C150" s="11">
+      <c r="C150" s="10">
         <v>-2.4</v>
       </c>
       <c r="D150" s="4"/>
@@ -6380,10 +6378,10 @@
       <c r="A151" s="7">
         <v>45904</v>
       </c>
-      <c r="B151" s="10">
+      <c r="B151" s="9">
         <v>0.12</v>
       </c>
-      <c r="C151" s="11">
+      <c r="C151" s="10">
         <v>0.12</v>
       </c>
       <c r="D151" s="4"/>
@@ -6415,10 +6413,10 @@
       <c r="A152" s="6">
         <v>45903</v>
       </c>
-      <c r="B152" s="11">
+      <c r="B152" s="10">
         <v>0.15</v>
       </c>
-      <c r="C152" s="10">
+      <c r="C152" s="9">
         <v>0.15</v>
       </c>
       <c r="D152" s="4"/>
@@ -6450,10 +6448,10 @@
       <c r="A153" s="7">
         <v>45902</v>
       </c>
-      <c r="B153" s="10">
+      <c r="B153" s="9">
         <v>1.02</v>
       </c>
-      <c r="C153" s="11">
+      <c r="C153" s="10">
         <v>1.02</v>
       </c>
       <c r="D153" s="4"/>
@@ -6485,10 +6483,10 @@
       <c r="A154" s="6">
         <v>45901</v>
       </c>
-      <c r="B154" s="11">
+      <c r="B154" s="10">
         <v>0.51</v>
       </c>
-      <c r="C154" s="10">
+      <c r="C154" s="9">
         <v>0.51</v>
       </c>
       <c r="D154" s="4"/>
@@ -6520,10 +6518,10 @@
       <c r="A155" s="7">
         <v>45898</v>
       </c>
-      <c r="B155" s="10">
+      <c r="B155" s="9">
         <v>0.48</v>
       </c>
-      <c r="C155" s="11">
+      <c r="C155" s="10">
         <v>0.48</v>
       </c>
       <c r="D155" s="4"/>
@@ -6555,10 +6553,10 @@
       <c r="A156" s="6">
         <v>45897</v>
       </c>
-      <c r="B156" s="11">
+      <c r="B156" s="10">
         <v>-1.49</v>
       </c>
-      <c r="C156" s="10">
+      <c r="C156" s="9">
         <v>-0.27</v>
       </c>
       <c r="D156" s="4"/>
@@ -6590,10 +6588,10 @@
       <c r="A157" s="7">
         <v>45896</v>
       </c>
-      <c r="B157" s="10">
+      <c r="B157" s="9">
         <v>0</v>
       </c>
-      <c r="C157" s="11">
+      <c r="C157" s="10">
         <v>0</v>
       </c>
       <c r="D157" s="4"/>
@@ -6625,10 +6623,10 @@
       <c r="A158" s="6">
         <v>45895</v>
       </c>
-      <c r="B158" s="11">
+      <c r="B158" s="10">
         <v>-0.36</v>
       </c>
-      <c r="C158" s="10">
+      <c r="C158" s="9">
         <v>-0.36</v>
       </c>
       <c r="D158" s="4"/>
@@ -6660,10 +6658,10 @@
       <c r="A159" s="7">
         <v>45894</v>
       </c>
-      <c r="B159" s="10">
+      <c r="B159" s="9">
         <v>0.67</v>
       </c>
-      <c r="C159" s="11">
+      <c r="C159" s="10">
         <v>0.67</v>
       </c>
       <c r="D159" s="4"/>
@@ -6695,10 +6693,10 @@
       <c r="A160" s="6">
         <v>45891</v>
       </c>
-      <c r="B160" s="11">
+      <c r="B160" s="10">
         <v>0</v>
       </c>
-      <c r="C160" s="10">
+      <c r="C160" s="9">
         <v>0</v>
       </c>
       <c r="D160" s="4"/>
@@ -6730,10 +6728,10 @@
       <c r="A161" s="7">
         <v>45890</v>
       </c>
-      <c r="B161" s="10">
+      <c r="B161" s="9">
         <v>0.8</v>
       </c>
-      <c r="C161" s="11">
+      <c r="C161" s="10">
         <v>0.8</v>
       </c>
       <c r="D161" s="4"/>
@@ -6765,10 +6763,10 @@
       <c r="A162" s="6">
         <v>45889</v>
       </c>
-      <c r="B162" s="11">
+      <c r="B162" s="10">
         <v>0.7</v>
       </c>
-      <c r="C162" s="10">
+      <c r="C162" s="9">
         <v>0.7</v>
       </c>
       <c r="D162" s="4"/>
@@ -6800,10 +6798,10 @@
       <c r="A163" s="7">
         <v>45888</v>
       </c>
-      <c r="B163" s="10">
+      <c r="B163" s="9">
         <v>1.07</v>
       </c>
-      <c r="C163" s="11">
+      <c r="C163" s="10">
         <v>1.07</v>
       </c>
       <c r="D163" s="4"/>
@@ -6835,10 +6833,10 @@
       <c r="A164" s="6">
         <v>45887</v>
       </c>
-      <c r="B164" s="11">
+      <c r="B164" s="10">
         <v>1.56</v>
       </c>
-      <c r="C164" s="11">
+      <c r="C164" s="10">
         <v>1.56</v>
       </c>
       <c r="D164" s="4"/>
@@ -6870,10 +6868,10 @@
       <c r="A165" s="6">
         <v>45883</v>
       </c>
-      <c r="B165" s="11">
+      <c r="B165" s="10">
         <v>1.82</v>
       </c>
-      <c r="C165" s="10">
+      <c r="C165" s="9">
         <v>1.82</v>
       </c>
       <c r="D165" s="4"/>
@@ -6905,10 +6903,10 @@
       <c r="A166" s="7">
         <v>45882</v>
       </c>
-      <c r="B166" s="10">
+      <c r="B166" s="9">
         <v>0.6</v>
       </c>
-      <c r="C166" s="11">
+      <c r="C166" s="10">
         <v>0.6</v>
       </c>
       <c r="D166" s="4"/>
@@ -6940,10 +6938,10 @@
       <c r="A167" s="6">
         <v>45881</v>
       </c>
-      <c r="B167" s="11">
+      <c r="B167" s="10">
         <v>-1.82</v>
       </c>
-      <c r="C167" s="11">
+      <c r="C167" s="10">
         <v>-0.69</v>
       </c>
       <c r="D167" s="4"/>
@@ -6975,10 +6973,10 @@
       <c r="A168" s="6">
         <v>45880</v>
       </c>
-      <c r="B168" s="11">
+      <c r="B168" s="10">
         <v>-0.68</v>
       </c>
-      <c r="C168" s="10">
+      <c r="C168" s="9">
         <v>-0.68</v>
       </c>
       <c r="D168" s="4"/>
@@ -7010,10 +7008,10 @@
       <c r="A169" s="7">
         <v>45877</v>
       </c>
-      <c r="B169" s="10">
+      <c r="B169" s="9">
         <v>0.17</v>
       </c>
-      <c r="C169" s="11">
+      <c r="C169" s="10">
         <v>0.17</v>
       </c>
       <c r="D169" s="4"/>
@@ -7045,10 +7043,10 @@
       <c r="A170" s="6">
         <v>45876</v>
       </c>
-      <c r="B170" s="11">
+      <c r="B170" s="10">
         <v>1.75</v>
       </c>
-      <c r="C170" s="11">
+      <c r="C170" s="10">
         <v>1.75</v>
       </c>
       <c r="D170" s="4"/>
@@ -7080,10 +7078,10 @@
       <c r="A171" s="6">
         <v>45875</v>
       </c>
-      <c r="B171" s="11">
+      <c r="B171" s="10">
         <v>0.72</v>
       </c>
-      <c r="C171" s="10">
+      <c r="C171" s="9">
         <v>0.72</v>
       </c>
       <c r="D171" s="4"/>
@@ -7115,10 +7113,10 @@
       <c r="A172" s="7">
         <v>45874</v>
       </c>
-      <c r="B172" s="10">
+      <c r="B172" s="9">
         <v>1.81</v>
       </c>
-      <c r="C172" s="11">
+      <c r="C172" s="10">
         <v>1.81</v>
       </c>
       <c r="D172" s="4"/>
@@ -7150,10 +7148,10 @@
       <c r="A173" s="6">
         <v>45873</v>
       </c>
-      <c r="B173" s="11">
+      <c r="B173" s="10">
         <v>0</v>
       </c>
-      <c r="C173" s="10">
+      <c r="C173" s="9">
         <v>0</v>
       </c>
       <c r="D173" s="4"/>
@@ -7185,10 +7183,10 @@
       <c r="A174" s="6">
         <v>45870</v>
       </c>
-      <c r="B174" s="10">
+      <c r="B174" s="9">
         <v>0.01</v>
       </c>
-      <c r="C174" s="10">
+      <c r="C174" s="9">
         <v>0.01</v>
       </c>
       <c r="D174" s="4"/>
@@ -7220,10 +7218,10 @@
       <c r="A175" s="6">
         <v>45869</v>
       </c>
-      <c r="B175" s="11">
+      <c r="B175" s="10">
         <v>1.61</v>
       </c>
-      <c r="C175" s="11">
+      <c r="C175" s="10">
         <v>1.61</v>
       </c>
       <c r="D175" s="4"/>
@@ -7255,10 +7253,10 @@
       <c r="A176" s="6">
         <v>45868</v>
       </c>
-      <c r="B176" s="10">
+      <c r="B176" s="9">
         <v>-0.65</v>
       </c>
-      <c r="C176" s="10">
+      <c r="C176" s="9">
         <v>-0.65</v>
       </c>
       <c r="D176" s="4"/>
@@ -7290,10 +7288,10 @@
       <c r="A177" s="6">
         <v>45867</v>
       </c>
-      <c r="B177" s="11">
+      <c r="B177" s="10">
         <v>1.41</v>
       </c>
-      <c r="C177" s="11">
+      <c r="C177" s="10">
         <v>2.42</v>
       </c>
       <c r="D177" s="4"/>
@@ -7325,10 +7323,10 @@
       <c r="A178" s="6">
         <v>45866</v>
       </c>
-      <c r="B178" s="10">
+      <c r="B178" s="9">
         <v>-0.05</v>
       </c>
-      <c r="C178" s="10">
+      <c r="C178" s="9">
         <v>-0.05</v>
       </c>
       <c r="D178" s="4"/>
@@ -7360,10 +7358,10 @@
       <c r="A179" s="6">
         <v>45863</v>
       </c>
-      <c r="B179" s="11">
+      <c r="B179" s="10">
         <v>0.12</v>
       </c>
-      <c r="C179" s="11">
+      <c r="C179" s="10">
         <v>0.12</v>
       </c>
       <c r="D179" s="4"/>
@@ -7395,10 +7393,10 @@
       <c r="A180" s="6">
         <v>45862</v>
       </c>
-      <c r="B180" s="10">
+      <c r="B180" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C180" s="10">
+      <c r="C180" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D180" s="4"/>
@@ -7430,10 +7428,10 @@
       <c r="A181" s="6">
         <v>45861</v>
       </c>
-      <c r="B181" s="11">
+      <c r="B181" s="10">
         <v>0.91</v>
       </c>
-      <c r="C181" s="11">
+      <c r="C181" s="10">
         <v>0.91</v>
       </c>
       <c r="D181" s="4"/>
@@ -7465,10 +7463,10 @@
       <c r="A182" s="6">
         <v>45860</v>
       </c>
-      <c r="B182" s="10">
+      <c r="B182" s="9">
         <v>1.37</v>
       </c>
-      <c r="C182" s="10">
+      <c r="C182" s="9">
         <v>1.37</v>
       </c>
       <c r="D182" s="4"/>
@@ -7500,10 +7498,10 @@
       <c r="A183" s="6">
         <v>45859</v>
       </c>
-      <c r="B183" s="11">
+      <c r="B183" s="10">
         <v>1</v>
       </c>
-      <c r="C183" s="11">
+      <c r="C183" s="10">
         <v>1</v>
       </c>
       <c r="D183" s="4"/>
@@ -7535,10 +7533,10 @@
       <c r="A184" s="6">
         <v>45856</v>
       </c>
-      <c r="B184" s="10">
+      <c r="B184" s="9">
         <v>-0.13</v>
       </c>
-      <c r="C184" s="10">
+      <c r="C184" s="9">
         <v>-0.13</v>
       </c>
       <c r="D184" s="4"/>
@@ -7570,10 +7568,10 @@
       <c r="A185" s="6">
         <v>45855</v>
       </c>
-      <c r="B185" s="11">
+      <c r="B185" s="10">
         <v>1.77</v>
       </c>
-      <c r="C185" s="11">
+      <c r="C185" s="10">
         <v>1.77</v>
       </c>
       <c r="D185" s="4"/>
@@ -7605,10 +7603,10 @@
       <c r="A186" s="6">
         <v>45854</v>
       </c>
-      <c r="B186" s="10">
+      <c r="B186" s="9">
         <v>0.34</v>
       </c>
-      <c r="C186" s="10">
+      <c r="C186" s="9">
         <v>0.34</v>
       </c>
       <c r="D186" s="4"/>
@@ -7640,10 +7638,10 @@
       <c r="A187" s="6">
         <v>45853</v>
       </c>
-      <c r="B187" s="11">
+      <c r="B187" s="10">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C187" s="11">
+      <c r="C187" s="10">
         <v>1.1000000000000001</v>
       </c>
       <c r="D187" s="4"/>
@@ -7675,10 +7673,10 @@
       <c r="A188" s="6">
         <v>45852</v>
       </c>
-      <c r="B188" s="10">
+      <c r="B188" s="9">
         <v>-0.27</v>
       </c>
-      <c r="C188" s="10">
+      <c r="C188" s="9">
         <v>-0.27</v>
       </c>
       <c r="D188" s="4"/>
@@ -7902,7 +7900,7 @@
       <c r="E195" s="4"/>
       <c r="F195" s="4"/>
       <c r="G195" s="3">
-        <v>0.72</v>
+        <v>1.03</v>
       </c>
       <c r="H195" s="4"/>
       <c r="I195" s="4"/>
@@ -7933,7 +7931,7 @@
       <c r="E196" s="4"/>
       <c r="F196" s="4"/>
       <c r="G196" s="3">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="H196" s="4"/>
       <c r="I196" s="4"/>
@@ -7964,7 +7962,7 @@
       <c r="E197" s="4"/>
       <c r="F197" s="4"/>
       <c r="G197" s="3">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="H197" s="4"/>
       <c r="I197" s="4"/>
@@ -7986,13 +7984,17 @@
       <c r="Y197" s="4"/>
     </row>
     <row r="198" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="8"/>
+      <c r="A198" s="6">
+        <v>45838</v>
+      </c>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
       <c r="D198" s="4"/>
       <c r="E198" s="4"/>
       <c r="F198" s="4"/>
-      <c r="G198" s="4"/>
+      <c r="G198" s="4">
+        <v>3.46</v>
+      </c>
       <c r="H198" s="4"/>
       <c r="I198" s="4"/>
       <c r="J198" s="4"/>
@@ -8013,13 +8015,17 @@
       <c r="Y198" s="4"/>
     </row>
     <row r="199" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="8"/>
+      <c r="A199" s="6">
+        <v>45835</v>
+      </c>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
       <c r="D199" s="4"/>
       <c r="E199" s="4"/>
       <c r="F199" s="4"/>
-      <c r="G199" s="4"/>
+      <c r="G199" s="4">
+        <v>0.11</v>
+      </c>
       <c r="H199" s="4"/>
       <c r="I199" s="4"/>
       <c r="J199" s="4"/>
@@ -8040,13 +8046,17 @@
       <c r="Y199" s="4"/>
     </row>
     <row r="200" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="8"/>
+      <c r="A200" s="6">
+        <v>45834</v>
+      </c>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
       <c r="D200" s="4"/>
       <c r="E200" s="4"/>
       <c r="F200" s="4"/>
-      <c r="G200" s="4"/>
+      <c r="G200" s="4">
+        <v>7.75</v>
+      </c>
       <c r="H200" s="4"/>
       <c r="I200" s="4"/>
       <c r="J200" s="4"/>
@@ -8067,13 +8077,17 @@
       <c r="Y200" s="4"/>
     </row>
     <row r="201" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="8"/>
+      <c r="A201" s="6">
+        <v>45833</v>
+      </c>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
       <c r="D201" s="4"/>
       <c r="E201" s="4"/>
       <c r="F201" s="4"/>
-      <c r="G201" s="4"/>
+      <c r="G201" s="4">
+        <v>-3.52</v>
+      </c>
       <c r="H201" s="4"/>
       <c r="I201" s="4"/>
       <c r="J201" s="4"/>
@@ -8094,13 +8108,17 @@
       <c r="Y201" s="4"/>
     </row>
     <row r="202" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="4"/>
+      <c r="A202" s="6">
+        <v>45832</v>
+      </c>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
       <c r="D202" s="4"/>
       <c r="E202" s="4"/>
       <c r="F202" s="4"/>
-      <c r="G202" s="4"/>
+      <c r="G202" s="4">
+        <v>1.65</v>
+      </c>
       <c r="H202" s="4"/>
       <c r="I202" s="4"/>
       <c r="J202" s="4"/>
@@ -8121,13 +8139,17 @@
       <c r="Y202" s="4"/>
     </row>
     <row r="203" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="4"/>
+      <c r="A203" s="6">
+        <v>45831</v>
+      </c>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
       <c r="D203" s="4"/>
       <c r="E203" s="4"/>
       <c r="F203" s="4"/>
-      <c r="G203" s="4"/>
+      <c r="G203" s="4">
+        <v>-6.06</v>
+      </c>
       <c r="H203" s="4"/>
       <c r="I203" s="4"/>
       <c r="J203" s="4"/>
@@ -8148,13 +8170,17 @@
       <c r="Y203" s="4"/>
     </row>
     <row r="204" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="4"/>
+      <c r="A204" s="6">
+        <v>45828</v>
+      </c>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
       <c r="D204" s="4"/>
       <c r="E204" s="4"/>
       <c r="F204" s="4"/>
-      <c r="G204" s="4"/>
+      <c r="G204" s="4">
+        <v>4.43</v>
+      </c>
       <c r="H204" s="4"/>
       <c r="I204" s="4"/>
       <c r="J204" s="4"/>
@@ -8175,13 +8201,17 @@
       <c r="Y204" s="4"/>
     </row>
     <row r="205" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="4"/>
+      <c r="A205" s="6">
+        <v>45827</v>
+      </c>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
       <c r="D205" s="4"/>
       <c r="E205" s="4"/>
       <c r="F205" s="4"/>
-      <c r="G205" s="4"/>
+      <c r="G205" s="4">
+        <v>-3.19</v>
+      </c>
       <c r="H205" s="4"/>
       <c r="I205" s="4"/>
       <c r="J205" s="4"/>
@@ -8202,13 +8232,17 @@
       <c r="Y205" s="4"/>
     </row>
     <row r="206" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="4"/>
+      <c r="A206" s="6">
+        <v>45826</v>
+      </c>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
       <c r="D206" s="4"/>
       <c r="E206" s="4"/>
       <c r="F206" s="4"/>
-      <c r="G206" s="4"/>
+      <c r="G206" s="4">
+        <v>1.71</v>
+      </c>
       <c r="H206" s="4"/>
       <c r="I206" s="4"/>
       <c r="J206" s="4"/>
@@ -8229,13 +8263,17 @@
       <c r="Y206" s="4"/>
     </row>
     <row r="207" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="4"/>
+      <c r="A207" s="6">
+        <v>45825</v>
+      </c>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
       <c r="D207" s="4"/>
       <c r="E207" s="4"/>
       <c r="F207" s="4"/>
-      <c r="G207" s="4"/>
+      <c r="G207" s="4">
+        <v>1.49</v>
+      </c>
       <c r="H207" s="4"/>
       <c r="I207" s="4"/>
       <c r="J207" s="4"/>
@@ -8256,13 +8294,17 @@
       <c r="Y207" s="4"/>
     </row>
     <row r="208" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="4"/>
+      <c r="A208" s="6">
+        <v>45824</v>
+      </c>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
       <c r="D208" s="4"/>
       <c r="E208" s="4"/>
       <c r="F208" s="4"/>
-      <c r="G208" s="4"/>
+      <c r="G208" s="4">
+        <v>6.65</v>
+      </c>
       <c r="H208" s="4"/>
       <c r="I208" s="4"/>
       <c r="J208" s="4"/>
@@ -8283,13 +8325,17 @@
       <c r="Y208" s="4"/>
     </row>
     <row r="209" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="4"/>
+      <c r="A209" s="6">
+        <v>45821</v>
+      </c>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
       <c r="D209" s="4"/>
       <c r="E209" s="4"/>
       <c r="F209" s="4"/>
-      <c r="G209" s="4"/>
+      <c r="G209" s="4">
+        <v>-0.64</v>
+      </c>
       <c r="H209" s="4"/>
       <c r="I209" s="4"/>
       <c r="J209" s="4"/>
@@ -8310,13 +8356,17 @@
       <c r="Y209" s="4"/>
     </row>
     <row r="210" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="4"/>
+      <c r="A210" s="6">
+        <v>45820</v>
+      </c>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
       <c r="D210" s="4"/>
       <c r="E210" s="4"/>
       <c r="F210" s="4"/>
-      <c r="G210" s="4"/>
+      <c r="G210" s="4">
+        <v>4.74</v>
+      </c>
       <c r="H210" s="4"/>
       <c r="I210" s="4"/>
       <c r="J210" s="4"/>
@@ -8337,13 +8387,17 @@
       <c r="Y210" s="4"/>
     </row>
     <row r="211" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="4"/>
+      <c r="A211" s="6">
+        <v>45819</v>
+      </c>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
       <c r="D211" s="4"/>
       <c r="E211" s="4"/>
       <c r="F211" s="4"/>
-      <c r="G211" s="4"/>
+      <c r="G211" s="4">
+        <v>-0.41</v>
+      </c>
       <c r="H211" s="4"/>
       <c r="I211" s="4"/>
       <c r="J211" s="4"/>
@@ -8364,13 +8418,17 @@
       <c r="Y211" s="4"/>
     </row>
     <row r="212" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="4"/>
+      <c r="A212" s="6">
+        <v>45818</v>
+      </c>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
       <c r="D212" s="4"/>
       <c r="E212" s="4"/>
       <c r="F212" s="4"/>
-      <c r="G212" s="4"/>
+      <c r="G212" s="4">
+        <v>2.75</v>
+      </c>
       <c r="H212" s="4"/>
       <c r="I212" s="4"/>
       <c r="J212" s="4"/>
@@ -8391,13 +8449,17 @@
       <c r="Y212" s="4"/>
     </row>
     <row r="213" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="4"/>
+      <c r="A213" s="6">
+        <v>45817</v>
+      </c>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
       <c r="D213" s="4"/>
       <c r="E213" s="4"/>
       <c r="F213" s="4"/>
-      <c r="G213" s="4"/>
+      <c r="G213" s="4">
+        <v>1.89</v>
+      </c>
       <c r="H213" s="4"/>
       <c r="I213" s="4"/>
       <c r="J213" s="4"/>
@@ -8418,13 +8480,17 @@
       <c r="Y213" s="4"/>
     </row>
     <row r="214" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="4"/>
+      <c r="A214" s="6">
+        <v>45814</v>
+      </c>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
       <c r="D214" s="4"/>
       <c r="E214" s="4"/>
       <c r="F214" s="4"/>
-      <c r="G214" s="4"/>
+      <c r="G214" s="4">
+        <v>4.47</v>
+      </c>
       <c r="H214" s="4"/>
       <c r="I214" s="4"/>
       <c r="J214" s="4"/>
@@ -8445,13 +8511,17 @@
       <c r="Y214" s="4"/>
     </row>
     <row r="215" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="4"/>
+      <c r="A215" s="6">
+        <v>45813</v>
+      </c>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
       <c r="D215" s="4"/>
       <c r="E215" s="4"/>
       <c r="F215" s="4"/>
-      <c r="G215" s="4"/>
+      <c r="G215" s="4">
+        <v>8.7100000000000009</v>
+      </c>
       <c r="H215" s="4"/>
       <c r="I215" s="4"/>
       <c r="J215" s="4"/>
@@ -8472,13 +8542,17 @@
       <c r="Y215" s="4"/>
     </row>
     <row r="216" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="4"/>
+      <c r="A216" s="6">
+        <v>45812</v>
+      </c>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
       <c r="D216" s="4"/>
       <c r="E216" s="4"/>
       <c r="F216" s="4"/>
-      <c r="G216" s="4"/>
+      <c r="G216" s="4">
+        <v>2.27</v>
+      </c>
       <c r="H216" s="4"/>
       <c r="I216" s="4"/>
       <c r="J216" s="4"/>
@@ -8499,13 +8573,17 @@
       <c r="Y216" s="4"/>
     </row>
     <row r="217" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="4"/>
+      <c r="A217" s="6">
+        <v>45811</v>
+      </c>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
       <c r="D217" s="4"/>
       <c r="E217" s="4"/>
       <c r="F217" s="4"/>
-      <c r="G217" s="4"/>
+      <c r="G217" s="4">
+        <v>5.05</v>
+      </c>
       <c r="H217" s="4"/>
       <c r="I217" s="4"/>
       <c r="J217" s="4"/>
@@ -8526,13 +8604,17 @@
       <c r="Y217" s="4"/>
     </row>
     <row r="218" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="4"/>
+      <c r="A218" s="6">
+        <v>45810</v>
+      </c>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
       <c r="D218" s="4"/>
       <c r="E218" s="4"/>
       <c r="F218" s="4"/>
-      <c r="G218" s="4"/>
+      <c r="G218" s="4">
+        <v>-1.1599999999999999</v>
+      </c>
       <c r="H218" s="4"/>
       <c r="I218" s="4"/>
       <c r="J218" s="4"/>
@@ -8553,13 +8635,17 @@
       <c r="Y218" s="4"/>
     </row>
     <row r="219" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="4"/>
+      <c r="A219" s="6">
+        <v>45807</v>
+      </c>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
       <c r="F219" s="4"/>
-      <c r="G219" s="4"/>
+      <c r="G219" s="4">
+        <v>-2.5</v>
+      </c>
       <c r="H219" s="4"/>
       <c r="I219" s="4"/>
       <c r="J219" s="4"/>
@@ -8580,13 +8666,17 @@
       <c r="Y219" s="4"/>
     </row>
     <row r="220" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="4"/>
+      <c r="A220" s="6">
+        <v>45806</v>
+      </c>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
       <c r="D220" s="4"/>
       <c r="E220" s="4"/>
       <c r="F220" s="4"/>
-      <c r="G220" s="4"/>
+      <c r="G220" s="4">
+        <v>-1.68</v>
+      </c>
       <c r="H220" s="4"/>
       <c r="I220" s="4"/>
       <c r="J220" s="4"/>
@@ -8607,13 +8697,17 @@
       <c r="Y220" s="4"/>
     </row>
     <row r="221" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A221" s="4"/>
+      <c r="A221" s="6">
+        <v>45805</v>
+      </c>
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
       <c r="D221" s="4"/>
       <c r="E221" s="4"/>
       <c r="F221" s="4"/>
-      <c r="G221" s="4"/>
+      <c r="G221" s="4">
+        <v>4.78</v>
+      </c>
       <c r="H221" s="4"/>
       <c r="I221" s="4"/>
       <c r="J221" s="4"/>
@@ -8634,13 +8728,17 @@
       <c r="Y221" s="4"/>
     </row>
     <row r="222" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="4"/>
+      <c r="A222" s="6">
+        <v>45804</v>
+      </c>
       <c r="B222" s="4"/>
       <c r="C222" s="4"/>
       <c r="D222" s="4"/>
       <c r="E222" s="4"/>
       <c r="F222" s="4"/>
-      <c r="G222" s="4"/>
+      <c r="G222" s="4">
+        <v>4.55</v>
+      </c>
       <c r="H222" s="4"/>
       <c r="I222" s="4"/>
       <c r="J222" s="4"/>
@@ -8661,13 +8759,17 @@
       <c r="Y222" s="4"/>
     </row>
     <row r="223" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="4"/>
+      <c r="A223" s="6">
+        <v>45803</v>
+      </c>
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
       <c r="D223" s="4"/>
       <c r="E223" s="4"/>
       <c r="F223" s="4"/>
-      <c r="G223" s="4"/>
+      <c r="G223" s="4">
+        <v>1.62</v>
+      </c>
       <c r="H223" s="4"/>
       <c r="I223" s="4"/>
       <c r="J223" s="4"/>
@@ -8688,13 +8790,17 @@
       <c r="Y223" s="4"/>
     </row>
     <row r="224" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="4"/>
+      <c r="A224" s="6">
+        <v>45800</v>
+      </c>
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
       <c r="D224" s="4"/>
       <c r="E224" s="4"/>
       <c r="F224" s="4"/>
-      <c r="G224" s="4"/>
+      <c r="G224" s="4">
+        <v>4.22</v>
+      </c>
       <c r="H224" s="4"/>
       <c r="I224" s="4"/>
       <c r="J224" s="4"/>
@@ -8715,13 +8821,17 @@
       <c r="Y224" s="4"/>
     </row>
     <row r="225" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="4"/>
+      <c r="A225" s="6">
+        <v>45799</v>
+      </c>
       <c r="B225" s="4"/>
       <c r="C225" s="4"/>
       <c r="D225" s="4"/>
       <c r="E225" s="4"/>
       <c r="F225" s="4"/>
-      <c r="G225" s="4"/>
+      <c r="G225" s="4">
+        <v>1.97</v>
+      </c>
       <c r="H225" s="4"/>
       <c r="I225" s="4"/>
       <c r="J225" s="4"/>
@@ -8742,13 +8852,17 @@
       <c r="Y225" s="4"/>
     </row>
     <row r="226" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="4"/>
+      <c r="A226" s="6">
+        <v>45798</v>
+      </c>
       <c r="B226" s="4"/>
       <c r="C226" s="4"/>
       <c r="D226" s="4"/>
       <c r="E226" s="4"/>
       <c r="F226" s="4"/>
-      <c r="G226" s="4"/>
+      <c r="G226" s="4">
+        <v>-8.26</v>
+      </c>
       <c r="H226" s="4"/>
       <c r="I226" s="4"/>
       <c r="J226" s="4"/>
@@ -8769,13 +8883,17 @@
       <c r="Y226" s="4"/>
     </row>
     <row r="227" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="4"/>
+      <c r="A227" s="6">
+        <v>45797</v>
+      </c>
       <c r="B227" s="4"/>
       <c r="C227" s="4"/>
       <c r="D227" s="4"/>
       <c r="E227" s="4"/>
       <c r="F227" s="4"/>
-      <c r="G227" s="4"/>
+      <c r="G227" s="4">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="H227" s="4"/>
       <c r="I227" s="4"/>
       <c r="J227" s="4"/>
@@ -8796,13 +8914,17 @@
       <c r="Y227" s="4"/>
     </row>
     <row r="228" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="4"/>
+      <c r="A228" s="6">
+        <v>45796</v>
+      </c>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
       <c r="D228" s="4"/>
       <c r="E228" s="4"/>
       <c r="F228" s="4"/>
-      <c r="G228" s="4"/>
+      <c r="G228" s="4">
+        <v>4.32</v>
+      </c>
       <c r="H228" s="4"/>
       <c r="I228" s="4"/>
       <c r="J228" s="4"/>
@@ -8823,13 +8945,17 @@
       <c r="Y228" s="4"/>
     </row>
     <row r="229" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="4"/>
+      <c r="A229" s="6">
+        <v>45793</v>
+      </c>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
       <c r="D229" s="4"/>
       <c r="E229" s="4"/>
       <c r="F229" s="4"/>
-      <c r="G229" s="4"/>
+      <c r="G229" s="4">
+        <v>1.48</v>
+      </c>
       <c r="H229" s="4"/>
       <c r="I229" s="4"/>
       <c r="J229" s="4"/>
@@ -8850,13 +8976,17 @@
       <c r="Y229" s="4"/>
     </row>
     <row r="230" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="4"/>
+      <c r="A230" s="6">
+        <v>45792</v>
+      </c>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
       <c r="F230" s="4"/>
-      <c r="G230" s="4"/>
+      <c r="G230" s="4">
+        <v>6.87</v>
+      </c>
       <c r="H230" s="4"/>
       <c r="I230" s="4"/>
       <c r="J230" s="4"/>
@@ -8877,13 +9007,17 @@
       <c r="Y230" s="4"/>
     </row>
     <row r="231" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="4"/>
+      <c r="A231" s="6">
+        <v>45791</v>
+      </c>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
       <c r="D231" s="4"/>
       <c r="E231" s="4"/>
       <c r="F231" s="4"/>
-      <c r="G231" s="4"/>
+      <c r="G231" s="4">
+        <v>1.1200000000000001</v>
+      </c>
       <c r="H231" s="4"/>
       <c r="I231" s="4"/>
       <c r="J231" s="4"/>
@@ -8904,13 +9038,17 @@
       <c r="Y231" s="4"/>
     </row>
     <row r="232" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="4"/>
+      <c r="A232" s="6">
+        <v>45790</v>
+      </c>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
       <c r="D232" s="4"/>
       <c r="E232" s="4"/>
       <c r="F232" s="4"/>
-      <c r="G232" s="4"/>
+      <c r="G232" s="4">
+        <v>2.5499999999999998</v>
+      </c>
       <c r="H232" s="4"/>
       <c r="I232" s="4"/>
       <c r="J232" s="4"/>
@@ -8931,13 +9069,17 @@
       <c r="Y232" s="4"/>
     </row>
     <row r="233" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="4"/>
+      <c r="A233" s="6">
+        <v>45789</v>
+      </c>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
       <c r="F233" s="4"/>
-      <c r="G233" s="4"/>
+      <c r="G233" s="4">
+        <v>0.61</v>
+      </c>
       <c r="H233" s="4"/>
       <c r="I233" s="4"/>
       <c r="J233" s="4"/>
@@ -8958,14 +9100,20 @@
       <c r="Y233" s="4"/>
     </row>
     <row r="234" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="4"/>
+      <c r="A234" s="6">
+        <v>45786</v>
+      </c>
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
       <c r="D234" s="4"/>
       <c r="E234" s="4"/>
       <c r="F234" s="4"/>
-      <c r="G234" s="4"/>
-      <c r="H234" s="4"/>
+      <c r="G234" s="4">
+        <v>3.28</v>
+      </c>
+      <c r="H234" s="4">
+        <v>4.6399999999999997</v>
+      </c>
       <c r="I234" s="4"/>
       <c r="J234" s="4"/>
       <c r="K234" s="4"/>
@@ -8985,13 +9133,17 @@
       <c r="Y234" s="4"/>
     </row>
     <row r="235" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="4"/>
+      <c r="A235" s="6">
+        <v>45785</v>
+      </c>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
       <c r="D235" s="4"/>
       <c r="E235" s="4"/>
       <c r="F235" s="4"/>
-      <c r="G235" s="4"/>
+      <c r="G235" s="4">
+        <v>2.63</v>
+      </c>
       <c r="H235" s="4"/>
       <c r="I235" s="4"/>
       <c r="J235" s="4"/>
@@ -9012,13 +9164,17 @@
       <c r="Y235" s="4"/>
     </row>
     <row r="236" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="4"/>
+      <c r="A236" s="6">
+        <v>45784</v>
+      </c>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
       <c r="D236" s="4"/>
       <c r="E236" s="4"/>
       <c r="F236" s="4"/>
-      <c r="G236" s="4"/>
+      <c r="G236" s="4">
+        <v>0.98</v>
+      </c>
       <c r="H236" s="4"/>
       <c r="I236" s="4"/>
       <c r="J236" s="4"/>
@@ -9039,13 +9195,17 @@
       <c r="Y236" s="4"/>
     </row>
     <row r="237" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A237" s="4"/>
+      <c r="A237" s="6">
+        <v>45783</v>
+      </c>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
       <c r="D237" s="4"/>
       <c r="E237" s="4"/>
       <c r="F237" s="4"/>
-      <c r="G237" s="4"/>
+      <c r="G237" s="4">
+        <v>4.41</v>
+      </c>
       <c r="H237" s="4"/>
       <c r="I237" s="4"/>
       <c r="J237" s="4"/>
@@ -9066,13 +9226,17 @@
       <c r="Y237" s="4"/>
     </row>
     <row r="238" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="4"/>
+      <c r="A238" s="6">
+        <v>45782</v>
+      </c>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
       <c r="D238" s="4"/>
       <c r="E238" s="4"/>
       <c r="F238" s="4"/>
-      <c r="G238" s="4"/>
+      <c r="G238" s="4">
+        <v>-2.72</v>
+      </c>
       <c r="H238" s="4"/>
       <c r="I238" s="4"/>
       <c r="J238" s="4"/>
@@ -9093,13 +9257,17 @@
       <c r="Y238" s="4"/>
     </row>
     <row r="239" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="4"/>
+      <c r="A239" s="6">
+        <v>45779</v>
+      </c>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
       <c r="D239" s="4"/>
       <c r="E239" s="4"/>
       <c r="F239" s="4"/>
-      <c r="G239" s="4"/>
+      <c r="G239" s="4">
+        <v>-4.29</v>
+      </c>
       <c r="H239" s="4"/>
       <c r="I239" s="4"/>
       <c r="J239" s="4"/>
@@ -9120,13 +9288,17 @@
       <c r="Y239" s="4"/>
     </row>
     <row r="240" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="4"/>
+      <c r="A240" s="6">
+        <v>45777</v>
+      </c>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
       <c r="D240" s="4"/>
       <c r="E240" s="4"/>
       <c r="F240" s="4"/>
-      <c r="G240" s="4"/>
+      <c r="G240" s="4">
+        <v>-1.38</v>
+      </c>
       <c r="H240" s="4"/>
       <c r="I240" s="4"/>
       <c r="J240" s="4"/>
@@ -9147,13 +9319,17 @@
       <c r="Y240" s="4"/>
     </row>
     <row r="241" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="4"/>
+      <c r="A241" s="6">
+        <v>45776</v>
+      </c>
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
       <c r="D241" s="4"/>
       <c r="E241" s="4"/>
       <c r="F241" s="4"/>
-      <c r="G241" s="4"/>
+      <c r="G241" s="4">
+        <v>0.69</v>
+      </c>
       <c r="H241" s="4"/>
       <c r="I241" s="4"/>
       <c r="J241" s="4"/>
@@ -9174,13 +9350,17 @@
       <c r="Y241" s="4"/>
     </row>
     <row r="242" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="4"/>
+      <c r="A242" s="6">
+        <v>45775</v>
+      </c>
       <c r="B242" s="4"/>
       <c r="C242" s="4"/>
       <c r="D242" s="4"/>
       <c r="E242" s="4"/>
       <c r="F242" s="4"/>
-      <c r="G242" s="4"/>
+      <c r="G242" s="4">
+        <v>7.09</v>
+      </c>
       <c r="H242" s="4"/>
       <c r="I242" s="4"/>
       <c r="J242" s="4"/>
@@ -9201,13 +9381,17 @@
       <c r="Y242" s="4"/>
     </row>
     <row r="243" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A243" s="4"/>
+      <c r="A243" s="6">
+        <v>45772</v>
+      </c>
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
       <c r="D243" s="4"/>
       <c r="E243" s="4"/>
       <c r="F243" s="4"/>
-      <c r="G243" s="4"/>
+      <c r="G243" s="4">
+        <v>0</v>
+      </c>
       <c r="H243" s="4"/>
       <c r="I243" s="4"/>
       <c r="J243" s="4"/>
@@ -9228,13 +9412,17 @@
       <c r="Y243" s="4"/>
     </row>
     <row r="244" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="4"/>
+      <c r="A244" s="6">
+        <v>45771</v>
+      </c>
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
       <c r="D244" s="4"/>
       <c r="E244" s="4"/>
       <c r="F244" s="4"/>
-      <c r="G244" s="4"/>
+      <c r="G244" s="4">
+        <v>0</v>
+      </c>
       <c r="H244" s="4"/>
       <c r="I244" s="4"/>
       <c r="J244" s="4"/>
@@ -9255,13 +9443,17 @@
       <c r="Y244" s="4"/>
     </row>
     <row r="245" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A245" s="4"/>
+      <c r="A245" s="6">
+        <v>45770</v>
+      </c>
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
       <c r="D245" s="4"/>
       <c r="E245" s="4"/>
       <c r="F245" s="4"/>
-      <c r="G245" s="4"/>
+      <c r="G245" s="4">
+        <v>-5.94</v>
+      </c>
       <c r="H245" s="4"/>
       <c r="I245" s="4"/>
       <c r="J245" s="4"/>
@@ -9282,13 +9474,17 @@
       <c r="Y245" s="4"/>
     </row>
     <row r="246" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="4"/>
+      <c r="A246" s="6">
+        <v>45769</v>
+      </c>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
       <c r="D246" s="4"/>
       <c r="E246" s="4"/>
       <c r="F246" s="4"/>
-      <c r="G246" s="4"/>
+      <c r="G246" s="4">
+        <v>-0.47</v>
+      </c>
       <c r="H246" s="4"/>
       <c r="I246" s="4"/>
       <c r="J246" s="4"/>
@@ -9309,13 +9505,17 @@
       <c r="Y246" s="4"/>
     </row>
     <row r="247" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A247" s="4"/>
+      <c r="A247" s="6">
+        <v>45768</v>
+      </c>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
       <c r="D247" s="4"/>
       <c r="E247" s="4"/>
       <c r="F247" s="4"/>
-      <c r="G247" s="4"/>
+      <c r="G247" s="4">
+        <v>4.03</v>
+      </c>
       <c r="H247" s="4"/>
       <c r="I247" s="4"/>
       <c r="J247" s="4"/>
@@ -9336,13 +9536,17 @@
       <c r="Y247" s="4"/>
     </row>
     <row r="248" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="4"/>
+      <c r="A248" s="6">
+        <v>45764</v>
+      </c>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
       <c r="D248" s="4"/>
       <c r="E248" s="4"/>
       <c r="F248" s="4"/>
-      <c r="G248" s="4"/>
+      <c r="G248" s="4">
+        <v>3.46</v>
+      </c>
       <c r="H248" s="4"/>
       <c r="I248" s="4"/>
       <c r="J248" s="4"/>
@@ -9363,13 +9567,17 @@
       <c r="Y248" s="4"/>
     </row>
     <row r="249" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="4"/>
+      <c r="A249" s="6">
+        <v>45763</v>
+      </c>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
       <c r="D249" s="4"/>
       <c r="E249" s="4"/>
       <c r="F249" s="4"/>
-      <c r="G249" s="4"/>
+      <c r="G249" s="4">
+        <v>-2.81</v>
+      </c>
       <c r="H249" s="4"/>
       <c r="I249" s="4"/>
       <c r="J249" s="4"/>
@@ -9390,13 +9598,17 @@
       <c r="Y249" s="4"/>
     </row>
     <row r="250" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="4"/>
+      <c r="A250" s="6">
+        <v>45762</v>
+      </c>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
       <c r="D250" s="4"/>
       <c r="E250" s="4"/>
       <c r="F250" s="4"/>
-      <c r="G250" s="4"/>
+      <c r="G250" s="4">
+        <v>7.81</v>
+      </c>
       <c r="H250" s="4"/>
       <c r="I250" s="4"/>
       <c r="J250" s="4"/>
@@ -9417,13 +9629,17 @@
       <c r="Y250" s="4"/>
     </row>
     <row r="251" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A251" s="4"/>
+      <c r="A251" s="6">
+        <v>45758</v>
+      </c>
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
       <c r="D251" s="4"/>
       <c r="E251" s="4"/>
       <c r="F251" s="4"/>
-      <c r="G251" s="4"/>
+      <c r="G251" s="4">
+        <v>-5.82</v>
+      </c>
       <c r="H251" s="4"/>
       <c r="I251" s="4"/>
       <c r="J251" s="4"/>
@@ -9444,13 +9660,17 @@
       <c r="Y251" s="4"/>
     </row>
     <row r="252" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A252" s="4"/>
+      <c r="A252" s="6">
+        <v>45756</v>
+      </c>
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
       <c r="D252" s="4"/>
       <c r="E252" s="4"/>
       <c r="F252" s="4"/>
-      <c r="G252" s="4"/>
+      <c r="G252" s="4">
+        <v>-0.56000000000000005</v>
+      </c>
       <c r="H252" s="4"/>
       <c r="I252" s="4"/>
       <c r="J252" s="4"/>
@@ -9471,13 +9691,17 @@
       <c r="Y252" s="4"/>
     </row>
     <row r="253" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A253" s="4"/>
+      <c r="A253" s="6">
+        <v>45755</v>
+      </c>
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
       <c r="D253" s="4"/>
       <c r="E253" s="4"/>
       <c r="F253" s="4"/>
-      <c r="G253" s="4"/>
+      <c r="G253" s="4">
+        <v>5.83</v>
+      </c>
       <c r="H253" s="4"/>
       <c r="I253" s="4"/>
       <c r="J253" s="4"/>
@@ -9498,13 +9722,17 @@
       <c r="Y253" s="4"/>
     </row>
     <row r="254" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A254" s="4"/>
+      <c r="A254" s="6">
+        <v>45754</v>
+      </c>
       <c r="B254" s="4"/>
       <c r="C254" s="4"/>
       <c r="D254" s="4"/>
       <c r="E254" s="4"/>
       <c r="F254" s="4"/>
-      <c r="G254" s="4"/>
+      <c r="G254" s="4">
+        <v>6.02</v>
+      </c>
       <c r="H254" s="4"/>
       <c r="I254" s="4"/>
       <c r="J254" s="4"/>
@@ -9525,13 +9753,17 @@
       <c r="Y254" s="4"/>
     </row>
     <row r="255" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A255" s="4"/>
+      <c r="A255" s="6">
+        <v>45751</v>
+      </c>
       <c r="B255" s="4"/>
       <c r="C255" s="4"/>
       <c r="D255" s="4"/>
       <c r="E255" s="4"/>
       <c r="F255" s="4"/>
-      <c r="G255" s="4"/>
+      <c r="G255" s="4">
+        <v>7.17</v>
+      </c>
       <c r="H255" s="4"/>
       <c r="I255" s="4"/>
       <c r="J255" s="4"/>
@@ -9552,13 +9784,17 @@
       <c r="Y255" s="4"/>
     </row>
     <row r="256" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="4"/>
+      <c r="A256" s="6">
+        <v>45750</v>
+      </c>
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
       <c r="D256" s="4"/>
       <c r="E256" s="4"/>
       <c r="F256" s="4"/>
-      <c r="G256" s="4"/>
+      <c r="G256" s="4">
+        <v>-3.37</v>
+      </c>
       <c r="H256" s="4"/>
       <c r="I256" s="4"/>
       <c r="J256" s="4"/>
@@ -9579,13 +9815,17 @@
       <c r="Y256" s="4"/>
     </row>
     <row r="257" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="4"/>
+      <c r="A257" s="6">
+        <v>45749</v>
+      </c>
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
       <c r="D257" s="4"/>
       <c r="E257" s="4"/>
       <c r="F257" s="4"/>
-      <c r="G257" s="4"/>
+      <c r="G257" s="4">
+        <v>1.8</v>
+      </c>
       <c r="H257" s="4"/>
       <c r="I257" s="4"/>
       <c r="J257" s="4"/>
@@ -9606,13 +9846,17 @@
       <c r="Y257" s="4"/>
     </row>
     <row r="258" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="4"/>
+      <c r="A258" s="6">
+        <v>45748</v>
+      </c>
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
       <c r="D258" s="4"/>
       <c r="E258" s="4"/>
       <c r="F258" s="4"/>
-      <c r="G258" s="4"/>
+      <c r="G258" s="4">
+        <v>0</v>
+      </c>
       <c r="H258" s="4"/>
       <c r="I258" s="4"/>
       <c r="J258" s="4"/>
@@ -28289,1437 +28533,6 @@
       <c r="X949" s="4"/>
       <c r="Y949" s="4"/>
     </row>
-    <row r="950" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A950" s="4"/>
-      <c r="B950" s="4"/>
-      <c r="C950" s="4"/>
-      <c r="D950" s="4"/>
-      <c r="E950" s="4"/>
-      <c r="F950" s="4"/>
-      <c r="G950" s="4"/>
-      <c r="H950" s="4"/>
-      <c r="I950" s="4"/>
-      <c r="J950" s="4"/>
-      <c r="K950" s="4"/>
-      <c r="L950" s="4"/>
-      <c r="M950" s="4"/>
-      <c r="N950" s="4"/>
-      <c r="O950" s="4"/>
-      <c r="P950" s="4"/>
-      <c r="Q950" s="4"/>
-      <c r="R950" s="4"/>
-      <c r="S950" s="4"/>
-      <c r="T950" s="4"/>
-      <c r="U950" s="4"/>
-      <c r="V950" s="4"/>
-      <c r="W950" s="4"/>
-      <c r="X950" s="4"/>
-      <c r="Y950" s="4"/>
-    </row>
-    <row r="951" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A951" s="4"/>
-      <c r="B951" s="4"/>
-      <c r="C951" s="4"/>
-      <c r="D951" s="4"/>
-      <c r="E951" s="4"/>
-      <c r="F951" s="4"/>
-      <c r="G951" s="4"/>
-      <c r="H951" s="4"/>
-      <c r="I951" s="4"/>
-      <c r="J951" s="4"/>
-      <c r="K951" s="4"/>
-      <c r="L951" s="4"/>
-      <c r="M951" s="4"/>
-      <c r="N951" s="4"/>
-      <c r="O951" s="4"/>
-      <c r="P951" s="4"/>
-      <c r="Q951" s="4"/>
-      <c r="R951" s="4"/>
-      <c r="S951" s="4"/>
-      <c r="T951" s="4"/>
-      <c r="U951" s="4"/>
-      <c r="V951" s="4"/>
-      <c r="W951" s="4"/>
-      <c r="X951" s="4"/>
-      <c r="Y951" s="4"/>
-    </row>
-    <row r="952" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A952" s="4"/>
-      <c r="B952" s="4"/>
-      <c r="C952" s="4"/>
-      <c r="D952" s="4"/>
-      <c r="E952" s="4"/>
-      <c r="F952" s="4"/>
-      <c r="G952" s="4"/>
-      <c r="H952" s="4"/>
-      <c r="I952" s="4"/>
-      <c r="J952" s="4"/>
-      <c r="K952" s="4"/>
-      <c r="L952" s="4"/>
-      <c r="M952" s="4"/>
-      <c r="N952" s="4"/>
-      <c r="O952" s="4"/>
-      <c r="P952" s="4"/>
-      <c r="Q952" s="4"/>
-      <c r="R952" s="4"/>
-      <c r="S952" s="4"/>
-      <c r="T952" s="4"/>
-      <c r="U952" s="4"/>
-      <c r="V952" s="4"/>
-      <c r="W952" s="4"/>
-      <c r="X952" s="4"/>
-      <c r="Y952" s="4"/>
-    </row>
-    <row r="953" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A953" s="4"/>
-      <c r="B953" s="4"/>
-      <c r="C953" s="4"/>
-      <c r="D953" s="4"/>
-      <c r="E953" s="4"/>
-      <c r="F953" s="4"/>
-      <c r="G953" s="4"/>
-      <c r="H953" s="4"/>
-      <c r="I953" s="4"/>
-      <c r="J953" s="4"/>
-      <c r="K953" s="4"/>
-      <c r="L953" s="4"/>
-      <c r="M953" s="4"/>
-      <c r="N953" s="4"/>
-      <c r="O953" s="4"/>
-      <c r="P953" s="4"/>
-      <c r="Q953" s="4"/>
-      <c r="R953" s="4"/>
-      <c r="S953" s="4"/>
-      <c r="T953" s="4"/>
-      <c r="U953" s="4"/>
-      <c r="V953" s="4"/>
-      <c r="W953" s="4"/>
-      <c r="X953" s="4"/>
-      <c r="Y953" s="4"/>
-    </row>
-    <row r="954" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A954" s="4"/>
-      <c r="B954" s="4"/>
-      <c r="C954" s="4"/>
-      <c r="D954" s="4"/>
-      <c r="E954" s="4"/>
-      <c r="F954" s="4"/>
-      <c r="G954" s="4"/>
-      <c r="H954" s="4"/>
-      <c r="I954" s="4"/>
-      <c r="J954" s="4"/>
-      <c r="K954" s="4"/>
-      <c r="L954" s="4"/>
-      <c r="M954" s="4"/>
-      <c r="N954" s="4"/>
-      <c r="O954" s="4"/>
-      <c r="P954" s="4"/>
-      <c r="Q954" s="4"/>
-      <c r="R954" s="4"/>
-      <c r="S954" s="4"/>
-      <c r="T954" s="4"/>
-      <c r="U954" s="4"/>
-      <c r="V954" s="4"/>
-      <c r="W954" s="4"/>
-      <c r="X954" s="4"/>
-      <c r="Y954" s="4"/>
-    </row>
-    <row r="955" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A955" s="4"/>
-      <c r="B955" s="4"/>
-      <c r="C955" s="4"/>
-      <c r="D955" s="4"/>
-      <c r="E955" s="4"/>
-      <c r="F955" s="4"/>
-      <c r="G955" s="4"/>
-      <c r="H955" s="4"/>
-      <c r="I955" s="4"/>
-      <c r="J955" s="4"/>
-      <c r="K955" s="4"/>
-      <c r="L955" s="4"/>
-      <c r="M955" s="4"/>
-      <c r="N955" s="4"/>
-      <c r="O955" s="4"/>
-      <c r="P955" s="4"/>
-      <c r="Q955" s="4"/>
-      <c r="R955" s="4"/>
-      <c r="S955" s="4"/>
-      <c r="T955" s="4"/>
-      <c r="U955" s="4"/>
-      <c r="V955" s="4"/>
-      <c r="W955" s="4"/>
-      <c r="X955" s="4"/>
-      <c r="Y955" s="4"/>
-    </row>
-    <row r="956" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A956" s="4"/>
-      <c r="B956" s="4"/>
-      <c r="C956" s="4"/>
-      <c r="D956" s="4"/>
-      <c r="E956" s="4"/>
-      <c r="F956" s="4"/>
-      <c r="G956" s="4"/>
-      <c r="H956" s="4"/>
-      <c r="I956" s="4"/>
-      <c r="J956" s="4"/>
-      <c r="K956" s="4"/>
-      <c r="L956" s="4"/>
-      <c r="M956" s="4"/>
-      <c r="N956" s="4"/>
-      <c r="O956" s="4"/>
-      <c r="P956" s="4"/>
-      <c r="Q956" s="4"/>
-      <c r="R956" s="4"/>
-      <c r="S956" s="4"/>
-      <c r="T956" s="4"/>
-      <c r="U956" s="4"/>
-      <c r="V956" s="4"/>
-      <c r="W956" s="4"/>
-      <c r="X956" s="4"/>
-      <c r="Y956" s="4"/>
-    </row>
-    <row r="957" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A957" s="4"/>
-      <c r="B957" s="4"/>
-      <c r="C957" s="4"/>
-      <c r="D957" s="4"/>
-      <c r="E957" s="4"/>
-      <c r="F957" s="4"/>
-      <c r="G957" s="4"/>
-      <c r="H957" s="4"/>
-      <c r="I957" s="4"/>
-      <c r="J957" s="4"/>
-      <c r="K957" s="4"/>
-      <c r="L957" s="4"/>
-      <c r="M957" s="4"/>
-      <c r="N957" s="4"/>
-      <c r="O957" s="4"/>
-      <c r="P957" s="4"/>
-      <c r="Q957" s="4"/>
-      <c r="R957" s="4"/>
-      <c r="S957" s="4"/>
-      <c r="T957" s="4"/>
-      <c r="U957" s="4"/>
-      <c r="V957" s="4"/>
-      <c r="W957" s="4"/>
-      <c r="X957" s="4"/>
-      <c r="Y957" s="4"/>
-    </row>
-    <row r="958" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A958" s="4"/>
-      <c r="B958" s="4"/>
-      <c r="C958" s="4"/>
-      <c r="D958" s="4"/>
-      <c r="E958" s="4"/>
-      <c r="F958" s="4"/>
-      <c r="G958" s="4"/>
-      <c r="H958" s="4"/>
-      <c r="I958" s="4"/>
-      <c r="J958" s="4"/>
-      <c r="K958" s="4"/>
-      <c r="L958" s="4"/>
-      <c r="M958" s="4"/>
-      <c r="N958" s="4"/>
-      <c r="O958" s="4"/>
-      <c r="P958" s="4"/>
-      <c r="Q958" s="4"/>
-      <c r="R958" s="4"/>
-      <c r="S958" s="4"/>
-      <c r="T958" s="4"/>
-      <c r="U958" s="4"/>
-      <c r="V958" s="4"/>
-      <c r="W958" s="4"/>
-      <c r="X958" s="4"/>
-      <c r="Y958" s="4"/>
-    </row>
-    <row r="959" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A959" s="4"/>
-      <c r="B959" s="4"/>
-      <c r="C959" s="4"/>
-      <c r="D959" s="4"/>
-      <c r="E959" s="4"/>
-      <c r="F959" s="4"/>
-      <c r="G959" s="4"/>
-      <c r="H959" s="4"/>
-      <c r="I959" s="4"/>
-      <c r="J959" s="4"/>
-      <c r="K959" s="4"/>
-      <c r="L959" s="4"/>
-      <c r="M959" s="4"/>
-      <c r="N959" s="4"/>
-      <c r="O959" s="4"/>
-      <c r="P959" s="4"/>
-      <c r="Q959" s="4"/>
-      <c r="R959" s="4"/>
-      <c r="S959" s="4"/>
-      <c r="T959" s="4"/>
-      <c r="U959" s="4"/>
-      <c r="V959" s="4"/>
-      <c r="W959" s="4"/>
-      <c r="X959" s="4"/>
-      <c r="Y959" s="4"/>
-    </row>
-    <row r="960" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A960" s="4"/>
-      <c r="B960" s="4"/>
-      <c r="C960" s="4"/>
-      <c r="D960" s="4"/>
-      <c r="E960" s="4"/>
-      <c r="F960" s="4"/>
-      <c r="G960" s="4"/>
-      <c r="H960" s="4"/>
-      <c r="I960" s="4"/>
-      <c r="J960" s="4"/>
-      <c r="K960" s="4"/>
-      <c r="L960" s="4"/>
-      <c r="M960" s="4"/>
-      <c r="N960" s="4"/>
-      <c r="O960" s="4"/>
-      <c r="P960" s="4"/>
-      <c r="Q960" s="4"/>
-      <c r="R960" s="4"/>
-      <c r="S960" s="4"/>
-      <c r="T960" s="4"/>
-      <c r="U960" s="4"/>
-      <c r="V960" s="4"/>
-      <c r="W960" s="4"/>
-      <c r="X960" s="4"/>
-      <c r="Y960" s="4"/>
-    </row>
-    <row r="961" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A961" s="4"/>
-      <c r="B961" s="4"/>
-      <c r="C961" s="4"/>
-      <c r="D961" s="4"/>
-      <c r="E961" s="4"/>
-      <c r="F961" s="4"/>
-      <c r="G961" s="4"/>
-      <c r="H961" s="4"/>
-      <c r="I961" s="4"/>
-      <c r="J961" s="4"/>
-      <c r="K961" s="4"/>
-      <c r="L961" s="4"/>
-      <c r="M961" s="4"/>
-      <c r="N961" s="4"/>
-      <c r="O961" s="4"/>
-      <c r="P961" s="4"/>
-      <c r="Q961" s="4"/>
-      <c r="R961" s="4"/>
-      <c r="S961" s="4"/>
-      <c r="T961" s="4"/>
-      <c r="U961" s="4"/>
-      <c r="V961" s="4"/>
-      <c r="W961" s="4"/>
-      <c r="X961" s="4"/>
-      <c r="Y961" s="4"/>
-    </row>
-    <row r="962" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A962" s="4"/>
-      <c r="B962" s="4"/>
-      <c r="C962" s="4"/>
-      <c r="D962" s="4"/>
-      <c r="E962" s="4"/>
-      <c r="F962" s="4"/>
-      <c r="G962" s="4"/>
-      <c r="H962" s="4"/>
-      <c r="I962" s="4"/>
-      <c r="J962" s="4"/>
-      <c r="K962" s="4"/>
-      <c r="L962" s="4"/>
-      <c r="M962" s="4"/>
-      <c r="N962" s="4"/>
-      <c r="O962" s="4"/>
-      <c r="P962" s="4"/>
-      <c r="Q962" s="4"/>
-      <c r="R962" s="4"/>
-      <c r="S962" s="4"/>
-      <c r="T962" s="4"/>
-      <c r="U962" s="4"/>
-      <c r="V962" s="4"/>
-      <c r="W962" s="4"/>
-      <c r="X962" s="4"/>
-      <c r="Y962" s="4"/>
-    </row>
-    <row r="963" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A963" s="4"/>
-      <c r="B963" s="4"/>
-      <c r="C963" s="4"/>
-      <c r="D963" s="4"/>
-      <c r="E963" s="4"/>
-      <c r="F963" s="4"/>
-      <c r="G963" s="4"/>
-      <c r="H963" s="4"/>
-      <c r="I963" s="4"/>
-      <c r="J963" s="4"/>
-      <c r="K963" s="4"/>
-      <c r="L963" s="4"/>
-      <c r="M963" s="4"/>
-      <c r="N963" s="4"/>
-      <c r="O963" s="4"/>
-      <c r="P963" s="4"/>
-      <c r="Q963" s="4"/>
-      <c r="R963" s="4"/>
-      <c r="S963" s="4"/>
-      <c r="T963" s="4"/>
-      <c r="U963" s="4"/>
-      <c r="V963" s="4"/>
-      <c r="W963" s="4"/>
-      <c r="X963" s="4"/>
-      <c r="Y963" s="4"/>
-    </row>
-    <row r="964" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A964" s="4"/>
-      <c r="B964" s="4"/>
-      <c r="C964" s="4"/>
-      <c r="D964" s="4"/>
-      <c r="E964" s="4"/>
-      <c r="F964" s="4"/>
-      <c r="G964" s="4"/>
-      <c r="H964" s="4"/>
-      <c r="I964" s="4"/>
-      <c r="J964" s="4"/>
-      <c r="K964" s="4"/>
-      <c r="L964" s="4"/>
-      <c r="M964" s="4"/>
-      <c r="N964" s="4"/>
-      <c r="O964" s="4"/>
-      <c r="P964" s="4"/>
-      <c r="Q964" s="4"/>
-      <c r="R964" s="4"/>
-      <c r="S964" s="4"/>
-      <c r="T964" s="4"/>
-      <c r="U964" s="4"/>
-      <c r="V964" s="4"/>
-      <c r="W964" s="4"/>
-      <c r="X964" s="4"/>
-      <c r="Y964" s="4"/>
-    </row>
-    <row r="965" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A965" s="4"/>
-      <c r="B965" s="4"/>
-      <c r="C965" s="4"/>
-      <c r="D965" s="4"/>
-      <c r="E965" s="4"/>
-      <c r="F965" s="4"/>
-      <c r="G965" s="4"/>
-      <c r="H965" s="4"/>
-      <c r="I965" s="4"/>
-      <c r="J965" s="4"/>
-      <c r="K965" s="4"/>
-      <c r="L965" s="4"/>
-      <c r="M965" s="4"/>
-      <c r="N965" s="4"/>
-      <c r="O965" s="4"/>
-      <c r="P965" s="4"/>
-      <c r="Q965" s="4"/>
-      <c r="R965" s="4"/>
-      <c r="S965" s="4"/>
-      <c r="T965" s="4"/>
-      <c r="U965" s="4"/>
-      <c r="V965" s="4"/>
-      <c r="W965" s="4"/>
-      <c r="X965" s="4"/>
-      <c r="Y965" s="4"/>
-    </row>
-    <row r="966" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A966" s="4"/>
-      <c r="B966" s="4"/>
-      <c r="C966" s="4"/>
-      <c r="D966" s="4"/>
-      <c r="E966" s="4"/>
-      <c r="F966" s="4"/>
-      <c r="G966" s="4"/>
-      <c r="H966" s="4"/>
-      <c r="I966" s="4"/>
-      <c r="J966" s="4"/>
-      <c r="K966" s="4"/>
-      <c r="L966" s="4"/>
-      <c r="M966" s="4"/>
-      <c r="N966" s="4"/>
-      <c r="O966" s="4"/>
-      <c r="P966" s="4"/>
-      <c r="Q966" s="4"/>
-      <c r="R966" s="4"/>
-      <c r="S966" s="4"/>
-      <c r="T966" s="4"/>
-      <c r="U966" s="4"/>
-      <c r="V966" s="4"/>
-      <c r="W966" s="4"/>
-      <c r="X966" s="4"/>
-      <c r="Y966" s="4"/>
-    </row>
-    <row r="967" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A967" s="4"/>
-      <c r="B967" s="4"/>
-      <c r="C967" s="4"/>
-      <c r="D967" s="4"/>
-      <c r="E967" s="4"/>
-      <c r="F967" s="4"/>
-      <c r="G967" s="4"/>
-      <c r="H967" s="4"/>
-      <c r="I967" s="4"/>
-      <c r="J967" s="4"/>
-      <c r="K967" s="4"/>
-      <c r="L967" s="4"/>
-      <c r="M967" s="4"/>
-      <c r="N967" s="4"/>
-      <c r="O967" s="4"/>
-      <c r="P967" s="4"/>
-      <c r="Q967" s="4"/>
-      <c r="R967" s="4"/>
-      <c r="S967" s="4"/>
-      <c r="T967" s="4"/>
-      <c r="U967" s="4"/>
-      <c r="V967" s="4"/>
-      <c r="W967" s="4"/>
-      <c r="X967" s="4"/>
-      <c r="Y967" s="4"/>
-    </row>
-    <row r="968" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A968" s="4"/>
-      <c r="B968" s="4"/>
-      <c r="C968" s="4"/>
-      <c r="D968" s="4"/>
-      <c r="E968" s="4"/>
-      <c r="F968" s="4"/>
-      <c r="G968" s="4"/>
-      <c r="H968" s="4"/>
-      <c r="I968" s="4"/>
-      <c r="J968" s="4"/>
-      <c r="K968" s="4"/>
-      <c r="L968" s="4"/>
-      <c r="M968" s="4"/>
-      <c r="N968" s="4"/>
-      <c r="O968" s="4"/>
-      <c r="P968" s="4"/>
-      <c r="Q968" s="4"/>
-      <c r="R968" s="4"/>
-      <c r="S968" s="4"/>
-      <c r="T968" s="4"/>
-      <c r="U968" s="4"/>
-      <c r="V968" s="4"/>
-      <c r="W968" s="4"/>
-      <c r="X968" s="4"/>
-      <c r="Y968" s="4"/>
-    </row>
-    <row r="969" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A969" s="4"/>
-      <c r="B969" s="4"/>
-      <c r="C969" s="4"/>
-      <c r="D969" s="4"/>
-      <c r="E969" s="4"/>
-      <c r="F969" s="4"/>
-      <c r="G969" s="4"/>
-      <c r="H969" s="4"/>
-      <c r="I969" s="4"/>
-      <c r="J969" s="4"/>
-      <c r="K969" s="4"/>
-      <c r="L969" s="4"/>
-      <c r="M969" s="4"/>
-      <c r="N969" s="4"/>
-      <c r="O969" s="4"/>
-      <c r="P969" s="4"/>
-      <c r="Q969" s="4"/>
-      <c r="R969" s="4"/>
-      <c r="S969" s="4"/>
-      <c r="T969" s="4"/>
-      <c r="U969" s="4"/>
-      <c r="V969" s="4"/>
-      <c r="W969" s="4"/>
-      <c r="X969" s="4"/>
-      <c r="Y969" s="4"/>
-    </row>
-    <row r="970" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A970" s="4"/>
-      <c r="B970" s="4"/>
-      <c r="C970" s="4"/>
-      <c r="D970" s="4"/>
-      <c r="E970" s="4"/>
-      <c r="F970" s="4"/>
-      <c r="G970" s="4"/>
-      <c r="H970" s="4"/>
-      <c r="I970" s="4"/>
-      <c r="J970" s="4"/>
-      <c r="K970" s="4"/>
-      <c r="L970" s="4"/>
-      <c r="M970" s="4"/>
-      <c r="N970" s="4"/>
-      <c r="O970" s="4"/>
-      <c r="P970" s="4"/>
-      <c r="Q970" s="4"/>
-      <c r="R970" s="4"/>
-      <c r="S970" s="4"/>
-      <c r="T970" s="4"/>
-      <c r="U970" s="4"/>
-      <c r="V970" s="4"/>
-      <c r="W970" s="4"/>
-      <c r="X970" s="4"/>
-      <c r="Y970" s="4"/>
-    </row>
-    <row r="971" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A971" s="4"/>
-      <c r="B971" s="4"/>
-      <c r="C971" s="4"/>
-      <c r="D971" s="4"/>
-      <c r="E971" s="4"/>
-      <c r="F971" s="4"/>
-      <c r="G971" s="4"/>
-      <c r="H971" s="4"/>
-      <c r="I971" s="4"/>
-      <c r="J971" s="4"/>
-      <c r="K971" s="4"/>
-      <c r="L971" s="4"/>
-      <c r="M971" s="4"/>
-      <c r="N971" s="4"/>
-      <c r="O971" s="4"/>
-      <c r="P971" s="4"/>
-      <c r="Q971" s="4"/>
-      <c r="R971" s="4"/>
-      <c r="S971" s="4"/>
-      <c r="T971" s="4"/>
-      <c r="U971" s="4"/>
-      <c r="V971" s="4"/>
-      <c r="W971" s="4"/>
-      <c r="X971" s="4"/>
-      <c r="Y971" s="4"/>
-    </row>
-    <row r="972" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A972" s="4"/>
-      <c r="B972" s="4"/>
-      <c r="C972" s="4"/>
-      <c r="D972" s="4"/>
-      <c r="E972" s="4"/>
-      <c r="F972" s="4"/>
-      <c r="G972" s="4"/>
-      <c r="H972" s="4"/>
-      <c r="I972" s="4"/>
-      <c r="J972" s="4"/>
-      <c r="K972" s="4"/>
-      <c r="L972" s="4"/>
-      <c r="M972" s="4"/>
-      <c r="N972" s="4"/>
-      <c r="O972" s="4"/>
-      <c r="P972" s="4"/>
-      <c r="Q972" s="4"/>
-      <c r="R972" s="4"/>
-      <c r="S972" s="4"/>
-      <c r="T972" s="4"/>
-      <c r="U972" s="4"/>
-      <c r="V972" s="4"/>
-      <c r="W972" s="4"/>
-      <c r="X972" s="4"/>
-      <c r="Y972" s="4"/>
-    </row>
-    <row r="973" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A973" s="4"/>
-      <c r="B973" s="4"/>
-      <c r="C973" s="4"/>
-      <c r="D973" s="4"/>
-      <c r="E973" s="4"/>
-      <c r="F973" s="4"/>
-      <c r="G973" s="4"/>
-      <c r="H973" s="4"/>
-      <c r="I973" s="4"/>
-      <c r="J973" s="4"/>
-      <c r="K973" s="4"/>
-      <c r="L973" s="4"/>
-      <c r="M973" s="4"/>
-      <c r="N973" s="4"/>
-      <c r="O973" s="4"/>
-      <c r="P973" s="4"/>
-      <c r="Q973" s="4"/>
-      <c r="R973" s="4"/>
-      <c r="S973" s="4"/>
-      <c r="T973" s="4"/>
-      <c r="U973" s="4"/>
-      <c r="V973" s="4"/>
-      <c r="W973" s="4"/>
-      <c r="X973" s="4"/>
-      <c r="Y973" s="4"/>
-    </row>
-    <row r="974" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A974" s="4"/>
-      <c r="B974" s="4"/>
-      <c r="C974" s="4"/>
-      <c r="D974" s="4"/>
-      <c r="E974" s="4"/>
-      <c r="F974" s="4"/>
-      <c r="G974" s="4"/>
-      <c r="H974" s="4"/>
-      <c r="I974" s="4"/>
-      <c r="J974" s="4"/>
-      <c r="K974" s="4"/>
-      <c r="L974" s="4"/>
-      <c r="M974" s="4"/>
-      <c r="N974" s="4"/>
-      <c r="O974" s="4"/>
-      <c r="P974" s="4"/>
-      <c r="Q974" s="4"/>
-      <c r="R974" s="4"/>
-      <c r="S974" s="4"/>
-      <c r="T974" s="4"/>
-      <c r="U974" s="4"/>
-      <c r="V974" s="4"/>
-      <c r="W974" s="4"/>
-      <c r="X974" s="4"/>
-      <c r="Y974" s="4"/>
-    </row>
-    <row r="975" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A975" s="4"/>
-      <c r="B975" s="4"/>
-      <c r="C975" s="4"/>
-      <c r="D975" s="4"/>
-      <c r="E975" s="4"/>
-      <c r="F975" s="4"/>
-      <c r="G975" s="4"/>
-      <c r="H975" s="4"/>
-      <c r="I975" s="4"/>
-      <c r="J975" s="4"/>
-      <c r="K975" s="4"/>
-      <c r="L975" s="4"/>
-      <c r="M975" s="4"/>
-      <c r="N975" s="4"/>
-      <c r="O975" s="4"/>
-      <c r="P975" s="4"/>
-      <c r="Q975" s="4"/>
-      <c r="R975" s="4"/>
-      <c r="S975" s="4"/>
-      <c r="T975" s="4"/>
-      <c r="U975" s="4"/>
-      <c r="V975" s="4"/>
-      <c r="W975" s="4"/>
-      <c r="X975" s="4"/>
-      <c r="Y975" s="4"/>
-    </row>
-    <row r="976" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A976" s="4"/>
-      <c r="B976" s="4"/>
-      <c r="C976" s="4"/>
-      <c r="D976" s="4"/>
-      <c r="E976" s="4"/>
-      <c r="F976" s="4"/>
-      <c r="G976" s="4"/>
-      <c r="H976" s="4"/>
-      <c r="I976" s="4"/>
-      <c r="J976" s="4"/>
-      <c r="K976" s="4"/>
-      <c r="L976" s="4"/>
-      <c r="M976" s="4"/>
-      <c r="N976" s="4"/>
-      <c r="O976" s="4"/>
-      <c r="P976" s="4"/>
-      <c r="Q976" s="4"/>
-      <c r="R976" s="4"/>
-      <c r="S976" s="4"/>
-      <c r="T976" s="4"/>
-      <c r="U976" s="4"/>
-      <c r="V976" s="4"/>
-      <c r="W976" s="4"/>
-      <c r="X976" s="4"/>
-      <c r="Y976" s="4"/>
-    </row>
-    <row r="977" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A977" s="4"/>
-      <c r="B977" s="4"/>
-      <c r="C977" s="4"/>
-      <c r="D977" s="4"/>
-      <c r="E977" s="4"/>
-      <c r="F977" s="4"/>
-      <c r="G977" s="4"/>
-      <c r="H977" s="4"/>
-      <c r="I977" s="4"/>
-      <c r="J977" s="4"/>
-      <c r="K977" s="4"/>
-      <c r="L977" s="4"/>
-      <c r="M977" s="4"/>
-      <c r="N977" s="4"/>
-      <c r="O977" s="4"/>
-      <c r="P977" s="4"/>
-      <c r="Q977" s="4"/>
-      <c r="R977" s="4"/>
-      <c r="S977" s="4"/>
-      <c r="T977" s="4"/>
-      <c r="U977" s="4"/>
-      <c r="V977" s="4"/>
-      <c r="W977" s="4"/>
-      <c r="X977" s="4"/>
-      <c r="Y977" s="4"/>
-    </row>
-    <row r="978" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A978" s="4"/>
-      <c r="B978" s="4"/>
-      <c r="C978" s="4"/>
-      <c r="D978" s="4"/>
-      <c r="E978" s="4"/>
-      <c r="F978" s="4"/>
-      <c r="G978" s="4"/>
-      <c r="H978" s="4"/>
-      <c r="I978" s="4"/>
-      <c r="J978" s="4"/>
-      <c r="K978" s="4"/>
-      <c r="L978" s="4"/>
-      <c r="M978" s="4"/>
-      <c r="N978" s="4"/>
-      <c r="O978" s="4"/>
-      <c r="P978" s="4"/>
-      <c r="Q978" s="4"/>
-      <c r="R978" s="4"/>
-      <c r="S978" s="4"/>
-      <c r="T978" s="4"/>
-      <c r="U978" s="4"/>
-      <c r="V978" s="4"/>
-      <c r="W978" s="4"/>
-      <c r="X978" s="4"/>
-      <c r="Y978" s="4"/>
-    </row>
-    <row r="979" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A979" s="4"/>
-      <c r="B979" s="4"/>
-      <c r="C979" s="4"/>
-      <c r="D979" s="4"/>
-      <c r="E979" s="4"/>
-      <c r="F979" s="4"/>
-      <c r="G979" s="4"/>
-      <c r="H979" s="4"/>
-      <c r="I979" s="4"/>
-      <c r="J979" s="4"/>
-      <c r="K979" s="4"/>
-      <c r="L979" s="4"/>
-      <c r="M979" s="4"/>
-      <c r="N979" s="4"/>
-      <c r="O979" s="4"/>
-      <c r="P979" s="4"/>
-      <c r="Q979" s="4"/>
-      <c r="R979" s="4"/>
-      <c r="S979" s="4"/>
-      <c r="T979" s="4"/>
-      <c r="U979" s="4"/>
-      <c r="V979" s="4"/>
-      <c r="W979" s="4"/>
-      <c r="X979" s="4"/>
-      <c r="Y979" s="4"/>
-    </row>
-    <row r="980" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A980" s="4"/>
-      <c r="B980" s="4"/>
-      <c r="C980" s="4"/>
-      <c r="D980" s="4"/>
-      <c r="E980" s="4"/>
-      <c r="F980" s="4"/>
-      <c r="G980" s="4"/>
-      <c r="H980" s="4"/>
-      <c r="I980" s="4"/>
-      <c r="J980" s="4"/>
-      <c r="K980" s="4"/>
-      <c r="L980" s="4"/>
-      <c r="M980" s="4"/>
-      <c r="N980" s="4"/>
-      <c r="O980" s="4"/>
-      <c r="P980" s="4"/>
-      <c r="Q980" s="4"/>
-      <c r="R980" s="4"/>
-      <c r="S980" s="4"/>
-      <c r="T980" s="4"/>
-      <c r="U980" s="4"/>
-      <c r="V980" s="4"/>
-      <c r="W980" s="4"/>
-      <c r="X980" s="4"/>
-      <c r="Y980" s="4"/>
-    </row>
-    <row r="981" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A981" s="4"/>
-      <c r="B981" s="4"/>
-      <c r="C981" s="4"/>
-      <c r="D981" s="4"/>
-      <c r="E981" s="4"/>
-      <c r="F981" s="4"/>
-      <c r="G981" s="4"/>
-      <c r="H981" s="4"/>
-      <c r="I981" s="4"/>
-      <c r="J981" s="4"/>
-      <c r="K981" s="4"/>
-      <c r="L981" s="4"/>
-      <c r="M981" s="4"/>
-      <c r="N981" s="4"/>
-      <c r="O981" s="4"/>
-      <c r="P981" s="4"/>
-      <c r="Q981" s="4"/>
-      <c r="R981" s="4"/>
-      <c r="S981" s="4"/>
-      <c r="T981" s="4"/>
-      <c r="U981" s="4"/>
-      <c r="V981" s="4"/>
-      <c r="W981" s="4"/>
-      <c r="X981" s="4"/>
-      <c r="Y981" s="4"/>
-    </row>
-    <row r="982" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A982" s="4"/>
-      <c r="B982" s="4"/>
-      <c r="C982" s="4"/>
-      <c r="D982" s="4"/>
-      <c r="E982" s="4"/>
-      <c r="F982" s="4"/>
-      <c r="G982" s="4"/>
-      <c r="H982" s="4"/>
-      <c r="I982" s="4"/>
-      <c r="J982" s="4"/>
-      <c r="K982" s="4"/>
-      <c r="L982" s="4"/>
-      <c r="M982" s="4"/>
-      <c r="N982" s="4"/>
-      <c r="O982" s="4"/>
-      <c r="P982" s="4"/>
-      <c r="Q982" s="4"/>
-      <c r="R982" s="4"/>
-      <c r="S982" s="4"/>
-      <c r="T982" s="4"/>
-      <c r="U982" s="4"/>
-      <c r="V982" s="4"/>
-      <c r="W982" s="4"/>
-      <c r="X982" s="4"/>
-      <c r="Y982" s="4"/>
-    </row>
-    <row r="983" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A983" s="4"/>
-      <c r="B983" s="4"/>
-      <c r="C983" s="4"/>
-      <c r="D983" s="4"/>
-      <c r="E983" s="4"/>
-      <c r="F983" s="4"/>
-      <c r="G983" s="4"/>
-      <c r="H983" s="4"/>
-      <c r="I983" s="4"/>
-      <c r="J983" s="4"/>
-      <c r="K983" s="4"/>
-      <c r="L983" s="4"/>
-      <c r="M983" s="4"/>
-      <c r="N983" s="4"/>
-      <c r="O983" s="4"/>
-      <c r="P983" s="4"/>
-      <c r="Q983" s="4"/>
-      <c r="R983" s="4"/>
-      <c r="S983" s="4"/>
-      <c r="T983" s="4"/>
-      <c r="U983" s="4"/>
-      <c r="V983" s="4"/>
-      <c r="W983" s="4"/>
-      <c r="X983" s="4"/>
-      <c r="Y983" s="4"/>
-    </row>
-    <row r="984" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A984" s="4"/>
-      <c r="B984" s="4"/>
-      <c r="C984" s="4"/>
-      <c r="D984" s="4"/>
-      <c r="E984" s="4"/>
-      <c r="F984" s="4"/>
-      <c r="G984" s="4"/>
-      <c r="H984" s="4"/>
-      <c r="I984" s="4"/>
-      <c r="J984" s="4"/>
-      <c r="K984" s="4"/>
-      <c r="L984" s="4"/>
-      <c r="M984" s="4"/>
-      <c r="N984" s="4"/>
-      <c r="O984" s="4"/>
-      <c r="P984" s="4"/>
-      <c r="Q984" s="4"/>
-      <c r="R984" s="4"/>
-      <c r="S984" s="4"/>
-      <c r="T984" s="4"/>
-      <c r="U984" s="4"/>
-      <c r="V984" s="4"/>
-      <c r="W984" s="4"/>
-      <c r="X984" s="4"/>
-      <c r="Y984" s="4"/>
-    </row>
-    <row r="985" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A985" s="4"/>
-      <c r="B985" s="4"/>
-      <c r="C985" s="4"/>
-      <c r="D985" s="4"/>
-      <c r="E985" s="4"/>
-      <c r="F985" s="4"/>
-      <c r="G985" s="4"/>
-      <c r="H985" s="4"/>
-      <c r="I985" s="4"/>
-      <c r="J985" s="4"/>
-      <c r="K985" s="4"/>
-      <c r="L985" s="4"/>
-      <c r="M985" s="4"/>
-      <c r="N985" s="4"/>
-      <c r="O985" s="4"/>
-      <c r="P985" s="4"/>
-      <c r="Q985" s="4"/>
-      <c r="R985" s="4"/>
-      <c r="S985" s="4"/>
-      <c r="T985" s="4"/>
-      <c r="U985" s="4"/>
-      <c r="V985" s="4"/>
-      <c r="W985" s="4"/>
-      <c r="X985" s="4"/>
-      <c r="Y985" s="4"/>
-    </row>
-    <row r="986" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A986" s="4"/>
-      <c r="B986" s="4"/>
-      <c r="C986" s="4"/>
-      <c r="D986" s="4"/>
-      <c r="E986" s="4"/>
-      <c r="F986" s="4"/>
-      <c r="G986" s="4"/>
-      <c r="H986" s="4"/>
-      <c r="I986" s="4"/>
-      <c r="J986" s="4"/>
-      <c r="K986" s="4"/>
-      <c r="L986" s="4"/>
-      <c r="M986" s="4"/>
-      <c r="N986" s="4"/>
-      <c r="O986" s="4"/>
-      <c r="P986" s="4"/>
-      <c r="Q986" s="4"/>
-      <c r="R986" s="4"/>
-      <c r="S986" s="4"/>
-      <c r="T986" s="4"/>
-      <c r="U986" s="4"/>
-      <c r="V986" s="4"/>
-      <c r="W986" s="4"/>
-      <c r="X986" s="4"/>
-      <c r="Y986" s="4"/>
-    </row>
-    <row r="987" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A987" s="4"/>
-      <c r="B987" s="4"/>
-      <c r="C987" s="4"/>
-      <c r="D987" s="4"/>
-      <c r="E987" s="4"/>
-      <c r="F987" s="4"/>
-      <c r="G987" s="4"/>
-      <c r="H987" s="4"/>
-      <c r="I987" s="4"/>
-      <c r="J987" s="4"/>
-      <c r="K987" s="4"/>
-      <c r="L987" s="4"/>
-      <c r="M987" s="4"/>
-      <c r="N987" s="4"/>
-      <c r="O987" s="4"/>
-      <c r="P987" s="4"/>
-      <c r="Q987" s="4"/>
-      <c r="R987" s="4"/>
-      <c r="S987" s="4"/>
-      <c r="T987" s="4"/>
-      <c r="U987" s="4"/>
-      <c r="V987" s="4"/>
-      <c r="W987" s="4"/>
-      <c r="X987" s="4"/>
-      <c r="Y987" s="4"/>
-    </row>
-    <row r="988" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A988" s="4"/>
-      <c r="B988" s="4"/>
-      <c r="C988" s="4"/>
-      <c r="D988" s="4"/>
-      <c r="E988" s="4"/>
-      <c r="F988" s="4"/>
-      <c r="G988" s="4"/>
-      <c r="H988" s="4"/>
-      <c r="I988" s="4"/>
-      <c r="J988" s="4"/>
-      <c r="K988" s="4"/>
-      <c r="L988" s="4"/>
-      <c r="M988" s="4"/>
-      <c r="N988" s="4"/>
-      <c r="O988" s="4"/>
-      <c r="P988" s="4"/>
-      <c r="Q988" s="4"/>
-      <c r="R988" s="4"/>
-      <c r="S988" s="4"/>
-      <c r="T988" s="4"/>
-      <c r="U988" s="4"/>
-      <c r="V988" s="4"/>
-      <c r="W988" s="4"/>
-      <c r="X988" s="4"/>
-      <c r="Y988" s="4"/>
-    </row>
-    <row r="989" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A989" s="4"/>
-      <c r="B989" s="4"/>
-      <c r="C989" s="4"/>
-      <c r="D989" s="4"/>
-      <c r="E989" s="4"/>
-      <c r="F989" s="4"/>
-      <c r="G989" s="4"/>
-      <c r="H989" s="4"/>
-      <c r="I989" s="4"/>
-      <c r="J989" s="4"/>
-      <c r="K989" s="4"/>
-      <c r="L989" s="4"/>
-      <c r="M989" s="4"/>
-      <c r="N989" s="4"/>
-      <c r="O989" s="4"/>
-      <c r="P989" s="4"/>
-      <c r="Q989" s="4"/>
-      <c r="R989" s="4"/>
-      <c r="S989" s="4"/>
-      <c r="T989" s="4"/>
-      <c r="U989" s="4"/>
-      <c r="V989" s="4"/>
-      <c r="W989" s="4"/>
-      <c r="X989" s="4"/>
-      <c r="Y989" s="4"/>
-    </row>
-    <row r="990" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A990" s="4"/>
-      <c r="B990" s="4"/>
-      <c r="C990" s="4"/>
-      <c r="D990" s="4"/>
-      <c r="E990" s="4"/>
-      <c r="F990" s="4"/>
-      <c r="G990" s="4"/>
-      <c r="H990" s="4"/>
-      <c r="I990" s="4"/>
-      <c r="J990" s="4"/>
-      <c r="K990" s="4"/>
-      <c r="L990" s="4"/>
-      <c r="M990" s="4"/>
-      <c r="N990" s="4"/>
-      <c r="O990" s="4"/>
-      <c r="P990" s="4"/>
-      <c r="Q990" s="4"/>
-      <c r="R990" s="4"/>
-      <c r="S990" s="4"/>
-      <c r="T990" s="4"/>
-      <c r="U990" s="4"/>
-      <c r="V990" s="4"/>
-      <c r="W990" s="4"/>
-      <c r="X990" s="4"/>
-      <c r="Y990" s="4"/>
-    </row>
-    <row r="991" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A991" s="4"/>
-      <c r="B991" s="4"/>
-      <c r="C991" s="4"/>
-      <c r="D991" s="4"/>
-      <c r="E991" s="4"/>
-      <c r="F991" s="4"/>
-      <c r="G991" s="4"/>
-      <c r="H991" s="4"/>
-      <c r="I991" s="4"/>
-      <c r="J991" s="4"/>
-      <c r="K991" s="4"/>
-      <c r="L991" s="4"/>
-      <c r="M991" s="4"/>
-      <c r="N991" s="4"/>
-      <c r="O991" s="4"/>
-      <c r="P991" s="4"/>
-      <c r="Q991" s="4"/>
-      <c r="R991" s="4"/>
-      <c r="S991" s="4"/>
-      <c r="T991" s="4"/>
-      <c r="U991" s="4"/>
-      <c r="V991" s="4"/>
-      <c r="W991" s="4"/>
-      <c r="X991" s="4"/>
-      <c r="Y991" s="4"/>
-    </row>
-    <row r="992" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A992" s="4"/>
-      <c r="B992" s="4"/>
-      <c r="C992" s="4"/>
-      <c r="D992" s="4"/>
-      <c r="E992" s="4"/>
-      <c r="F992" s="4"/>
-      <c r="G992" s="4"/>
-      <c r="H992" s="4"/>
-      <c r="I992" s="4"/>
-      <c r="J992" s="4"/>
-      <c r="K992" s="4"/>
-      <c r="L992" s="4"/>
-      <c r="M992" s="4"/>
-      <c r="N992" s="4"/>
-      <c r="O992" s="4"/>
-      <c r="P992" s="4"/>
-      <c r="Q992" s="4"/>
-      <c r="R992" s="4"/>
-      <c r="S992" s="4"/>
-      <c r="T992" s="4"/>
-      <c r="U992" s="4"/>
-      <c r="V992" s="4"/>
-      <c r="W992" s="4"/>
-      <c r="X992" s="4"/>
-      <c r="Y992" s="4"/>
-    </row>
-    <row r="993" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A993" s="4"/>
-      <c r="B993" s="4"/>
-      <c r="C993" s="4"/>
-      <c r="D993" s="4"/>
-      <c r="E993" s="4"/>
-      <c r="F993" s="4"/>
-      <c r="G993" s="4"/>
-      <c r="H993" s="4"/>
-      <c r="I993" s="4"/>
-      <c r="J993" s="4"/>
-      <c r="K993" s="4"/>
-      <c r="L993" s="4"/>
-      <c r="M993" s="4"/>
-      <c r="N993" s="4"/>
-      <c r="O993" s="4"/>
-      <c r="P993" s="4"/>
-      <c r="Q993" s="4"/>
-      <c r="R993" s="4"/>
-      <c r="S993" s="4"/>
-      <c r="T993" s="4"/>
-      <c r="U993" s="4"/>
-      <c r="V993" s="4"/>
-      <c r="W993" s="4"/>
-      <c r="X993" s="4"/>
-      <c r="Y993" s="4"/>
-    </row>
-    <row r="994" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A994" s="4"/>
-      <c r="B994" s="4"/>
-      <c r="C994" s="4"/>
-      <c r="D994" s="4"/>
-      <c r="E994" s="4"/>
-      <c r="F994" s="4"/>
-      <c r="G994" s="4"/>
-      <c r="H994" s="4"/>
-      <c r="I994" s="4"/>
-      <c r="J994" s="4"/>
-      <c r="K994" s="4"/>
-      <c r="L994" s="4"/>
-      <c r="M994" s="4"/>
-      <c r="N994" s="4"/>
-      <c r="O994" s="4"/>
-      <c r="P994" s="4"/>
-      <c r="Q994" s="4"/>
-      <c r="R994" s="4"/>
-      <c r="S994" s="4"/>
-      <c r="T994" s="4"/>
-      <c r="U994" s="4"/>
-      <c r="V994" s="4"/>
-      <c r="W994" s="4"/>
-      <c r="X994" s="4"/>
-      <c r="Y994" s="4"/>
-    </row>
-    <row r="995" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A995" s="4"/>
-      <c r="B995" s="4"/>
-      <c r="C995" s="4"/>
-      <c r="D995" s="4"/>
-      <c r="E995" s="4"/>
-      <c r="F995" s="4"/>
-      <c r="G995" s="4"/>
-      <c r="H995" s="4"/>
-      <c r="I995" s="4"/>
-      <c r="J995" s="4"/>
-      <c r="K995" s="4"/>
-      <c r="L995" s="4"/>
-      <c r="M995" s="4"/>
-      <c r="N995" s="4"/>
-      <c r="O995" s="4"/>
-      <c r="P995" s="4"/>
-      <c r="Q995" s="4"/>
-      <c r="R995" s="4"/>
-      <c r="S995" s="4"/>
-      <c r="T995" s="4"/>
-      <c r="U995" s="4"/>
-      <c r="V995" s="4"/>
-      <c r="W995" s="4"/>
-      <c r="X995" s="4"/>
-      <c r="Y995" s="4"/>
-    </row>
-    <row r="996" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A996" s="4"/>
-      <c r="B996" s="4"/>
-      <c r="C996" s="4"/>
-      <c r="D996" s="4"/>
-      <c r="E996" s="4"/>
-      <c r="F996" s="4"/>
-      <c r="G996" s="4"/>
-      <c r="H996" s="4"/>
-      <c r="I996" s="4"/>
-      <c r="J996" s="4"/>
-      <c r="K996" s="4"/>
-      <c r="L996" s="4"/>
-      <c r="M996" s="4"/>
-      <c r="N996" s="4"/>
-      <c r="O996" s="4"/>
-      <c r="P996" s="4"/>
-      <c r="Q996" s="4"/>
-      <c r="R996" s="4"/>
-      <c r="S996" s="4"/>
-      <c r="T996" s="4"/>
-      <c r="U996" s="4"/>
-      <c r="V996" s="4"/>
-      <c r="W996" s="4"/>
-      <c r="X996" s="4"/>
-      <c r="Y996" s="4"/>
-    </row>
-    <row r="997" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A997" s="4"/>
-      <c r="B997" s="4"/>
-      <c r="C997" s="4"/>
-      <c r="D997" s="4"/>
-      <c r="E997" s="4"/>
-      <c r="F997" s="4"/>
-      <c r="G997" s="4"/>
-      <c r="H997" s="4"/>
-      <c r="I997" s="4"/>
-      <c r="J997" s="4"/>
-      <c r="K997" s="4"/>
-      <c r="L997" s="4"/>
-      <c r="M997" s="4"/>
-      <c r="N997" s="4"/>
-      <c r="O997" s="4"/>
-      <c r="P997" s="4"/>
-      <c r="Q997" s="4"/>
-      <c r="R997" s="4"/>
-      <c r="S997" s="4"/>
-      <c r="T997" s="4"/>
-      <c r="U997" s="4"/>
-      <c r="V997" s="4"/>
-      <c r="W997" s="4"/>
-      <c r="X997" s="4"/>
-      <c r="Y997" s="4"/>
-    </row>
-    <row r="998" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A998" s="4"/>
-      <c r="B998" s="4"/>
-      <c r="C998" s="4"/>
-      <c r="D998" s="4"/>
-      <c r="E998" s="4"/>
-      <c r="F998" s="4"/>
-      <c r="G998" s="4"/>
-      <c r="H998" s="4"/>
-      <c r="I998" s="4"/>
-      <c r="J998" s="4"/>
-      <c r="K998" s="4"/>
-      <c r="L998" s="4"/>
-      <c r="M998" s="4"/>
-      <c r="N998" s="4"/>
-      <c r="O998" s="4"/>
-      <c r="P998" s="4"/>
-      <c r="Q998" s="4"/>
-      <c r="R998" s="4"/>
-      <c r="S998" s="4"/>
-      <c r="T998" s="4"/>
-      <c r="U998" s="4"/>
-      <c r="V998" s="4"/>
-      <c r="W998" s="4"/>
-      <c r="X998" s="4"/>
-      <c r="Y998" s="4"/>
-    </row>
-    <row r="999" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A999" s="4"/>
-      <c r="B999" s="4"/>
-      <c r="C999" s="4"/>
-      <c r="D999" s="4"/>
-      <c r="E999" s="4"/>
-      <c r="F999" s="4"/>
-      <c r="G999" s="4"/>
-      <c r="H999" s="4"/>
-      <c r="I999" s="4"/>
-      <c r="J999" s="4"/>
-      <c r="K999" s="4"/>
-      <c r="L999" s="4"/>
-      <c r="M999" s="4"/>
-      <c r="N999" s="4"/>
-      <c r="O999" s="4"/>
-      <c r="P999" s="4"/>
-      <c r="Q999" s="4"/>
-      <c r="R999" s="4"/>
-      <c r="S999" s="4"/>
-      <c r="T999" s="4"/>
-      <c r="U999" s="4"/>
-      <c r="V999" s="4"/>
-      <c r="W999" s="4"/>
-      <c r="X999" s="4"/>
-      <c r="Y999" s="4"/>
-    </row>
-    <row r="1000" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1000" s="4"/>
-      <c r="B1000" s="4"/>
-      <c r="C1000" s="4"/>
-      <c r="D1000" s="4"/>
-      <c r="E1000" s="4"/>
-      <c r="F1000" s="4"/>
-      <c r="G1000" s="4"/>
-      <c r="H1000" s="4"/>
-      <c r="I1000" s="4"/>
-      <c r="J1000" s="4"/>
-      <c r="K1000" s="4"/>
-      <c r="L1000" s="4"/>
-      <c r="M1000" s="4"/>
-      <c r="N1000" s="4"/>
-      <c r="O1000" s="4"/>
-      <c r="P1000" s="4"/>
-      <c r="Q1000" s="4"/>
-      <c r="R1000" s="4"/>
-      <c r="S1000" s="4"/>
-      <c r="T1000" s="4"/>
-      <c r="U1000" s="4"/>
-      <c r="V1000" s="4"/>
-      <c r="W1000" s="4"/>
-      <c r="X1000" s="4"/>
-      <c r="Y1000" s="4"/>
-    </row>
-    <row r="1001" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1001" s="4"/>
-      <c r="B1001" s="4"/>
-      <c r="C1001" s="4"/>
-      <c r="D1001" s="4"/>
-      <c r="E1001" s="4"/>
-      <c r="F1001" s="4"/>
-      <c r="G1001" s="4"/>
-      <c r="H1001" s="4"/>
-      <c r="I1001" s="4"/>
-      <c r="J1001" s="4"/>
-      <c r="K1001" s="4"/>
-      <c r="L1001" s="4"/>
-      <c r="M1001" s="4"/>
-      <c r="N1001" s="4"/>
-      <c r="O1001" s="4"/>
-      <c r="P1001" s="4"/>
-      <c r="Q1001" s="4"/>
-      <c r="R1001" s="4"/>
-      <c r="S1001" s="4"/>
-      <c r="T1001" s="4"/>
-      <c r="U1001" s="4"/>
-      <c r="V1001" s="4"/>
-      <c r="W1001" s="4"/>
-      <c r="X1001" s="4"/>
-      <c r="Y1001" s="4"/>
-    </row>
-    <row r="1002" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1002" s="4"/>
-      <c r="B1002" s="4"/>
-      <c r="C1002" s="4"/>
-      <c r="D1002" s="4"/>
-      <c r="E1002" s="4"/>
-      <c r="F1002" s="4"/>
-      <c r="G1002" s="4"/>
-      <c r="H1002" s="4"/>
-      <c r="I1002" s="4"/>
-      <c r="J1002" s="4"/>
-      <c r="K1002" s="4"/>
-      <c r="L1002" s="4"/>
-      <c r="M1002" s="4"/>
-      <c r="N1002" s="4"/>
-      <c r="O1002" s="4"/>
-      <c r="P1002" s="4"/>
-      <c r="Q1002" s="4"/>
-      <c r="R1002" s="4"/>
-      <c r="S1002" s="4"/>
-      <c r="T1002" s="4"/>
-      <c r="U1002" s="4"/>
-      <c r="V1002" s="4"/>
-      <c r="W1002" s="4"/>
-      <c r="X1002" s="4"/>
-      <c r="Y1002" s="4"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/dashboard/data/Elite.xlsx
+++ b/dashboard/data/Elite.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PCS\Desktop\Python\Practice\dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72AAEA64-AFC4-4217-A811-05BFA3E0ECB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5A49A6-F70D-480C-8C22-00B95B6E4213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C510DD15-1ECC-4C0C-BE9E-FD99F7348715}"/>
   </bookViews>
@@ -110,7 +110,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -206,11 +206,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -247,6 +258,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -562,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E436C2D-E939-47CC-A565-7B11CCD28B8F}">
-  <dimension ref="A1:Y949"/>
+  <dimension ref="A1:Y950"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="10.140625" bestFit="1" customWidth="1"/>
@@ -570,7 +584,7 @@
     <col min="7" max="7" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -612,26 +626,14 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6">
-        <v>46127</v>
-      </c>
-      <c r="B2" s="12">
-        <v>0.84</v>
-      </c>
-      <c r="C2" s="12">
-        <v>0.43</v>
-      </c>
-      <c r="D2" s="12">
-        <v>0.85</v>
-      </c>
-      <c r="E2" s="12">
-        <v>0.66</v>
-      </c>
-      <c r="F2" s="12">
-        <v>-0.81</v>
-      </c>
+      <c r="A2" s="13"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
       <c r="G2" s="12">
-        <v>-1.28</v>
+        <v>3.79</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
@@ -654,25 +656,25 @@
     </row>
     <row r="3" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
-        <v>46125</v>
-      </c>
-      <c r="B3" s="8">
-        <v>1.94</v>
-      </c>
-      <c r="C3" s="8">
-        <v>1.84</v>
-      </c>
-      <c r="D3" s="8">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="E3" s="8">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="F3" s="8">
-        <v>-17.72</v>
-      </c>
-      <c r="G3" s="8">
-        <v>0</v>
+        <v>46127</v>
+      </c>
+      <c r="B3" s="12">
+        <v>0.84</v>
+      </c>
+      <c r="C3" s="12">
+        <v>0.43</v>
+      </c>
+      <c r="D3" s="12">
+        <v>0.85</v>
+      </c>
+      <c r="E3" s="12">
+        <v>0.66</v>
+      </c>
+      <c r="F3" s="12">
+        <v>-0.81</v>
+      </c>
+      <c r="G3" s="12">
+        <v>-1.28</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -695,25 +697,25 @@
     </row>
     <row r="4" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
-        <v>46122</v>
-      </c>
-      <c r="B4" s="9">
+        <v>46125</v>
+      </c>
+      <c r="B4" s="8">
+        <v>1.94</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1.84</v>
+      </c>
+      <c r="D4" s="8">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="E4" s="8">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="F4" s="8">
+        <v>-17.72</v>
+      </c>
+      <c r="G4" s="8">
         <v>0</v>
-      </c>
-      <c r="C4" s="9">
-        <v>0</v>
-      </c>
-      <c r="D4" s="9">
-        <v>0.44</v>
-      </c>
-      <c r="E4" s="9">
-        <v>1.08</v>
-      </c>
-      <c r="F4" s="9">
-        <v>-0.19</v>
-      </c>
-      <c r="G4" s="9">
-        <v>-3.03</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -736,25 +738,25 @@
     </row>
     <row r="5" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
-        <v>46121</v>
-      </c>
-      <c r="B5" s="10">
-        <v>0.46</v>
-      </c>
-      <c r="C5" s="10">
-        <v>0.09</v>
-      </c>
-      <c r="D5" s="10">
-        <v>1.51</v>
-      </c>
-      <c r="E5" s="10">
-        <v>1.72</v>
-      </c>
-      <c r="F5" s="10">
-        <v>0.59</v>
-      </c>
-      <c r="G5" s="10">
-        <v>2.02</v>
+        <v>46122</v>
+      </c>
+      <c r="B5" s="9">
+        <v>0</v>
+      </c>
+      <c r="C5" s="9">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0.44</v>
+      </c>
+      <c r="E5" s="9">
+        <v>1.08</v>
+      </c>
+      <c r="F5" s="9">
+        <v>-0.19</v>
+      </c>
+      <c r="G5" s="9">
+        <v>-3.03</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
@@ -777,25 +779,25 @@
     </row>
     <row r="6" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
-        <v>46120</v>
-      </c>
-      <c r="B6" s="9">
-        <v>-0.12</v>
-      </c>
-      <c r="C6" s="9">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="D6" s="9">
-        <v>-0.56999999999999995</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.94</v>
-      </c>
-      <c r="F6" s="9">
-        <v>0</v>
-      </c>
-      <c r="G6" s="9">
-        <v>0</v>
+        <v>46121</v>
+      </c>
+      <c r="B6" s="10">
+        <v>0.46</v>
+      </c>
+      <c r="C6" s="10">
+        <v>0.09</v>
+      </c>
+      <c r="D6" s="10">
+        <v>1.51</v>
+      </c>
+      <c r="E6" s="10">
+        <v>1.72</v>
+      </c>
+      <c r="F6" s="10">
+        <v>0.59</v>
+      </c>
+      <c r="G6" s="10">
+        <v>2.02</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
@@ -818,25 +820,25 @@
     </row>
     <row r="7" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
-        <v>46119</v>
-      </c>
-      <c r="B7" s="10">
-        <v>0.95</v>
-      </c>
-      <c r="C7" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="D7" s="10">
-        <v>-0.4</v>
-      </c>
-      <c r="E7" s="10">
-        <v>0.39</v>
-      </c>
-      <c r="F7" s="10">
+        <v>46120</v>
+      </c>
+      <c r="B7" s="9">
+        <v>-0.12</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="D7" s="9">
+        <v>-0.56999999999999995</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0.94</v>
+      </c>
+      <c r="F7" s="9">
         <v>0</v>
       </c>
-      <c r="G7" s="10">
-        <v>1.1499999999999999</v>
+      <c r="G7" s="9">
+        <v>0</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -859,25 +861,25 @@
     </row>
     <row r="8" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
-        <v>46118</v>
-      </c>
-      <c r="B8" s="9">
-        <v>-0.14000000000000001</v>
-      </c>
-      <c r="C8" s="9">
-        <v>-0.46</v>
-      </c>
-      <c r="D8" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B8" s="10">
+        <v>0.95</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="D8" s="10">
+        <v>-0.4</v>
+      </c>
+      <c r="E8" s="10">
+        <v>0.39</v>
+      </c>
+      <c r="F8" s="10">
         <v>0</v>
       </c>
-      <c r="E8" s="9">
-        <v>0</v>
-      </c>
-      <c r="F8" s="9">
-        <v>0.13</v>
-      </c>
-      <c r="G8" s="9">
-        <v>4.22</v>
+      <c r="G8" s="10">
+        <v>1.1499999999999999</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -900,25 +902,25 @@
     </row>
     <row r="9" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B9" s="9">
-        <v>1.22</v>
+        <v>-0.14000000000000001</v>
       </c>
       <c r="C9" s="9">
-        <v>0.1</v>
+        <v>-0.46</v>
       </c>
       <c r="D9" s="9">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="E9" s="9">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="F9" s="9">
-        <v>-0.52</v>
+        <v>0.13</v>
       </c>
       <c r="G9" s="9">
-        <v>-1.5</v>
+        <v>4.22</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -941,25 +943,25 @@
     </row>
     <row r="10" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
-        <v>46113</v>
-      </c>
-      <c r="B10" s="10">
-        <v>-1.21</v>
-      </c>
-      <c r="C10" s="10">
-        <v>-1.38</v>
-      </c>
-      <c r="D10" s="10">
-        <v>-0.84</v>
-      </c>
-      <c r="E10" s="10">
-        <v>-1.81</v>
-      </c>
-      <c r="F10" s="10">
-        <v>-1.96</v>
-      </c>
-      <c r="G10" s="10">
-        <v>-2.73</v>
+        <v>46114</v>
+      </c>
+      <c r="B10" s="9">
+        <v>1.22</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="D10" s="9">
+        <v>1.07</v>
+      </c>
+      <c r="E10" s="9">
+        <v>1.51</v>
+      </c>
+      <c r="F10" s="9">
+        <v>-0.52</v>
+      </c>
+      <c r="G10" s="9">
+        <v>-1.5</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
@@ -982,25 +984,25 @@
     </row>
     <row r="11" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
-        <v>46111</v>
-      </c>
-      <c r="B11" s="9">
-        <v>-1.73</v>
-      </c>
-      <c r="C11" s="9">
-        <v>0.13</v>
-      </c>
-      <c r="D11" s="9">
-        <v>1.21</v>
-      </c>
-      <c r="E11" s="9">
-        <v>1.73</v>
-      </c>
-      <c r="F11" s="9">
-        <v>0</v>
-      </c>
-      <c r="G11" s="9">
-        <v>0</v>
+        <v>46113</v>
+      </c>
+      <c r="B11" s="10">
+        <v>-1.21</v>
+      </c>
+      <c r="C11" s="10">
+        <v>-1.38</v>
+      </c>
+      <c r="D11" s="10">
+        <v>-0.84</v>
+      </c>
+      <c r="E11" s="10">
+        <v>-1.81</v>
+      </c>
+      <c r="F11" s="10">
+        <v>-1.96</v>
+      </c>
+      <c r="G11" s="10">
+        <v>-2.73</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -1023,25 +1025,25 @@
     </row>
     <row r="12" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
-        <v>46108</v>
-      </c>
-      <c r="B12" s="10">
+        <v>46111</v>
+      </c>
+      <c r="B12" s="9">
+        <v>-1.73</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0.13</v>
+      </c>
+      <c r="D12" s="9">
+        <v>1.21</v>
+      </c>
+      <c r="E12" s="9">
+        <v>1.73</v>
+      </c>
+      <c r="F12" s="9">
         <v>0</v>
       </c>
-      <c r="C12" s="10">
+      <c r="G12" s="9">
         <v>0</v>
-      </c>
-      <c r="D12" s="10">
-        <v>1.95</v>
-      </c>
-      <c r="E12" s="10">
-        <v>1.94</v>
-      </c>
-      <c r="F12" s="10">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="G12" s="10">
-        <v>7.63</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -1064,25 +1066,25 @@
     </row>
     <row r="13" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
-        <v>46106</v>
-      </c>
-      <c r="B13" s="9">
-        <v>0.93</v>
-      </c>
-      <c r="C13" s="9">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="D13" s="9">
-        <v>0.16</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-0.41</v>
-      </c>
-      <c r="F13" s="9">
+        <v>46108</v>
+      </c>
+      <c r="B13" s="10">
         <v>0</v>
       </c>
-      <c r="G13" s="9">
-        <v>2.29</v>
+      <c r="C13" s="10">
+        <v>0</v>
+      </c>
+      <c r="D13" s="10">
+        <v>1.95</v>
+      </c>
+      <c r="E13" s="10">
+        <v>1.94</v>
+      </c>
+      <c r="F13" s="10">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="G13" s="10">
+        <v>7.63</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -1105,25 +1107,25 @@
     </row>
     <row r="14" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
-        <v>46105</v>
-      </c>
-      <c r="B14" s="10">
-        <v>0.19</v>
-      </c>
-      <c r="C14" s="10">
-        <v>-1.29</v>
-      </c>
-      <c r="D14" s="10">
-        <v>1.45</v>
-      </c>
-      <c r="E14" s="10">
-        <v>0.33</v>
-      </c>
-      <c r="F14" s="10">
-        <v>-3.09</v>
-      </c>
-      <c r="G14" s="10">
-        <v>-0.61</v>
+        <v>46106</v>
+      </c>
+      <c r="B14" s="9">
+        <v>0.93</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0.16</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-0.41</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>2.29</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
@@ -1146,25 +1148,25 @@
     </row>
     <row r="15" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
-        <v>46104</v>
-      </c>
-      <c r="B15" s="9">
-        <v>0.3</v>
-      </c>
-      <c r="C15" s="9">
-        <v>0.31</v>
-      </c>
-      <c r="D15" s="9">
-        <v>1.03</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-1.97</v>
-      </c>
-      <c r="F15" s="9">
-        <v>0</v>
-      </c>
-      <c r="G15" s="9">
-        <v>4.28</v>
+        <v>46105</v>
+      </c>
+      <c r="B15" s="10">
+        <v>0.19</v>
+      </c>
+      <c r="C15" s="10">
+        <v>-1.29</v>
+      </c>
+      <c r="D15" s="10">
+        <v>1.45</v>
+      </c>
+      <c r="E15" s="10">
+        <v>0.33</v>
+      </c>
+      <c r="F15" s="10">
+        <v>-3.09</v>
+      </c>
+      <c r="G15" s="10">
+        <v>-0.61</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -1187,25 +1189,25 @@
     </row>
     <row r="16" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
-        <v>46101</v>
-      </c>
-      <c r="B16" s="10">
+        <v>46104</v>
+      </c>
+      <c r="B16" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0.31</v>
+      </c>
+      <c r="D16" s="9">
+        <v>1.03</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-1.97</v>
+      </c>
+      <c r="F16" s="9">
         <v>0</v>
       </c>
-      <c r="C16" s="10">
-        <v>0</v>
-      </c>
-      <c r="D16" s="10">
-        <v>-0.27</v>
-      </c>
-      <c r="E16" s="10">
-        <v>-0.24</v>
-      </c>
-      <c r="F16" s="10">
-        <v>-2.88</v>
-      </c>
-      <c r="G16" s="10">
-        <v>-3.94</v>
+      <c r="G16" s="9">
+        <v>4.28</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -1228,25 +1230,25 @@
     </row>
     <row r="17" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
-        <v>46100</v>
-      </c>
-      <c r="B17" s="9">
-        <v>1.35</v>
-      </c>
-      <c r="C17" s="9">
-        <v>1.18</v>
-      </c>
-      <c r="D17" s="9">
-        <v>2</v>
-      </c>
-      <c r="E17" s="9">
-        <v>1.96</v>
-      </c>
-      <c r="F17" s="9">
-        <v>2.85</v>
-      </c>
-      <c r="G17" s="9">
-        <v>6.27</v>
+        <v>46101</v>
+      </c>
+      <c r="B17" s="10">
+        <v>0</v>
+      </c>
+      <c r="C17" s="10">
+        <v>0</v>
+      </c>
+      <c r="D17" s="10">
+        <v>-0.27</v>
+      </c>
+      <c r="E17" s="10">
+        <v>-0.24</v>
+      </c>
+      <c r="F17" s="10">
+        <v>-2.88</v>
+      </c>
+      <c r="G17" s="10">
+        <v>-3.94</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
@@ -1269,25 +1271,25 @@
     </row>
     <row r="18" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
-        <v>46099</v>
-      </c>
-      <c r="B18" s="10">
-        <v>-1.93</v>
-      </c>
-      <c r="C18" s="10">
-        <v>0.35</v>
-      </c>
-      <c r="D18" s="10">
-        <v>0.36</v>
-      </c>
-      <c r="E18" s="10">
-        <v>-2.0299999999999998</v>
-      </c>
-      <c r="F18" s="10">
-        <v>0</v>
-      </c>
-      <c r="G18" s="10">
-        <v>0.3</v>
+        <v>46100</v>
+      </c>
+      <c r="B18" s="9">
+        <v>1.35</v>
+      </c>
+      <c r="C18" s="9">
+        <v>1.18</v>
+      </c>
+      <c r="D18" s="9">
+        <v>2</v>
+      </c>
+      <c r="E18" s="9">
+        <v>1.96</v>
+      </c>
+      <c r="F18" s="9">
+        <v>2.85</v>
+      </c>
+      <c r="G18" s="9">
+        <v>6.27</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
@@ -1310,25 +1312,25 @@
     </row>
     <row r="19" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
-        <v>46098</v>
-      </c>
-      <c r="B19" s="9">
-        <v>0.03</v>
-      </c>
-      <c r="C19" s="9">
-        <v>0.11</v>
-      </c>
-      <c r="D19" s="9">
-        <v>-0.4</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-1.22</v>
-      </c>
-      <c r="F19" s="9">
+        <v>46099</v>
+      </c>
+      <c r="B19" s="10">
+        <v>-1.93</v>
+      </c>
+      <c r="C19" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="D19" s="10">
+        <v>0.36</v>
+      </c>
+      <c r="E19" s="10">
+        <v>-2.0299999999999998</v>
+      </c>
+      <c r="F19" s="10">
         <v>0</v>
       </c>
-      <c r="G19" s="9">
-        <v>3.95</v>
+      <c r="G19" s="10">
+        <v>0.3</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
@@ -1351,25 +1353,25 @@
     </row>
     <row r="20" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
-        <v>46097</v>
-      </c>
-      <c r="B20" s="10">
-        <v>-1.46</v>
-      </c>
-      <c r="C20" s="10">
-        <v>-2.2000000000000002</v>
-      </c>
-      <c r="D20" s="10">
-        <v>-1.91</v>
-      </c>
-      <c r="E20" s="10">
-        <v>-1.97</v>
-      </c>
-      <c r="F20" s="10">
-        <v>2.64</v>
-      </c>
-      <c r="G20" s="10">
-        <v>6.07</v>
+        <v>46098</v>
+      </c>
+      <c r="B20" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0.11</v>
+      </c>
+      <c r="D20" s="9">
+        <v>-0.4</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-1.22</v>
+      </c>
+      <c r="F20" s="9">
+        <v>0</v>
+      </c>
+      <c r="G20" s="9">
+        <v>3.95</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
@@ -1392,25 +1394,25 @@
     </row>
     <row r="21" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
-        <v>46094</v>
-      </c>
-      <c r="B21" s="9">
-        <v>0</v>
-      </c>
-      <c r="C21" s="9">
-        <v>0</v>
-      </c>
-      <c r="D21" s="9">
-        <v>-1.22</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-1.7</v>
-      </c>
-      <c r="F21" s="9">
-        <v>0</v>
-      </c>
-      <c r="G21" s="9">
-        <v>-0.15</v>
+        <v>46097</v>
+      </c>
+      <c r="B21" s="10">
+        <v>-1.46</v>
+      </c>
+      <c r="C21" s="10">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="D21" s="10">
+        <v>-1.91</v>
+      </c>
+      <c r="E21" s="10">
+        <v>-1.97</v>
+      </c>
+      <c r="F21" s="10">
+        <v>2.64</v>
+      </c>
+      <c r="G21" s="10">
+        <v>6.07</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
@@ -1433,25 +1435,25 @@
     </row>
     <row r="22" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
-        <v>46093</v>
-      </c>
-      <c r="B22" s="10">
-        <v>-1.38</v>
-      </c>
-      <c r="C22" s="10">
-        <v>-0.26</v>
-      </c>
-      <c r="D22" s="10">
-        <v>-1.9</v>
-      </c>
-      <c r="E22" s="10">
-        <v>-2.14</v>
-      </c>
-      <c r="F22" s="10">
+        <v>46094</v>
+      </c>
+      <c r="B22" s="9">
         <v>0</v>
       </c>
-      <c r="G22" s="10">
-        <v>0.72</v>
+      <c r="C22" s="9">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9">
+        <v>-1.22</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-1.7</v>
+      </c>
+      <c r="F22" s="9">
+        <v>0</v>
+      </c>
+      <c r="G22" s="9">
+        <v>-0.15</v>
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
@@ -1474,25 +1476,25 @@
     </row>
     <row r="23" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
-        <v>46092</v>
-      </c>
-      <c r="B23" s="9">
-        <v>-1.56</v>
-      </c>
-      <c r="C23" s="9">
-        <v>-0.6</v>
-      </c>
-      <c r="D23" s="9">
-        <v>0.45</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-2.09</v>
-      </c>
-      <c r="F23" s="9">
-        <v>1.76</v>
-      </c>
-      <c r="G23" s="9">
-        <v>3.64</v>
+        <v>46093</v>
+      </c>
+      <c r="B23" s="10">
+        <v>-1.38</v>
+      </c>
+      <c r="C23" s="10">
+        <v>-0.26</v>
+      </c>
+      <c r="D23" s="10">
+        <v>-1.9</v>
+      </c>
+      <c r="E23" s="10">
+        <v>-2.14</v>
+      </c>
+      <c r="F23" s="10">
+        <v>0</v>
+      </c>
+      <c r="G23" s="10">
+        <v>0.72</v>
       </c>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
@@ -1515,25 +1517,25 @@
     </row>
     <row r="24" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
-        <v>46091</v>
-      </c>
-      <c r="B24" s="10">
-        <v>0.31</v>
-      </c>
-      <c r="C24" s="10">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="D24" s="10">
-        <v>-1.73</v>
-      </c>
-      <c r="E24" s="10">
-        <v>0.96</v>
-      </c>
-      <c r="F24" s="10">
-        <v>3.2</v>
-      </c>
-      <c r="G24" s="10">
-        <v>7.06</v>
+        <v>46092</v>
+      </c>
+      <c r="B24" s="9">
+        <v>-1.56</v>
+      </c>
+      <c r="C24" s="9">
+        <v>-0.6</v>
+      </c>
+      <c r="D24" s="9">
+        <v>0.45</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-2.09</v>
+      </c>
+      <c r="F24" s="9">
+        <v>1.76</v>
+      </c>
+      <c r="G24" s="9">
+        <v>3.64</v>
       </c>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
@@ -1556,25 +1558,25 @@
     </row>
     <row r="25" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
-        <v>46090</v>
-      </c>
-      <c r="B25" s="9">
-        <v>0.82</v>
-      </c>
-      <c r="C25" s="9">
-        <v>-0.37</v>
-      </c>
-      <c r="D25" s="9">
-        <v>0.99</v>
-      </c>
-      <c r="E25" s="9">
-        <v>1.28</v>
-      </c>
-      <c r="F25" s="9">
-        <v>0</v>
-      </c>
-      <c r="G25" s="9">
-        <v>5.85</v>
+        <v>46091</v>
+      </c>
+      <c r="B25" s="10">
+        <v>0.31</v>
+      </c>
+      <c r="C25" s="10">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="D25" s="10">
+        <v>-1.73</v>
+      </c>
+      <c r="E25" s="10">
+        <v>0.96</v>
+      </c>
+      <c r="F25" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="G25" s="10">
+        <v>7.06</v>
       </c>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
@@ -1597,25 +1599,25 @@
     </row>
     <row r="26" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
-        <v>46087</v>
-      </c>
-      <c r="B26" s="10">
+        <v>46090</v>
+      </c>
+      <c r="B26" s="9">
+        <v>0.82</v>
+      </c>
+      <c r="C26" s="9">
+        <v>-0.37</v>
+      </c>
+      <c r="D26" s="9">
+        <v>0.99</v>
+      </c>
+      <c r="E26" s="9">
+        <v>1.28</v>
+      </c>
+      <c r="F26" s="9">
         <v>0</v>
       </c>
-      <c r="C26" s="10">
-        <v>0</v>
-      </c>
-      <c r="D26" s="10">
-        <v>-1.81</v>
-      </c>
-      <c r="E26" s="10">
-        <v>1.57</v>
-      </c>
-      <c r="F26" s="10">
-        <v>-3.5</v>
-      </c>
-      <c r="G26" s="10">
-        <v>1.46</v>
+      <c r="G26" s="9">
+        <v>5.85</v>
       </c>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
@@ -1638,25 +1640,25 @@
     </row>
     <row r="27" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
-        <v>46086</v>
-      </c>
-      <c r="B27" s="9">
-        <v>1.63</v>
-      </c>
-      <c r="C27" s="9">
-        <v>0.3</v>
-      </c>
-      <c r="D27" s="9">
-        <v>-0.47</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-0.08</v>
-      </c>
-      <c r="F27" s="9">
+        <v>46087</v>
+      </c>
+      <c r="B27" s="10">
         <v>0</v>
       </c>
-      <c r="G27" s="9">
-        <v>3.79</v>
+      <c r="C27" s="10">
+        <v>0</v>
+      </c>
+      <c r="D27" s="10">
+        <v>-1.81</v>
+      </c>
+      <c r="E27" s="10">
+        <v>1.57</v>
+      </c>
+      <c r="F27" s="10">
+        <v>-3.5</v>
+      </c>
+      <c r="G27" s="10">
+        <v>1.46</v>
       </c>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
@@ -1679,25 +1681,25 @@
     </row>
     <row r="28" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
-        <v>46085</v>
-      </c>
-      <c r="B28" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="C28" s="10">
-        <v>-1.2</v>
-      </c>
-      <c r="D28" s="10">
-        <v>0.51</v>
-      </c>
-      <c r="E28" s="10">
-        <v>1.27</v>
-      </c>
-      <c r="F28" s="10">
-        <v>-3.08</v>
-      </c>
-      <c r="G28" s="10">
-        <v>-10.52</v>
+        <v>46086</v>
+      </c>
+      <c r="B28" s="9">
+        <v>1.63</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="D28" s="9">
+        <v>-0.47</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-0.08</v>
+      </c>
+      <c r="F28" s="9">
+        <v>0</v>
+      </c>
+      <c r="G28" s="9">
+        <v>3.79</v>
       </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
@@ -1720,25 +1722,25 @@
     </row>
     <row r="29" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
-        <v>46083</v>
-      </c>
-      <c r="B29" s="9">
-        <v>-1.08</v>
-      </c>
-      <c r="C29" s="9">
-        <v>-0.78</v>
-      </c>
-      <c r="D29" s="9">
+        <v>46085</v>
+      </c>
+      <c r="B29" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="C29" s="10">
+        <v>-1.2</v>
+      </c>
+      <c r="D29" s="10">
+        <v>0.51</v>
+      </c>
+      <c r="E29" s="10">
         <v>1.27</v>
       </c>
-      <c r="E29" s="9">
-        <v>-0.09</v>
-      </c>
-      <c r="F29" s="9">
-        <v>0</v>
-      </c>
-      <c r="G29" s="9">
-        <v>3.42</v>
+      <c r="F29" s="10">
+        <v>-3.08</v>
+      </c>
+      <c r="G29" s="10">
+        <v>-10.52</v>
       </c>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
@@ -1761,25 +1763,25 @@
     </row>
     <row r="30" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
-        <v>46080</v>
-      </c>
-      <c r="B30" s="10">
+        <v>46083</v>
+      </c>
+      <c r="B30" s="9">
+        <v>-1.08</v>
+      </c>
+      <c r="C30" s="9">
+        <v>-0.78</v>
+      </c>
+      <c r="D30" s="9">
+        <v>1.27</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-0.09</v>
+      </c>
+      <c r="F30" s="9">
         <v>0</v>
       </c>
-      <c r="C30" s="10">
-        <v>0</v>
-      </c>
-      <c r="D30" s="10">
-        <v>-1.83</v>
-      </c>
-      <c r="E30" s="10">
-        <v>-0.04</v>
-      </c>
-      <c r="F30" s="10">
-        <v>2.44</v>
-      </c>
-      <c r="G30" s="10">
-        <v>0.63</v>
+      <c r="G30" s="9">
+        <v>3.42</v>
       </c>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
@@ -1802,25 +1804,25 @@
     </row>
     <row r="31" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
-        <v>46079</v>
-      </c>
-      <c r="B31" s="9">
-        <v>-0.22</v>
-      </c>
-      <c r="C31" s="9">
-        <v>0.05</v>
-      </c>
-      <c r="D31" s="9">
-        <v>0.33</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-1.53</v>
-      </c>
-      <c r="F31" s="9">
-        <v>0.48</v>
-      </c>
-      <c r="G31" s="9">
-        <v>-2.42</v>
+        <v>46080</v>
+      </c>
+      <c r="B31" s="10">
+        <v>0</v>
+      </c>
+      <c r="C31" s="10">
+        <v>0</v>
+      </c>
+      <c r="D31" s="10">
+        <v>-1.83</v>
+      </c>
+      <c r="E31" s="10">
+        <v>-0.04</v>
+      </c>
+      <c r="F31" s="10">
+        <v>2.44</v>
+      </c>
+      <c r="G31" s="10">
+        <v>0.63</v>
       </c>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
@@ -1843,25 +1845,25 @@
     </row>
     <row r="32" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
-        <v>46078</v>
-      </c>
-      <c r="B32" s="10">
-        <v>-0.04</v>
-      </c>
-      <c r="C32" s="10">
-        <v>0.47</v>
-      </c>
-      <c r="D32" s="10">
-        <v>-0.21</v>
-      </c>
-      <c r="E32" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="F32" s="10">
-        <v>-2.88</v>
-      </c>
-      <c r="G32" s="10">
-        <v>-5.39</v>
+        <v>46079</v>
+      </c>
+      <c r="B32" s="9">
+        <v>-0.22</v>
+      </c>
+      <c r="C32" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0.33</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-1.53</v>
+      </c>
+      <c r="F32" s="9">
+        <v>0.48</v>
+      </c>
+      <c r="G32" s="9">
+        <v>-2.42</v>
       </c>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -1884,25 +1886,25 @@
     </row>
     <row r="33" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
-        <v>46077</v>
-      </c>
-      <c r="B33" s="9">
-        <v>0.05</v>
-      </c>
-      <c r="C33" s="9">
-        <v>-0.28000000000000003</v>
-      </c>
-      <c r="D33" s="9">
-        <v>-1.06</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-0.5</v>
-      </c>
-      <c r="F33" s="9">
-        <v>0</v>
-      </c>
-      <c r="G33" s="9">
-        <v>-1.24</v>
+        <v>46078</v>
+      </c>
+      <c r="B33" s="10">
+        <v>-0.04</v>
+      </c>
+      <c r="C33" s="10">
+        <v>0.47</v>
+      </c>
+      <c r="D33" s="10">
+        <v>-0.21</v>
+      </c>
+      <c r="E33" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="F33" s="10">
+        <v>-2.88</v>
+      </c>
+      <c r="G33" s="10">
+        <v>-5.39</v>
       </c>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
@@ -1925,25 +1927,25 @@
     </row>
     <row r="34" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
-        <v>46076</v>
-      </c>
-      <c r="B34" s="10">
-        <v>0.38</v>
-      </c>
-      <c r="C34" s="10">
-        <v>0.61</v>
-      </c>
-      <c r="D34" s="10">
-        <v>0.26</v>
-      </c>
-      <c r="E34" s="10">
-        <v>0.41</v>
-      </c>
-      <c r="F34" s="10">
-        <v>-4.07</v>
-      </c>
-      <c r="G34" s="10">
-        <v>4.2</v>
+        <v>46077</v>
+      </c>
+      <c r="B34" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="C34" s="9">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="D34" s="9">
+        <v>-1.06</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-0.5</v>
+      </c>
+      <c r="F34" s="9">
+        <v>0</v>
+      </c>
+      <c r="G34" s="9">
+        <v>-1.24</v>
       </c>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
@@ -1966,25 +1968,25 @@
     </row>
     <row r="35" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
-        <v>46073</v>
-      </c>
-      <c r="B35" s="9">
-        <v>0</v>
-      </c>
-      <c r="C35" s="9">
-        <v>0</v>
-      </c>
-      <c r="D35" s="9">
+        <v>46076</v>
+      </c>
+      <c r="B35" s="10">
+        <v>0.38</v>
+      </c>
+      <c r="C35" s="10">
+        <v>0.61</v>
+      </c>
+      <c r="D35" s="10">
         <v>0.26</v>
       </c>
-      <c r="E35" s="9">
-        <v>0</v>
-      </c>
-      <c r="F35" s="9">
-        <v>0</v>
-      </c>
-      <c r="G35" s="9">
-        <v>-2.13</v>
+      <c r="E35" s="10">
+        <v>0.41</v>
+      </c>
+      <c r="F35" s="10">
+        <v>-4.07</v>
+      </c>
+      <c r="G35" s="10">
+        <v>4.2</v>
       </c>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
@@ -2007,25 +2009,25 @@
     </row>
     <row r="36" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
-        <v>46072</v>
-      </c>
-      <c r="B36" s="10">
-        <v>-0.79</v>
-      </c>
-      <c r="C36" s="10">
-        <v>-0.45</v>
-      </c>
-      <c r="D36" s="10">
-        <v>0.74</v>
-      </c>
-      <c r="E36" s="10">
-        <v>0.95</v>
-      </c>
-      <c r="F36" s="10">
-        <v>3.44</v>
-      </c>
-      <c r="G36" s="10">
-        <v>2.97</v>
+        <v>46073</v>
+      </c>
+      <c r="B36" s="9">
+        <v>0</v>
+      </c>
+      <c r="C36" s="9">
+        <v>0</v>
+      </c>
+      <c r="D36" s="9">
+        <v>0.26</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0</v>
+      </c>
+      <c r="F36" s="9">
+        <v>0</v>
+      </c>
+      <c r="G36" s="9">
+        <v>-2.13</v>
       </c>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
@@ -2048,25 +2050,25 @@
     </row>
     <row r="37" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
-        <v>46071</v>
-      </c>
-      <c r="B37" s="9">
-        <v>0.63</v>
-      </c>
-      <c r="C37" s="9">
-        <v>0.11</v>
-      </c>
-      <c r="D37" s="9">
-        <v>0.46</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-0.47</v>
-      </c>
-      <c r="F37" s="9">
-        <v>0</v>
-      </c>
-      <c r="G37" s="9">
-        <v>-0.23</v>
+        <v>46072</v>
+      </c>
+      <c r="B37" s="10">
+        <v>-0.79</v>
+      </c>
+      <c r="C37" s="10">
+        <v>-0.45</v>
+      </c>
+      <c r="D37" s="10">
+        <v>0.74</v>
+      </c>
+      <c r="E37" s="10">
+        <v>0.95</v>
+      </c>
+      <c r="F37" s="10">
+        <v>3.44</v>
+      </c>
+      <c r="G37" s="10">
+        <v>2.97</v>
       </c>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
@@ -2089,25 +2091,25 @@
     </row>
     <row r="38" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
-        <v>46070</v>
-      </c>
-      <c r="B38" s="10">
-        <v>-0.38</v>
-      </c>
-      <c r="C38" s="10">
-        <v>-0.28000000000000003</v>
-      </c>
-      <c r="D38" s="10">
-        <v>-1.33</v>
-      </c>
-      <c r="E38" s="10">
-        <v>-1.44</v>
-      </c>
-      <c r="F38" s="10">
+        <v>46071</v>
+      </c>
+      <c r="B38" s="9">
+        <v>0.63</v>
+      </c>
+      <c r="C38" s="9">
+        <v>0.11</v>
+      </c>
+      <c r="D38" s="9">
+        <v>0.46</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-0.47</v>
+      </c>
+      <c r="F38" s="9">
         <v>0</v>
       </c>
-      <c r="G38" s="10">
-        <v>2.3199999999999998</v>
+      <c r="G38" s="9">
+        <v>-0.23</v>
       </c>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
@@ -2130,25 +2132,25 @@
     </row>
     <row r="39" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
-        <v>46069</v>
-      </c>
-      <c r="B39" s="9">
-        <v>-1.58</v>
-      </c>
-      <c r="C39" s="9">
-        <v>-1.05</v>
-      </c>
-      <c r="D39" s="9">
-        <v>-1.56</v>
-      </c>
-      <c r="E39" s="9">
-        <v>0.09</v>
-      </c>
-      <c r="F39" s="9">
-        <v>3.2</v>
-      </c>
-      <c r="G39" s="9">
-        <v>5.12</v>
+        <v>46070</v>
+      </c>
+      <c r="B39" s="10">
+        <v>-0.38</v>
+      </c>
+      <c r="C39" s="10">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="D39" s="10">
+        <v>-1.33</v>
+      </c>
+      <c r="E39" s="10">
+        <v>-1.44</v>
+      </c>
+      <c r="F39" s="10">
+        <v>0</v>
+      </c>
+      <c r="G39" s="10">
+        <v>2.3199999999999998</v>
       </c>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
@@ -2171,25 +2173,25 @@
     </row>
     <row r="40" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
-        <v>46066</v>
-      </c>
-      <c r="B40" s="10">
-        <v>0</v>
-      </c>
-      <c r="C40" s="10">
-        <v>0</v>
-      </c>
-      <c r="D40" s="10">
-        <v>-0.41</v>
-      </c>
-      <c r="E40" s="10">
-        <v>-0.41</v>
-      </c>
-      <c r="F40" s="10">
-        <v>3.94</v>
-      </c>
-      <c r="G40" s="10">
-        <v>2.5</v>
+        <v>46069</v>
+      </c>
+      <c r="B40" s="9">
+        <v>-1.58</v>
+      </c>
+      <c r="C40" s="9">
+        <v>-1.05</v>
+      </c>
+      <c r="D40" s="9">
+        <v>-1.56</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0.09</v>
+      </c>
+      <c r="F40" s="9">
+        <v>3.2</v>
+      </c>
+      <c r="G40" s="9">
+        <v>5.12</v>
       </c>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
@@ -2212,25 +2214,25 @@
     </row>
     <row r="41" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6">
-        <v>46065</v>
-      </c>
-      <c r="B41" s="9">
-        <v>0.26</v>
-      </c>
-      <c r="C41" s="9">
-        <v>0.18</v>
-      </c>
-      <c r="D41" s="9">
-        <v>0.36</v>
-      </c>
-      <c r="E41" s="9">
-        <v>0.52</v>
-      </c>
-      <c r="F41" s="9">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="G41" s="9">
-        <v>3.77</v>
+        <v>46066</v>
+      </c>
+      <c r="B41" s="10">
+        <v>0</v>
+      </c>
+      <c r="C41" s="10">
+        <v>0</v>
+      </c>
+      <c r="D41" s="10">
+        <v>-0.41</v>
+      </c>
+      <c r="E41" s="10">
+        <v>-0.41</v>
+      </c>
+      <c r="F41" s="10">
+        <v>3.94</v>
+      </c>
+      <c r="G41" s="10">
+        <v>2.5</v>
       </c>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
@@ -2253,25 +2255,25 @@
     </row>
     <row r="42" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
-        <v>46064</v>
-      </c>
-      <c r="B42" s="10">
-        <v>0.25</v>
-      </c>
-      <c r="C42" s="10">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D42" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="E42" s="10">
-        <v>0.43</v>
-      </c>
-      <c r="F42" s="10">
-        <v>0</v>
-      </c>
-      <c r="G42" s="10">
-        <v>7.0000000000000007E-2</v>
+        <v>46065</v>
+      </c>
+      <c r="B42" s="9">
+        <v>0.26</v>
+      </c>
+      <c r="C42" s="9">
+        <v>0.18</v>
+      </c>
+      <c r="D42" s="9">
+        <v>0.36</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.52</v>
+      </c>
+      <c r="F42" s="9">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="G42" s="9">
+        <v>3.77</v>
       </c>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
@@ -2294,25 +2296,25 @@
     </row>
     <row r="43" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6">
-        <v>46063</v>
-      </c>
-      <c r="B43" s="9">
-        <v>1.03</v>
-      </c>
-      <c r="C43" s="9">
-        <v>0.39</v>
-      </c>
-      <c r="D43" s="9">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="E43" s="9">
-        <v>0.74</v>
-      </c>
-      <c r="F43" s="9">
+        <v>46064</v>
+      </c>
+      <c r="B43" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="C43" s="10">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D43" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="E43" s="10">
+        <v>0.43</v>
+      </c>
+      <c r="F43" s="10">
         <v>0</v>
       </c>
-      <c r="G43" s="9">
-        <v>1.36</v>
+      <c r="G43" s="10">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
@@ -2335,25 +2337,25 @@
     </row>
     <row r="44" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6">
-        <v>46062</v>
-      </c>
-      <c r="B44" s="10">
-        <v>0.72</v>
-      </c>
-      <c r="C44" s="10">
-        <v>0.64</v>
-      </c>
-      <c r="D44" s="10">
-        <v>0.67</v>
-      </c>
-      <c r="E44" s="10">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="F44" s="10">
-        <v>3.59</v>
-      </c>
-      <c r="G44" s="10">
-        <v>4.92</v>
+        <v>46063</v>
+      </c>
+      <c r="B44" s="9">
+        <v>1.03</v>
+      </c>
+      <c r="C44" s="9">
+        <v>0.39</v>
+      </c>
+      <c r="D44" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E44" s="9">
+        <v>0.74</v>
+      </c>
+      <c r="F44" s="9">
+        <v>0</v>
+      </c>
+      <c r="G44" s="9">
+        <v>1.36</v>
       </c>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
@@ -2376,25 +2378,25 @@
     </row>
     <row r="45" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
-        <v>46059</v>
-      </c>
-      <c r="B45" s="9">
-        <v>0</v>
-      </c>
-      <c r="C45" s="9">
-        <v>0</v>
-      </c>
-      <c r="D45" s="9">
-        <v>-0.94</v>
-      </c>
-      <c r="E45" s="9">
-        <v>0.06</v>
-      </c>
-      <c r="F45" s="9">
-        <v>3.23</v>
-      </c>
-      <c r="G45" s="9">
-        <v>3.24</v>
+        <v>46062</v>
+      </c>
+      <c r="B45" s="10">
+        <v>0.72</v>
+      </c>
+      <c r="C45" s="10">
+        <v>0.64</v>
+      </c>
+      <c r="D45" s="10">
+        <v>0.67</v>
+      </c>
+      <c r="E45" s="10">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F45" s="10">
+        <v>3.59</v>
+      </c>
+      <c r="G45" s="10">
+        <v>4.92</v>
       </c>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
@@ -2417,25 +2419,25 @@
     </row>
     <row r="46" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6">
-        <v>46058</v>
-      </c>
-      <c r="B46" s="10">
-        <v>1.82</v>
-      </c>
-      <c r="C46" s="10">
-        <v>1.48</v>
-      </c>
-      <c r="D46" s="10">
-        <v>1.52</v>
-      </c>
-      <c r="E46" s="10">
-        <v>1.38</v>
-      </c>
-      <c r="F46" s="10">
-        <v>-2.68</v>
-      </c>
-      <c r="G46" s="10">
-        <v>3.31</v>
+        <v>46059</v>
+      </c>
+      <c r="B46" s="9">
+        <v>0</v>
+      </c>
+      <c r="C46" s="9">
+        <v>0</v>
+      </c>
+      <c r="D46" s="9">
+        <v>-0.94</v>
+      </c>
+      <c r="E46" s="9">
+        <v>0.06</v>
+      </c>
+      <c r="F46" s="9">
+        <v>3.23</v>
+      </c>
+      <c r="G46" s="9">
+        <v>3.24</v>
       </c>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
@@ -2458,25 +2460,25 @@
     </row>
     <row r="47" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
-        <v>46057</v>
-      </c>
-      <c r="B47" s="9">
-        <v>-0.13</v>
-      </c>
-      <c r="C47" s="9">
-        <v>0.22</v>
-      </c>
-      <c r="D47" s="9">
-        <v>1.51</v>
-      </c>
-      <c r="E47" s="9">
-        <v>0.87</v>
-      </c>
-      <c r="F47" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="G47" s="9">
-        <v>4.21</v>
+        <v>46058</v>
+      </c>
+      <c r="B47" s="10">
+        <v>1.82</v>
+      </c>
+      <c r="C47" s="10">
+        <v>1.48</v>
+      </c>
+      <c r="D47" s="10">
+        <v>1.52</v>
+      </c>
+      <c r="E47" s="10">
+        <v>1.38</v>
+      </c>
+      <c r="F47" s="10">
+        <v>-2.68</v>
+      </c>
+      <c r="G47" s="10">
+        <v>3.31</v>
       </c>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
@@ -2499,25 +2501,25 @@
     </row>
     <row r="48" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
-        <v>46056</v>
-      </c>
-      <c r="B48" s="10">
-        <v>1.18</v>
-      </c>
-      <c r="C48" s="10">
-        <v>1.05</v>
-      </c>
-      <c r="D48" s="10">
-        <v>2.59</v>
-      </c>
-      <c r="E48" s="10">
-        <v>2.04</v>
-      </c>
-      <c r="F48" s="10">
-        <v>4.55</v>
-      </c>
-      <c r="G48" s="10">
-        <v>0</v>
+        <v>46057</v>
+      </c>
+      <c r="B48" s="9">
+        <v>-0.13</v>
+      </c>
+      <c r="C48" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="D48" s="9">
+        <v>1.51</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0.87</v>
+      </c>
+      <c r="F48" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="G48" s="9">
+        <v>4.21</v>
       </c>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
@@ -2540,25 +2542,25 @@
     </row>
     <row r="49" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6">
-        <v>46055</v>
-      </c>
-      <c r="B49" s="9">
-        <v>1.6</v>
-      </c>
-      <c r="C49" s="9">
-        <v>1.7</v>
-      </c>
-      <c r="D49" s="9">
-        <v>1.82</v>
-      </c>
-      <c r="E49" s="9">
+        <v>46056</v>
+      </c>
+      <c r="B49" s="10">
+        <v>1.18</v>
+      </c>
+      <c r="C49" s="10">
         <v>1.05</v>
       </c>
-      <c r="F49" s="9">
-        <v>-0.14000000000000001</v>
-      </c>
-      <c r="G49" s="9">
-        <v>4.97</v>
+      <c r="D49" s="10">
+        <v>2.59</v>
+      </c>
+      <c r="E49" s="10">
+        <v>2.04</v>
+      </c>
+      <c r="F49" s="10">
+        <v>4.55</v>
+      </c>
+      <c r="G49" s="10">
+        <v>0</v>
       </c>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
@@ -2581,25 +2583,25 @@
     </row>
     <row r="50" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6">
-        <v>46054</v>
-      </c>
-      <c r="B50" s="10">
-        <v>0</v>
-      </c>
-      <c r="C50" s="10">
-        <v>0</v>
-      </c>
-      <c r="D50" s="10">
-        <v>0</v>
-      </c>
-      <c r="E50" s="10">
-        <v>0</v>
-      </c>
-      <c r="F50" s="10">
-        <v>1.34</v>
-      </c>
-      <c r="G50" s="10">
-        <v>5.0599999999999996</v>
+        <v>46055</v>
+      </c>
+      <c r="B50" s="9">
+        <v>1.6</v>
+      </c>
+      <c r="C50" s="9">
+        <v>1.7</v>
+      </c>
+      <c r="D50" s="9">
+        <v>1.82</v>
+      </c>
+      <c r="E50" s="9">
+        <v>1.05</v>
+      </c>
+      <c r="F50" s="9">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="G50" s="9">
+        <v>4.97</v>
       </c>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
@@ -2622,25 +2624,25 @@
     </row>
     <row r="51" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6">
-        <v>46052</v>
-      </c>
-      <c r="B51" s="9">
+        <v>46054</v>
+      </c>
+      <c r="B51" s="10">
         <v>0</v>
       </c>
-      <c r="C51" s="9">
+      <c r="C51" s="10">
         <v>0</v>
       </c>
-      <c r="D51" s="9">
-        <v>-0.17</v>
-      </c>
-      <c r="E51" s="9">
-        <v>0.05</v>
-      </c>
-      <c r="F51" s="9">
-        <v>-1.07</v>
-      </c>
-      <c r="G51" s="9">
-        <v>-4</v>
+      <c r="D51" s="10">
+        <v>0</v>
+      </c>
+      <c r="E51" s="10">
+        <v>0</v>
+      </c>
+      <c r="F51" s="10">
+        <v>1.34</v>
+      </c>
+      <c r="G51" s="10">
+        <v>5.0599999999999996</v>
       </c>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
@@ -2663,25 +2665,25 @@
     </row>
     <row r="52" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
-        <v>46051</v>
-      </c>
-      <c r="B52" s="10">
-        <v>-0.12</v>
-      </c>
-      <c r="C52" s="10">
-        <v>0.82</v>
-      </c>
-      <c r="D52" s="10">
-        <v>0.72</v>
-      </c>
-      <c r="E52" s="10">
-        <v>1.33</v>
-      </c>
-      <c r="F52" s="10">
-        <v>1.75</v>
-      </c>
-      <c r="G52" s="10">
-        <v>2</v>
+        <v>46052</v>
+      </c>
+      <c r="B52" s="9">
+        <v>0</v>
+      </c>
+      <c r="C52" s="9">
+        <v>0</v>
+      </c>
+      <c r="D52" s="9">
+        <v>-0.17</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="F52" s="9">
+        <v>-1.07</v>
+      </c>
+      <c r="G52" s="9">
+        <v>-4</v>
       </c>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
@@ -2703,26 +2705,26 @@
       <c r="Y52" s="4"/>
     </row>
     <row r="53" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="7">
-        <v>46050</v>
-      </c>
-      <c r="B53" s="9">
-        <v>1.68</v>
-      </c>
-      <c r="C53" s="9">
-        <v>1.58</v>
-      </c>
-      <c r="D53" s="9">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E53" s="9">
-        <v>1.36</v>
-      </c>
-      <c r="F53" s="9">
-        <v>1.32</v>
-      </c>
-      <c r="G53" s="9">
-        <v>1</v>
+      <c r="A53" s="6">
+        <v>46051</v>
+      </c>
+      <c r="B53" s="10">
+        <v>-0.12</v>
+      </c>
+      <c r="C53" s="10">
+        <v>0.82</v>
+      </c>
+      <c r="D53" s="10">
+        <v>0.72</v>
+      </c>
+      <c r="E53" s="10">
+        <v>1.33</v>
+      </c>
+      <c r="F53" s="10">
+        <v>1.75</v>
+      </c>
+      <c r="G53" s="10">
+        <v>2</v>
       </c>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
@@ -2745,25 +2747,25 @@
     </row>
     <row r="54" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
-        <v>46049</v>
-      </c>
-      <c r="B54" s="10">
-        <v>0.22</v>
-      </c>
-      <c r="C54" s="10">
-        <v>0.64</v>
-      </c>
-      <c r="D54" s="10">
-        <v>-1.7</v>
-      </c>
-      <c r="E54" s="10">
-        <v>-0.99</v>
-      </c>
-      <c r="F54" s="10">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="G54" s="10">
-        <v>5.08</v>
+        <v>46050</v>
+      </c>
+      <c r="B54" s="9">
+        <v>1.68</v>
+      </c>
+      <c r="C54" s="9">
+        <v>1.58</v>
+      </c>
+      <c r="D54" s="9">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E54" s="9">
+        <v>1.36</v>
+      </c>
+      <c r="F54" s="9">
+        <v>1.32</v>
+      </c>
+      <c r="G54" s="9">
+        <v>1</v>
       </c>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
@@ -2785,26 +2787,26 @@
       <c r="Y54" s="4"/>
     </row>
     <row r="55" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="6">
-        <v>46045</v>
-      </c>
-      <c r="B55" s="9">
-        <v>0</v>
-      </c>
-      <c r="C55" s="9">
-        <v>0</v>
-      </c>
-      <c r="D55" s="9">
-        <v>0.3</v>
-      </c>
-      <c r="E55" s="9">
-        <v>0.37</v>
-      </c>
-      <c r="F55" s="9">
-        <v>-2.25</v>
-      </c>
-      <c r="G55" s="9">
-        <v>4.72</v>
+      <c r="A55" s="7">
+        <v>46049</v>
+      </c>
+      <c r="B55" s="10">
+        <v>0.22</v>
+      </c>
+      <c r="C55" s="10">
+        <v>0.64</v>
+      </c>
+      <c r="D55" s="10">
+        <v>-1.7</v>
+      </c>
+      <c r="E55" s="10">
+        <v>-0.99</v>
+      </c>
+      <c r="F55" s="10">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="G55" s="10">
+        <v>5.08</v>
       </c>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
@@ -2827,25 +2829,25 @@
     </row>
     <row r="56" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6">
-        <v>46044</v>
-      </c>
-      <c r="B56" s="10">
-        <v>-1.44</v>
-      </c>
-      <c r="C56" s="10">
-        <v>-2.2599999999999998</v>
-      </c>
-      <c r="D56" s="10">
-        <v>-1.26</v>
-      </c>
-      <c r="E56" s="10">
-        <v>-0.79</v>
-      </c>
-      <c r="F56" s="10">
-        <v>4.37</v>
-      </c>
-      <c r="G56" s="10">
+        <v>46045</v>
+      </c>
+      <c r="B56" s="9">
         <v>0</v>
+      </c>
+      <c r="C56" s="9">
+        <v>0</v>
+      </c>
+      <c r="D56" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="E56" s="9">
+        <v>0.37</v>
+      </c>
+      <c r="F56" s="9">
+        <v>-2.25</v>
+      </c>
+      <c r="G56" s="9">
+        <v>4.72</v>
       </c>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
@@ -2868,25 +2870,25 @@
     </row>
     <row r="57" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6">
-        <v>46043</v>
-      </c>
-      <c r="B57" s="9">
-        <v>1.31</v>
-      </c>
-      <c r="C57" s="9">
-        <v>-0.9</v>
-      </c>
-      <c r="D57" s="9">
-        <v>-1.75</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-2.0099999999999998</v>
-      </c>
-      <c r="F57" s="9">
-        <v>0.23</v>
-      </c>
-      <c r="G57" s="9">
-        <v>-3.64</v>
+        <v>46044</v>
+      </c>
+      <c r="B57" s="10">
+        <v>-1.44</v>
+      </c>
+      <c r="C57" s="10">
+        <v>-2.2599999999999998</v>
+      </c>
+      <c r="D57" s="10">
+        <v>-1.26</v>
+      </c>
+      <c r="E57" s="10">
+        <v>-0.79</v>
+      </c>
+      <c r="F57" s="10">
+        <v>4.37</v>
+      </c>
+      <c r="G57" s="10">
+        <v>0</v>
       </c>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
@@ -2908,24 +2910,26 @@
       <c r="Y57" s="4"/>
     </row>
     <row r="58" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="7">
-        <v>46042</v>
-      </c>
-      <c r="B58" s="10">
-        <v>1.23</v>
-      </c>
-      <c r="C58" s="10">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="D58" s="10">
-        <v>0.43</v>
-      </c>
-      <c r="E58" s="10">
-        <v>-0.03</v>
-      </c>
-      <c r="F58" s="4"/>
-      <c r="G58" s="2">
-        <v>4.87</v>
+      <c r="A58" s="6">
+        <v>46043</v>
+      </c>
+      <c r="B58" s="9">
+        <v>1.31</v>
+      </c>
+      <c r="C58" s="9">
+        <v>-0.9</v>
+      </c>
+      <c r="D58" s="9">
+        <v>-1.75</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-2.0099999999999998</v>
+      </c>
+      <c r="F58" s="9">
+        <v>0.23</v>
+      </c>
+      <c r="G58" s="9">
+        <v>-3.64</v>
       </c>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
@@ -2947,24 +2951,24 @@
       <c r="Y58" s="4"/>
     </row>
     <row r="59" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="6">
-        <v>46041</v>
-      </c>
-      <c r="B59" s="9">
-        <v>0.15</v>
-      </c>
-      <c r="C59" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="D59" s="9">
-        <v>-0.16</v>
-      </c>
-      <c r="E59" s="9">
-        <v>0.03</v>
+      <c r="A59" s="7">
+        <v>46042</v>
+      </c>
+      <c r="B59" s="10">
+        <v>1.23</v>
+      </c>
+      <c r="C59" s="10">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="D59" s="10">
+        <v>0.43</v>
+      </c>
+      <c r="E59" s="10">
+        <v>-0.03</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="2">
-        <v>1.73</v>
+        <v>4.87</v>
       </c>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
@@ -2987,23 +2991,23 @@
     </row>
     <row r="60" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6">
-        <v>46038</v>
-      </c>
-      <c r="B60" s="10">
-        <v>0</v>
-      </c>
-      <c r="C60" s="10">
-        <v>0</v>
-      </c>
-      <c r="D60" s="10">
-        <v>-0.73</v>
-      </c>
-      <c r="E60" s="10">
-        <v>-0.77</v>
+        <v>46041</v>
+      </c>
+      <c r="B60" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="C60" s="9">
+        <v>0.04</v>
+      </c>
+      <c r="D60" s="9">
+        <v>-0.16</v>
+      </c>
+      <c r="E60" s="9">
+        <v>0.03</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="2">
-        <v>-3.21</v>
+        <v>1.73</v>
       </c>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
@@ -3026,23 +3030,23 @@
     </row>
     <row r="61" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6">
-        <v>46036</v>
-      </c>
-      <c r="B61" s="9">
-        <v>-1.56</v>
-      </c>
-      <c r="C61" s="9">
-        <v>-0.98</v>
-      </c>
-      <c r="D61" s="9">
-        <v>-1.47</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-0.86</v>
+        <v>46038</v>
+      </c>
+      <c r="B61" s="10">
+        <v>0</v>
+      </c>
+      <c r="C61" s="10">
+        <v>0</v>
+      </c>
+      <c r="D61" s="10">
+        <v>-0.73</v>
+      </c>
+      <c r="E61" s="10">
+        <v>-0.77</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="2">
-        <v>-2.66</v>
+        <v>-3.21</v>
       </c>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
@@ -3065,23 +3069,23 @@
     </row>
     <row r="62" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
-        <v>46035</v>
-      </c>
-      <c r="B62" s="10">
-        <v>-1.78</v>
-      </c>
-      <c r="C62" s="10">
-        <v>-1.96</v>
-      </c>
-      <c r="D62" s="10">
-        <v>-1.91</v>
-      </c>
-      <c r="E62" s="10">
-        <v>-1.21</v>
+        <v>46036</v>
+      </c>
+      <c r="B62" s="9">
+        <v>-1.56</v>
+      </c>
+      <c r="C62" s="9">
+        <v>-0.98</v>
+      </c>
+      <c r="D62" s="9">
+        <v>-1.47</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-0.86</v>
       </c>
       <c r="F62" s="4"/>
       <c r="G62" s="2">
-        <v>-2.9</v>
+        <v>-2.66</v>
       </c>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
@@ -3103,24 +3107,24 @@
       <c r="Y62" s="4"/>
     </row>
     <row r="63" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="7">
-        <v>46034</v>
-      </c>
-      <c r="B63" s="9">
+      <c r="A63" s="6">
+        <v>46035</v>
+      </c>
+      <c r="B63" s="10">
+        <v>-1.78</v>
+      </c>
+      <c r="C63" s="10">
+        <v>-1.96</v>
+      </c>
+      <c r="D63" s="10">
+        <v>-1.91</v>
+      </c>
+      <c r="E63" s="10">
         <v>-1.21</v>
-      </c>
-      <c r="C63" s="9">
-        <v>-1.64</v>
-      </c>
-      <c r="D63" s="9">
-        <v>-1.67</v>
-      </c>
-      <c r="E63" s="9">
-        <v>-1.06</v>
       </c>
       <c r="F63" s="4"/>
       <c r="G63" s="2">
-        <v>5.85</v>
+        <v>-2.9</v>
       </c>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
@@ -3142,24 +3146,24 @@
       <c r="Y63" s="4"/>
     </row>
     <row r="64" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="6">
-        <v>46031</v>
-      </c>
-      <c r="B64" s="10">
-        <v>0</v>
-      </c>
-      <c r="C64" s="10">
-        <v>0</v>
-      </c>
-      <c r="D64" s="10">
-        <v>-0.2</v>
-      </c>
-      <c r="E64" s="10">
-        <v>-1.52</v>
+      <c r="A64" s="7">
+        <v>46034</v>
+      </c>
+      <c r="B64" s="9">
+        <v>-1.21</v>
+      </c>
+      <c r="C64" s="9">
+        <v>-1.64</v>
+      </c>
+      <c r="D64" s="9">
+        <v>-1.67</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-1.06</v>
       </c>
       <c r="F64" s="4"/>
       <c r="G64" s="2">
-        <v>1.81</v>
+        <v>5.85</v>
       </c>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
@@ -3182,23 +3186,23 @@
     </row>
     <row r="65" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6">
-        <v>46030</v>
-      </c>
-      <c r="B65" s="9">
-        <v>0.9</v>
-      </c>
-      <c r="C65" s="9">
-        <v>0.88</v>
-      </c>
-      <c r="D65" s="9">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="E65" s="9">
-        <v>0.99</v>
+        <v>46031</v>
+      </c>
+      <c r="B65" s="10">
+        <v>0</v>
+      </c>
+      <c r="C65" s="10">
+        <v>0</v>
+      </c>
+      <c r="D65" s="10">
+        <v>-0.2</v>
+      </c>
+      <c r="E65" s="10">
+        <v>-1.52</v>
       </c>
       <c r="F65" s="4"/>
       <c r="G65" s="2">
-        <v>3</v>
+        <v>1.81</v>
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
@@ -3221,23 +3225,23 @@
     </row>
     <row r="66" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6">
-        <v>46029</v>
-      </c>
-      <c r="B66" s="10">
-        <v>-0.06</v>
-      </c>
-      <c r="C66" s="10">
-        <v>-0.11</v>
-      </c>
-      <c r="D66" s="10">
-        <v>-1.03</v>
-      </c>
-      <c r="E66" s="10">
-        <v>0.18</v>
+        <v>46030</v>
+      </c>
+      <c r="B66" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="C66" s="9">
+        <v>0.88</v>
+      </c>
+      <c r="D66" s="9">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="E66" s="9">
+        <v>0.99</v>
       </c>
       <c r="F66" s="4"/>
       <c r="G66" s="2">
-        <v>0.19</v>
+        <v>3</v>
       </c>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
@@ -3260,23 +3264,23 @@
     </row>
     <row r="67" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6">
-        <v>46028</v>
-      </c>
-      <c r="B67" s="9">
-        <v>-0.78</v>
-      </c>
-      <c r="C67" s="9">
-        <v>0.84</v>
-      </c>
-      <c r="D67" s="9">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="E67" s="9">
-        <v>0.12</v>
+        <v>46029</v>
+      </c>
+      <c r="B67" s="10">
+        <v>-0.06</v>
+      </c>
+      <c r="C67" s="10">
+        <v>-0.11</v>
+      </c>
+      <c r="D67" s="10">
+        <v>-1.03</v>
+      </c>
+      <c r="E67" s="10">
+        <v>0.18</v>
       </c>
       <c r="F67" s="4"/>
       <c r="G67" s="2">
-        <v>6</v>
+        <v>0.19</v>
       </c>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
@@ -3298,24 +3302,24 @@
       <c r="Y67" s="4"/>
     </row>
     <row r="68" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="7">
-        <v>46027</v>
-      </c>
-      <c r="B68" s="10">
-        <v>0</v>
-      </c>
-      <c r="C68" s="10">
-        <v>-0.25</v>
-      </c>
-      <c r="D68" s="10">
-        <v>0.09</v>
-      </c>
-      <c r="E68" s="10">
-        <v>0</v>
+      <c r="A68" s="6">
+        <v>46028</v>
+      </c>
+      <c r="B68" s="9">
+        <v>-0.78</v>
+      </c>
+      <c r="C68" s="9">
+        <v>0.84</v>
+      </c>
+      <c r="D68" s="9">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E68" s="9">
+        <v>0.12</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="2">
-        <v>1.34</v>
+        <v>6</v>
       </c>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
@@ -3337,24 +3341,24 @@
       <c r="Y68" s="4"/>
     </row>
     <row r="69" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="6">
-        <v>46024</v>
-      </c>
-      <c r="B69" s="9">
+      <c r="A69" s="7">
+        <v>46027</v>
+      </c>
+      <c r="B69" s="10">
         <v>0</v>
       </c>
-      <c r="C69" s="9">
+      <c r="C69" s="10">
+        <v>-0.25</v>
+      </c>
+      <c r="D69" s="10">
+        <v>0.09</v>
+      </c>
+      <c r="E69" s="10">
         <v>0</v>
-      </c>
-      <c r="D69" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-0.02</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="2">
-        <v>-0.8</v>
+        <v>1.34</v>
       </c>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
@@ -3377,23 +3381,23 @@
     </row>
     <row r="70" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6">
-        <v>46023</v>
-      </c>
-      <c r="B70" s="10">
-        <v>1.18</v>
-      </c>
-      <c r="C70" s="10">
-        <v>1.17</v>
-      </c>
-      <c r="D70" s="10">
-        <v>1.52</v>
-      </c>
-      <c r="E70" s="10">
-        <v>0.36</v>
+        <v>46024</v>
+      </c>
+      <c r="B70" s="9">
+        <v>0</v>
+      </c>
+      <c r="C70" s="9">
+        <v>0</v>
+      </c>
+      <c r="D70" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-0.02</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="2">
-        <v>0.53</v>
+        <v>-0.8</v>
       </c>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
@@ -3416,23 +3420,23 @@
     </row>
     <row r="71" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6">
-        <v>46022</v>
-      </c>
-      <c r="B71" s="9">
-        <v>-1.1399999999999999</v>
-      </c>
-      <c r="C71" s="9">
-        <v>-0.42</v>
-      </c>
-      <c r="D71" s="9">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="E71" s="9">
-        <v>0.03</v>
+        <v>46023</v>
+      </c>
+      <c r="B71" s="10">
+        <v>1.18</v>
+      </c>
+      <c r="C71" s="10">
+        <v>1.17</v>
+      </c>
+      <c r="D71" s="10">
+        <v>1.52</v>
+      </c>
+      <c r="E71" s="10">
+        <v>0.36</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="2">
-        <v>4.12</v>
+        <v>0.53</v>
       </c>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
@@ -3455,23 +3459,23 @@
     </row>
     <row r="72" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6">
-        <v>46021</v>
-      </c>
-      <c r="B72" s="10">
-        <v>1.19</v>
-      </c>
-      <c r="C72" s="10">
-        <v>1.25</v>
-      </c>
-      <c r="D72" s="10">
-        <v>0.12</v>
-      </c>
-      <c r="E72" s="10">
-        <v>1.04</v>
+        <v>46022</v>
+      </c>
+      <c r="B72" s="9">
+        <v>-1.1399999999999999</v>
+      </c>
+      <c r="C72" s="9">
+        <v>-0.42</v>
+      </c>
+      <c r="D72" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E72" s="9">
+        <v>0.03</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="2">
-        <v>1.38</v>
+        <v>4.12</v>
       </c>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
@@ -3493,24 +3497,24 @@
       <c r="Y72" s="4"/>
     </row>
     <row r="73" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="7">
-        <v>46020</v>
-      </c>
-      <c r="B73" s="9">
+      <c r="A73" s="6">
+        <v>46021</v>
+      </c>
+      <c r="B73" s="10">
+        <v>1.19</v>
+      </c>
+      <c r="C73" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="D73" s="10">
         <v>0.12</v>
       </c>
-      <c r="C73" s="9">
-        <v>0.12</v>
-      </c>
-      <c r="D73" s="9">
-        <v>0.73</v>
-      </c>
-      <c r="E73" s="9">
-        <v>-0.1</v>
+      <c r="E73" s="10">
+        <v>1.04</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="2">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
@@ -3532,20 +3536,20 @@
       <c r="Y73" s="4"/>
     </row>
     <row r="74" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="6">
-        <v>46017</v>
-      </c>
-      <c r="B74" s="10">
-        <v>0</v>
-      </c>
-      <c r="C74" s="10">
-        <v>0</v>
-      </c>
-      <c r="D74" s="10">
-        <v>0.42</v>
-      </c>
-      <c r="E74" s="10">
-        <v>0.66</v>
+      <c r="A74" s="7">
+        <v>46020</v>
+      </c>
+      <c r="B74" s="9">
+        <v>0.12</v>
+      </c>
+      <c r="C74" s="9">
+        <v>0.12</v>
+      </c>
+      <c r="D74" s="9">
+        <v>0.73</v>
+      </c>
+      <c r="E74" s="9">
+        <v>-0.1</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="2">
@@ -3572,19 +3576,19 @@
     </row>
     <row r="75" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6">
-        <v>46015</v>
-      </c>
-      <c r="B75" s="9">
-        <v>1.17</v>
-      </c>
-      <c r="C75" s="9">
-        <v>0.94</v>
-      </c>
-      <c r="D75" s="9">
-        <v>0.95</v>
-      </c>
-      <c r="E75" s="9">
-        <v>1.51</v>
+        <v>46017</v>
+      </c>
+      <c r="B75" s="10">
+        <v>0</v>
+      </c>
+      <c r="C75" s="10">
+        <v>0</v>
+      </c>
+      <c r="D75" s="10">
+        <v>0.42</v>
+      </c>
+      <c r="E75" s="10">
+        <v>0.66</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="2">
@@ -3611,23 +3615,23 @@
     </row>
     <row r="76" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6">
-        <v>46014</v>
-      </c>
-      <c r="B76" s="10">
-        <v>0.52</v>
-      </c>
-      <c r="C76" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="D76" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="E76" s="10">
-        <v>0.34</v>
+        <v>46015</v>
+      </c>
+      <c r="B76" s="9">
+        <v>1.17</v>
+      </c>
+      <c r="C76" s="9">
+        <v>0.94</v>
+      </c>
+      <c r="D76" s="9">
+        <v>0.95</v>
+      </c>
+      <c r="E76" s="9">
+        <v>1.51</v>
       </c>
       <c r="F76" s="4"/>
       <c r="G76" s="2">
-        <v>-1.23</v>
+        <v>0</v>
       </c>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
@@ -3650,23 +3654,23 @@
     </row>
     <row r="77" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6">
-        <v>46013</v>
-      </c>
-      <c r="B77" s="9">
-        <v>0.79</v>
-      </c>
-      <c r="C77" s="9">
-        <v>0.73</v>
-      </c>
-      <c r="D77" s="9">
-        <v>0.83</v>
-      </c>
-      <c r="E77" s="9">
-        <v>0.74</v>
+        <v>46014</v>
+      </c>
+      <c r="B77" s="10">
+        <v>0.52</v>
+      </c>
+      <c r="C77" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="D77" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="E77" s="10">
+        <v>0.34</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="2">
-        <v>1.18</v>
+        <v>-1.23</v>
       </c>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
@@ -3688,24 +3692,24 @@
       <c r="Y77" s="4"/>
     </row>
     <row r="78" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="7">
-        <v>46010</v>
-      </c>
-      <c r="B78" s="10">
-        <v>0</v>
-      </c>
-      <c r="C78" s="10">
-        <v>0</v>
-      </c>
-      <c r="D78" s="10">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="E78" s="10">
-        <v>0.97</v>
+      <c r="A78" s="6">
+        <v>46013</v>
+      </c>
+      <c r="B78" s="9">
+        <v>0.79</v>
+      </c>
+      <c r="C78" s="9">
+        <v>0.73</v>
+      </c>
+      <c r="D78" s="9">
+        <v>0.83</v>
+      </c>
+      <c r="E78" s="9">
+        <v>0.74</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="2">
-        <v>4.7699999999999996</v>
+        <v>1.18</v>
       </c>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
@@ -3727,24 +3731,24 @@
       <c r="Y78" s="4"/>
     </row>
     <row r="79" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="6">
-        <v>46009</v>
-      </c>
-      <c r="B79" s="9">
+      <c r="A79" s="7">
+        <v>46010</v>
+      </c>
+      <c r="B79" s="10">
+        <v>0</v>
+      </c>
+      <c r="C79" s="10">
+        <v>0</v>
+      </c>
+      <c r="D79" s="10">
         <v>1.1100000000000001</v>
       </c>
-      <c r="C79" s="9">
-        <v>1.3</v>
-      </c>
-      <c r="D79" s="9">
-        <v>0.67</v>
-      </c>
-      <c r="E79" s="9">
-        <v>1.1200000000000001</v>
+      <c r="E79" s="10">
+        <v>0.97</v>
       </c>
       <c r="F79" s="4"/>
       <c r="G79" s="2">
-        <v>1.1299999999999999</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
@@ -3767,23 +3771,23 @@
     </row>
     <row r="80" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6">
-        <v>46008</v>
-      </c>
-      <c r="B80" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="C80" s="10">
-        <v>0.87</v>
-      </c>
-      <c r="D80" s="10">
-        <v>0.42</v>
-      </c>
-      <c r="E80" s="10">
-        <v>0.33</v>
+        <v>46009</v>
+      </c>
+      <c r="B80" s="9">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="C80" s="9">
+        <v>1.3</v>
+      </c>
+      <c r="D80" s="9">
+        <v>0.67</v>
+      </c>
+      <c r="E80" s="9">
+        <v>1.1200000000000001</v>
       </c>
       <c r="F80" s="4"/>
       <c r="G80" s="2">
-        <v>0</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
@@ -3806,19 +3810,19 @@
     </row>
     <row r="81" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6">
-        <v>46007</v>
-      </c>
-      <c r="B81" s="9">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="C81" s="9">
-        <v>1.9</v>
-      </c>
-      <c r="D81" s="9">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="E81" s="9">
-        <v>0.71</v>
+        <v>46008</v>
+      </c>
+      <c r="B81" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="C81" s="10">
+        <v>0.87</v>
+      </c>
+      <c r="D81" s="10">
+        <v>0.42</v>
+      </c>
+      <c r="E81" s="10">
+        <v>0.33</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="2">
@@ -3845,23 +3849,23 @@
     </row>
     <row r="82" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6">
-        <v>46006</v>
-      </c>
-      <c r="B82" s="10">
-        <v>0.51</v>
-      </c>
-      <c r="C82" s="10">
-        <v>0.43</v>
-      </c>
-      <c r="D82" s="10">
-        <v>1.08</v>
-      </c>
-      <c r="E82" s="10">
-        <v>0.27</v>
+        <v>46007</v>
+      </c>
+      <c r="B82" s="9">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="C82" s="9">
+        <v>1.9</v>
+      </c>
+      <c r="D82" s="9">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="E82" s="9">
+        <v>0.71</v>
       </c>
       <c r="F82" s="4"/>
       <c r="G82" s="2">
-        <v>-6.13</v>
+        <v>0</v>
       </c>
       <c r="H82" s="4"/>
       <c r="I82" s="4"/>
@@ -3884,23 +3888,23 @@
     </row>
     <row r="83" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6">
-        <v>46003</v>
-      </c>
-      <c r="B83" s="9">
-        <v>0</v>
-      </c>
-      <c r="C83" s="9">
-        <v>0</v>
-      </c>
-      <c r="D83" s="9">
-        <v>1.03</v>
-      </c>
-      <c r="E83" s="9">
-        <v>1.1200000000000001</v>
+        <v>46006</v>
+      </c>
+      <c r="B83" s="10">
+        <v>0.51</v>
+      </c>
+      <c r="C83" s="10">
+        <v>0.43</v>
+      </c>
+      <c r="D83" s="10">
+        <v>1.08</v>
+      </c>
+      <c r="E83" s="10">
+        <v>0.27</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="2">
-        <v>5.15</v>
+        <v>-6.13</v>
       </c>
       <c r="H83" s="4"/>
       <c r="I83" s="4"/>
@@ -3923,23 +3927,23 @@
     </row>
     <row r="84" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6">
-        <v>46002</v>
-      </c>
-      <c r="B84" s="10">
-        <v>-1.38</v>
-      </c>
-      <c r="C84" s="10">
-        <v>-1.21</v>
-      </c>
-      <c r="D84" s="10">
-        <v>-1.6</v>
-      </c>
-      <c r="E84" s="10">
-        <v>-1.69</v>
+        <v>46003</v>
+      </c>
+      <c r="B84" s="9">
+        <v>0</v>
+      </c>
+      <c r="C84" s="9">
+        <v>0</v>
+      </c>
+      <c r="D84" s="9">
+        <v>1.03</v>
+      </c>
+      <c r="E84" s="9">
+        <v>1.1200000000000001</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="2">
-        <v>0.87</v>
+        <v>5.15</v>
       </c>
       <c r="H84" s="4"/>
       <c r="I84" s="4"/>
@@ -3962,23 +3966,23 @@
     </row>
     <row r="85" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6">
-        <v>46001</v>
-      </c>
-      <c r="B85" s="9">
-        <v>-0.14000000000000001</v>
-      </c>
-      <c r="C85" s="9">
-        <v>-0.23</v>
-      </c>
-      <c r="D85" s="9">
-        <v>-0.71</v>
-      </c>
-      <c r="E85" s="9">
-        <v>-0.06</v>
+        <v>46002</v>
+      </c>
+      <c r="B85" s="10">
+        <v>-1.38</v>
+      </c>
+      <c r="C85" s="10">
+        <v>-1.21</v>
+      </c>
+      <c r="D85" s="10">
+        <v>-1.6</v>
+      </c>
+      <c r="E85" s="10">
+        <v>-1.69</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="2">
-        <v>1.43</v>
+        <v>0.87</v>
       </c>
       <c r="H85" s="4"/>
       <c r="I85" s="4"/>
@@ -4001,23 +4005,23 @@
     </row>
     <row r="86" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6">
-        <v>46000</v>
-      </c>
-      <c r="B86" s="10">
-        <v>-1.87</v>
-      </c>
-      <c r="C86" s="10">
-        <v>0.98</v>
-      </c>
-      <c r="D86" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="E86" s="10">
-        <v>1.39</v>
+        <v>46001</v>
+      </c>
+      <c r="B86" s="9">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="C86" s="9">
+        <v>-0.23</v>
+      </c>
+      <c r="D86" s="9">
+        <v>-0.71</v>
+      </c>
+      <c r="E86" s="9">
+        <v>-0.06</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="2">
-        <v>-1.03</v>
+        <v>1.43</v>
       </c>
       <c r="H86" s="4"/>
       <c r="I86" s="4"/>
@@ -4040,23 +4044,23 @@
     </row>
     <row r="87" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6">
-        <v>45999</v>
-      </c>
-      <c r="B87" s="9">
-        <v>-0.36</v>
-      </c>
-      <c r="C87" s="9">
-        <v>-0.36</v>
-      </c>
-      <c r="D87" s="9">
-        <v>-0.03</v>
-      </c>
-      <c r="E87" s="9">
-        <v>0.68</v>
+        <v>46000</v>
+      </c>
+      <c r="B87" s="10">
+        <v>-1.87</v>
+      </c>
+      <c r="C87" s="10">
+        <v>0.98</v>
+      </c>
+      <c r="D87" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="E87" s="10">
+        <v>1.39</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="2">
-        <v>7.09</v>
+        <v>-1.03</v>
       </c>
       <c r="H87" s="4"/>
       <c r="I87" s="4"/>
@@ -4079,23 +4083,23 @@
     </row>
     <row r="88" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
-        <v>45996</v>
-      </c>
-      <c r="B88" s="10">
-        <v>0</v>
-      </c>
-      <c r="C88" s="10">
-        <v>0</v>
-      </c>
-      <c r="D88" s="10">
-        <v>0.33</v>
-      </c>
-      <c r="E88" s="10">
-        <v>-1.53</v>
+        <v>45999</v>
+      </c>
+      <c r="B88" s="9">
+        <v>-0.36</v>
+      </c>
+      <c r="C88" s="9">
+        <v>-0.36</v>
+      </c>
+      <c r="D88" s="9">
+        <v>-0.03</v>
+      </c>
+      <c r="E88" s="9">
+        <v>0.68</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="2">
-        <v>3.39</v>
+        <v>7.09</v>
       </c>
       <c r="H88" s="4"/>
       <c r="I88" s="4"/>
@@ -4118,23 +4122,23 @@
     </row>
     <row r="89" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
-        <v>45995</v>
-      </c>
-      <c r="B89" s="9">
-        <v>-0.7</v>
-      </c>
-      <c r="C89" s="9">
-        <v>-0.7</v>
-      </c>
-      <c r="D89" s="9">
-        <v>1.43</v>
-      </c>
-      <c r="E89" s="9">
-        <v>1.06</v>
+        <v>45996</v>
+      </c>
+      <c r="B89" s="10">
+        <v>0</v>
+      </c>
+      <c r="C89" s="10">
+        <v>0</v>
+      </c>
+      <c r="D89" s="10">
+        <v>0.33</v>
+      </c>
+      <c r="E89" s="10">
+        <v>-1.53</v>
       </c>
       <c r="F89" s="4"/>
       <c r="G89" s="2">
-        <v>1.64</v>
+        <v>3.39</v>
       </c>
       <c r="H89" s="4"/>
       <c r="I89" s="4"/>
@@ -4157,23 +4161,23 @@
     </row>
     <row r="90" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
-        <v>45994</v>
-      </c>
-      <c r="B90" s="10">
-        <v>0.06</v>
-      </c>
-      <c r="C90" s="10">
-        <v>0.06</v>
+        <v>45995</v>
+      </c>
+      <c r="B90" s="9">
+        <v>-0.7</v>
+      </c>
+      <c r="C90" s="9">
+        <v>-0.7</v>
       </c>
       <c r="D90" s="9">
-        <v>0.09</v>
-      </c>
-      <c r="E90" s="10">
-        <v>-0.16</v>
+        <v>1.43</v>
+      </c>
+      <c r="E90" s="9">
+        <v>1.06</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="2">
-        <v>2.29</v>
+        <v>1.64</v>
       </c>
       <c r="H90" s="4"/>
       <c r="I90" s="4"/>
@@ -4196,23 +4200,23 @@
     </row>
     <row r="91" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
-        <v>45993</v>
-      </c>
-      <c r="B91" s="9">
-        <v>1.28</v>
+        <v>45994</v>
+      </c>
+      <c r="B91" s="10">
+        <v>0.06</v>
       </c>
       <c r="C91" s="10">
-        <v>1.18</v>
+        <v>0.06</v>
       </c>
       <c r="D91" s="9">
-        <v>0.82</v>
+        <v>0.09</v>
       </c>
       <c r="E91" s="10">
-        <v>0.68</v>
+        <v>-0.16</v>
       </c>
       <c r="F91" s="4"/>
       <c r="G91" s="2">
-        <v>5.25</v>
+        <v>2.29</v>
       </c>
       <c r="H91" s="4"/>
       <c r="I91" s="4"/>
@@ -4235,23 +4239,23 @@
     </row>
     <row r="92" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
-        <v>45992</v>
-      </c>
-      <c r="B92" s="10">
-        <v>0.76</v>
+        <v>45993</v>
+      </c>
+      <c r="B92" s="9">
+        <v>1.28</v>
       </c>
       <c r="C92" s="10">
-        <v>0.65</v>
-      </c>
-      <c r="D92" s="10">
-        <v>0.74</v>
-      </c>
-      <c r="E92" s="9">
-        <v>-0.38</v>
+        <v>1.18</v>
+      </c>
+      <c r="D92" s="9">
+        <v>0.82</v>
+      </c>
+      <c r="E92" s="10">
+        <v>0.68</v>
       </c>
       <c r="F92" s="4"/>
       <c r="G92" s="2">
-        <v>-0.08</v>
+        <v>5.25</v>
       </c>
       <c r="H92" s="4"/>
       <c r="I92" s="4"/>
@@ -4274,23 +4278,23 @@
     </row>
     <row r="93" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B93" s="10">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="C93" s="10">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="D93" s="10">
-        <v>0.97</v>
+        <v>0.74</v>
       </c>
       <c r="E93" s="9">
-        <v>0.98</v>
+        <v>-0.38</v>
       </c>
       <c r="F93" s="4"/>
       <c r="G93" s="2">
-        <v>0.83</v>
+        <v>-0.08</v>
       </c>
       <c r="H93" s="4"/>
       <c r="I93" s="4"/>
@@ -4313,23 +4317,23 @@
     </row>
     <row r="94" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="B94" s="10">
-        <v>-1.1599999999999999</v>
+        <v>0</v>
       </c>
       <c r="C94" s="10">
-        <v>-1.41</v>
+        <v>0</v>
       </c>
       <c r="D94" s="10">
-        <v>-1.88</v>
+        <v>0.97</v>
       </c>
       <c r="E94" s="9">
-        <v>-1.31</v>
+        <v>0.98</v>
       </c>
       <c r="F94" s="4"/>
       <c r="G94" s="2">
-        <v>2.7</v>
+        <v>0.83</v>
       </c>
       <c r="H94" s="4"/>
       <c r="I94" s="4"/>
@@ -4352,23 +4356,23 @@
     </row>
     <row r="95" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
-        <v>45987</v>
+        <v>45988</v>
       </c>
       <c r="B95" s="10">
-        <v>-1.1399999999999999</v>
+        <v>-1.1599999999999999</v>
       </c>
       <c r="C95" s="10">
-        <v>-1.06</v>
+        <v>-1.41</v>
       </c>
       <c r="D95" s="10">
-        <v>-0.32</v>
+        <v>-1.88</v>
       </c>
       <c r="E95" s="9">
-        <v>-0.42</v>
+        <v>-1.31</v>
       </c>
       <c r="F95" s="4"/>
       <c r="G95" s="2">
-        <v>-3.03</v>
+        <v>2.7</v>
       </c>
       <c r="H95" s="4"/>
       <c r="I95" s="4"/>
@@ -4391,23 +4395,23 @@
     </row>
     <row r="96" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B96" s="10">
-        <v>1.79</v>
+        <v>-1.1399999999999999</v>
       </c>
       <c r="C96" s="10">
-        <v>1.26</v>
+        <v>-1.06</v>
       </c>
       <c r="D96" s="10">
-        <v>1.31</v>
+        <v>-0.32</v>
       </c>
       <c r="E96" s="9">
-        <v>0.56999999999999995</v>
+        <v>-0.42</v>
       </c>
       <c r="F96" s="4"/>
       <c r="G96" s="2">
-        <v>1.1100000000000001</v>
+        <v>-3.03</v>
       </c>
       <c r="H96" s="4"/>
       <c r="I96" s="4"/>
@@ -4430,23 +4434,23 @@
     </row>
     <row r="97" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B97" s="10">
-        <v>0.23</v>
+        <v>1.79</v>
       </c>
       <c r="C97" s="10">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="D97" s="10">
-        <v>0.54</v>
+        <v>1.31</v>
       </c>
       <c r="E97" s="9">
-        <v>0.42</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="F97" s="4"/>
       <c r="G97" s="2">
-        <v>4.3499999999999996</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="H97" s="4"/>
       <c r="I97" s="4"/>
@@ -4469,23 +4473,23 @@
     </row>
     <row r="98" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B98" s="10">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="C98" s="10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="D98" s="10">
-        <v>-1.3</v>
+        <v>0.54</v>
       </c>
       <c r="E98" s="9">
-        <v>-0.93</v>
+        <v>0.42</v>
       </c>
       <c r="F98" s="4"/>
       <c r="G98" s="2">
-        <v>1.98</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="H98" s="4"/>
       <c r="I98" s="4"/>
@@ -4508,23 +4512,23 @@
     </row>
     <row r="99" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B99" s="10">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C99" s="10">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="D99" s="10">
-        <v>1.06</v>
+        <v>-1.3</v>
       </c>
       <c r="E99" s="9">
-        <v>-0.17</v>
+        <v>-0.93</v>
       </c>
       <c r="F99" s="4"/>
       <c r="G99" s="2">
-        <v>4.55</v>
+        <v>1.98</v>
       </c>
       <c r="H99" s="4"/>
       <c r="I99" s="4"/>
@@ -4547,23 +4551,23 @@
     </row>
     <row r="100" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B100" s="10">
-        <v>-0.66</v>
+        <v>0.5</v>
       </c>
       <c r="C100" s="10">
-        <v>-0.15</v>
+        <v>0.86</v>
       </c>
       <c r="D100" s="10">
-        <v>-0.5</v>
+        <v>1.06</v>
       </c>
       <c r="E100" s="9">
-        <v>0.01</v>
+        <v>-0.17</v>
       </c>
       <c r="F100" s="4"/>
       <c r="G100" s="2">
-        <v>1.77</v>
+        <v>4.55</v>
       </c>
       <c r="H100" s="4"/>
       <c r="I100" s="4"/>
@@ -4586,23 +4590,23 @@
     </row>
     <row r="101" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B101" s="10">
-        <v>1.62</v>
+        <v>-0.66</v>
       </c>
       <c r="C101" s="10">
-        <v>1.9</v>
+        <v>-0.15</v>
       </c>
       <c r="D101" s="10">
-        <v>1.75</v>
+        <v>-0.5</v>
       </c>
       <c r="E101" s="9">
-        <v>0.6</v>
+        <v>0.01</v>
       </c>
       <c r="F101" s="4"/>
       <c r="G101" s="2">
-        <v>-6.56</v>
+        <v>1.77</v>
       </c>
       <c r="H101" s="4"/>
       <c r="I101" s="4"/>
@@ -4625,23 +4629,23 @@
     </row>
     <row r="102" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B102" s="10">
-        <v>-0.12</v>
+        <v>1.62</v>
       </c>
       <c r="C102" s="10">
-        <v>-0.1</v>
+        <v>1.9</v>
       </c>
       <c r="D102" s="10">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="E102" s="9">
-        <v>0.91</v>
+        <v>0.6</v>
       </c>
       <c r="F102" s="4"/>
       <c r="G102" s="2">
-        <v>4.5199999999999996</v>
+        <v>-6.56</v>
       </c>
       <c r="H102" s="4"/>
       <c r="I102" s="4"/>
@@ -4664,23 +4668,23 @@
     </row>
     <row r="103" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B103" s="10">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="C103" s="10">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D103" s="10">
-        <v>0.12</v>
+        <v>1.04</v>
       </c>
       <c r="E103" s="9">
-        <v>0.45</v>
+        <v>0.91</v>
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="2">
-        <v>-0.27</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="H103" s="4"/>
       <c r="I103" s="4"/>
@@ -4703,23 +4707,23 @@
     </row>
     <row r="104" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B104" s="10">
-        <v>-0.86</v>
+        <v>0</v>
       </c>
       <c r="C104" s="10">
-        <v>-0.86</v>
+        <v>0</v>
       </c>
       <c r="D104" s="10">
-        <v>-0.51</v>
-      </c>
-      <c r="E104" s="10">
-        <v>-1.79</v>
+        <v>0.12</v>
+      </c>
+      <c r="E104" s="9">
+        <v>0.45</v>
       </c>
       <c r="F104" s="4"/>
       <c r="G104" s="2">
-        <v>-1.32</v>
+        <v>-0.27</v>
       </c>
       <c r="H104" s="4"/>
       <c r="I104" s="4"/>
@@ -4742,23 +4746,23 @@
     </row>
     <row r="105" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B105" s="10">
-        <v>0.42</v>
+        <v>-0.86</v>
       </c>
       <c r="C105" s="10">
-        <v>0.27</v>
+        <v>-0.86</v>
       </c>
       <c r="D105" s="10">
-        <v>0.75</v>
-      </c>
-      <c r="E105" s="9">
-        <v>0.74</v>
+        <v>-0.51</v>
+      </c>
+      <c r="E105" s="10">
+        <v>-1.79</v>
       </c>
       <c r="F105" s="4"/>
       <c r="G105" s="2">
-        <v>3.6</v>
+        <v>-1.32</v>
       </c>
       <c r="H105" s="4"/>
       <c r="I105" s="4"/>
@@ -4781,23 +4785,23 @@
     </row>
     <row r="106" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B106" s="10">
-        <v>-0.67</v>
+        <v>0.42</v>
       </c>
       <c r="C106" s="10">
-        <v>-0.55000000000000004</v>
+        <v>0.27</v>
       </c>
       <c r="D106" s="10">
-        <v>1.42</v>
-      </c>
-      <c r="E106" s="10">
-        <v>2.6</v>
+        <v>0.75</v>
+      </c>
+      <c r="E106" s="9">
+        <v>0.74</v>
       </c>
       <c r="F106" s="4"/>
       <c r="G106" s="2">
-        <v>-2.02</v>
+        <v>3.6</v>
       </c>
       <c r="H106" s="4"/>
       <c r="I106" s="4"/>
@@ -4820,23 +4824,23 @@
     </row>
     <row r="107" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B107" s="10">
-        <v>0.14000000000000001</v>
+        <v>-0.67</v>
       </c>
       <c r="C107" s="10">
-        <v>-0.65</v>
+        <v>-0.55000000000000004</v>
       </c>
       <c r="D107" s="10">
-        <v>0.52</v>
+        <v>1.42</v>
       </c>
       <c r="E107" s="10">
-        <v>0.26</v>
+        <v>2.6</v>
       </c>
       <c r="F107" s="4"/>
       <c r="G107" s="2">
-        <v>4.59</v>
+        <v>-2.02</v>
       </c>
       <c r="H107" s="4"/>
       <c r="I107" s="4"/>
@@ -4858,24 +4862,24 @@
       <c r="Y107" s="4"/>
     </row>
     <row r="108" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="7">
-        <v>45968</v>
-      </c>
-      <c r="B108" s="9">
-        <v>0</v>
+      <c r="A108" s="6">
+        <v>45971</v>
+      </c>
+      <c r="B108" s="10">
+        <v>0.14000000000000001</v>
       </c>
       <c r="C108" s="10">
-        <v>0</v>
+        <v>-0.65</v>
       </c>
       <c r="D108" s="10">
-        <v>0.28999999999999998</v>
+        <v>0.52</v>
       </c>
       <c r="E108" s="10">
-        <v>-0.32</v>
+        <v>0.26</v>
       </c>
       <c r="F108" s="4"/>
       <c r="G108" s="2">
-        <v>0.84</v>
+        <v>4.59</v>
       </c>
       <c r="H108" s="4"/>
       <c r="I108" s="4"/>
@@ -4897,24 +4901,24 @@
       <c r="Y108" s="4"/>
     </row>
     <row r="109" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="6">
-        <v>45967</v>
-      </c>
-      <c r="B109" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="C109" s="9">
-        <v>1.08</v>
+      <c r="A109" s="7">
+        <v>45968</v>
+      </c>
+      <c r="B109" s="9">
+        <v>0</v>
+      </c>
+      <c r="C109" s="10">
+        <v>0</v>
       </c>
       <c r="D109" s="10">
-        <v>0.25</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E109" s="10">
-        <v>-0.35</v>
+        <v>-0.32</v>
       </c>
       <c r="F109" s="4"/>
       <c r="G109" s="2">
-        <v>-1.59</v>
+        <v>0.84</v>
       </c>
       <c r="H109" s="4"/>
       <c r="I109" s="4"/>
@@ -4936,22 +4940,24 @@
       <c r="Y109" s="4"/>
     </row>
     <row r="110" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="7">
-        <v>45965</v>
-      </c>
-      <c r="B110" s="9">
-        <v>1.79</v>
+      <c r="A110" s="6">
+        <v>45967</v>
+      </c>
+      <c r="B110" s="10">
+        <v>0.2</v>
       </c>
       <c r="C110" s="9">
-        <v>1.98</v>
-      </c>
-      <c r="D110" s="11"/>
+        <v>1.08</v>
+      </c>
+      <c r="D110" s="10">
+        <v>0.25</v>
+      </c>
       <c r="E110" s="10">
-        <v>1.68</v>
+        <v>-0.35</v>
       </c>
       <c r="F110" s="4"/>
       <c r="G110" s="2">
-        <v>-1.35</v>
+        <v>-1.59</v>
       </c>
       <c r="H110" s="4"/>
       <c r="I110" s="4"/>
@@ -4973,22 +4979,22 @@
       <c r="Y110" s="4"/>
     </row>
     <row r="111" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="6">
-        <v>45964</v>
-      </c>
-      <c r="B111" s="10">
-        <v>0.34</v>
-      </c>
-      <c r="C111" s="10">
-        <v>0.63</v>
+      <c r="A111" s="7">
+        <v>45965</v>
+      </c>
+      <c r="B111" s="9">
+        <v>1.79</v>
+      </c>
+      <c r="C111" s="9">
+        <v>1.98</v>
       </c>
       <c r="D111" s="11"/>
       <c r="E111" s="10">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="2">
-        <v>1.19</v>
+        <v>-1.35</v>
       </c>
       <c r="H111" s="4"/>
       <c r="I111" s="4"/>
@@ -5011,19 +5017,21 @@
     </row>
     <row r="112" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B112" s="10">
-        <v>-1.99</v>
+        <v>0.34</v>
       </c>
       <c r="C112" s="10">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="D112" s="4"/>
-      <c r="E112" s="4"/>
+        <v>0.63</v>
+      </c>
+      <c r="D112" s="11"/>
+      <c r="E112" s="10">
+        <v>1.38</v>
+      </c>
       <c r="F112" s="4"/>
       <c r="G112" s="2">
-        <v>3.27</v>
+        <v>1.19</v>
       </c>
       <c r="H112" s="4"/>
       <c r="I112" s="4"/>
@@ -5045,20 +5053,20 @@
       <c r="Y112" s="4"/>
     </row>
     <row r="113" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="7">
-        <v>45960</v>
-      </c>
-      <c r="B113" s="9">
-        <v>1.84</v>
+      <c r="A113" s="6">
+        <v>45961</v>
+      </c>
+      <c r="B113" s="10">
+        <v>-1.99</v>
       </c>
       <c r="C113" s="10">
-        <v>1.33</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
       <c r="G113" s="2">
-        <v>0.2</v>
+        <v>3.27</v>
       </c>
       <c r="H113" s="4"/>
       <c r="I113" s="4"/>
@@ -5080,20 +5088,20 @@
       <c r="Y113" s="4"/>
     </row>
     <row r="114" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="6">
-        <v>45959</v>
-      </c>
-      <c r="B114" s="10">
-        <v>0.46</v>
-      </c>
-      <c r="C114" s="9">
-        <v>0.27</v>
+      <c r="A114" s="7">
+        <v>45960</v>
+      </c>
+      <c r="B114" s="9">
+        <v>1.84</v>
+      </c>
+      <c r="C114" s="10">
+        <v>1.33</v>
       </c>
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
       <c r="G114" s="2">
-        <v>4.0999999999999996</v>
+        <v>0.2</v>
       </c>
       <c r="H114" s="4"/>
       <c r="I114" s="4"/>
@@ -5116,19 +5124,19 @@
     </row>
     <row r="115" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B115" s="10">
-        <v>0.97</v>
-      </c>
-      <c r="C115" s="10">
-        <v>0.54</v>
+        <v>0.46</v>
+      </c>
+      <c r="C115" s="9">
+        <v>0.27</v>
       </c>
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
       <c r="G115" s="2">
-        <v>-4.8600000000000003</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="H115" s="4"/>
       <c r="I115" s="4"/>
@@ -5151,19 +5159,19 @@
     </row>
     <row r="116" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B116" s="10">
-        <v>-1.95</v>
+        <v>0.97</v>
       </c>
       <c r="C116" s="10">
-        <v>-1.24</v>
+        <v>0.54</v>
       </c>
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
       <c r="G116" s="2">
-        <v>-1.74</v>
+        <v>-4.8600000000000003</v>
       </c>
       <c r="H116" s="4"/>
       <c r="I116" s="4"/>
@@ -5185,20 +5193,20 @@
       <c r="Y116" s="4"/>
     </row>
     <row r="117" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="7">
-        <v>45954</v>
-      </c>
-      <c r="B117" s="9">
-        <v>0.65</v>
-      </c>
-      <c r="C117" s="9">
-        <v>0.56000000000000005</v>
+      <c r="A117" s="6">
+        <v>45957</v>
+      </c>
+      <c r="B117" s="10">
+        <v>-1.95</v>
+      </c>
+      <c r="C117" s="10">
+        <v>-1.24</v>
       </c>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
       <c r="G117" s="2">
-        <v>3.2</v>
+        <v>-1.74</v>
       </c>
       <c r="H117" s="4"/>
       <c r="I117" s="4"/>
@@ -5220,20 +5228,20 @@
       <c r="Y117" s="4"/>
     </row>
     <row r="118" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="6">
-        <v>45953</v>
-      </c>
-      <c r="B118" s="10">
-        <v>1.73</v>
-      </c>
-      <c r="C118" s="10">
-        <v>1.4</v>
+      <c r="A118" s="7">
+        <v>45954</v>
+      </c>
+      <c r="B118" s="9">
+        <v>0.65</v>
+      </c>
+      <c r="C118" s="9">
+        <v>0.56000000000000005</v>
       </c>
       <c r="D118" s="4"/>
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
-      <c r="G118" s="3">
-        <v>0</v>
+      <c r="G118" s="2">
+        <v>3.2</v>
       </c>
       <c r="H118" s="4"/>
       <c r="I118" s="4"/>
@@ -5256,19 +5264,19 @@
     </row>
     <row r="119" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="B119" s="10">
-        <v>0.01</v>
+        <v>1.73</v>
       </c>
       <c r="C119" s="10">
-        <v>0.01</v>
+        <v>1.4</v>
       </c>
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
       <c r="F119" s="4"/>
-      <c r="G119" s="2">
-        <v>1.05</v>
+      <c r="G119" s="3">
+        <v>0</v>
       </c>
       <c r="H119" s="4"/>
       <c r="I119" s="4"/>
@@ -5290,20 +5298,20 @@
       <c r="Y119" s="4"/>
     </row>
     <row r="120" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="7">
-        <v>45950</v>
-      </c>
-      <c r="B120" s="9">
-        <v>-1.85</v>
+      <c r="A120" s="6">
+        <v>45951</v>
+      </c>
+      <c r="B120" s="10">
+        <v>0.01</v>
       </c>
       <c r="C120" s="10">
-        <v>0.51</v>
+        <v>0.01</v>
       </c>
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
       <c r="F120" s="4"/>
       <c r="G120" s="2">
-        <v>-1.1000000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="H120" s="4"/>
       <c r="I120" s="4"/>
@@ -5325,20 +5333,20 @@
       <c r="Y120" s="4"/>
     </row>
     <row r="121" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="6">
-        <v>45947</v>
-      </c>
-      <c r="B121" s="10">
-        <v>-1.61</v>
-      </c>
-      <c r="C121" s="9">
-        <v>-1.76</v>
+      <c r="A121" s="7">
+        <v>45950</v>
+      </c>
+      <c r="B121" s="9">
+        <v>-1.85</v>
+      </c>
+      <c r="C121" s="10">
+        <v>0.51</v>
       </c>
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
       <c r="F121" s="4"/>
       <c r="G121" s="2">
-        <v>0.22</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="H121" s="4"/>
       <c r="I121" s="4"/>
@@ -5361,19 +5369,19 @@
     </row>
     <row r="122" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B122" s="10">
-        <v>2</v>
-      </c>
-      <c r="C122" s="10">
-        <v>1.02</v>
+        <v>-1.61</v>
+      </c>
+      <c r="C122" s="9">
+        <v>-1.76</v>
       </c>
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
       <c r="F122" s="4"/>
       <c r="G122" s="2">
-        <v>4.09</v>
+        <v>0.22</v>
       </c>
       <c r="H122" s="4"/>
       <c r="I122" s="4"/>
@@ -5396,19 +5404,19 @@
     </row>
     <row r="123" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B123" s="10">
-        <v>0.57999999999999996</v>
+        <v>2</v>
       </c>
       <c r="C123" s="10">
-        <v>0.41</v>
+        <v>1.02</v>
       </c>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
       <c r="F123" s="4"/>
       <c r="G123" s="2">
-        <v>3.24</v>
+        <v>4.09</v>
       </c>
       <c r="H123" s="4"/>
       <c r="I123" s="4"/>
@@ -5430,20 +5438,20 @@
       <c r="Y123" s="4"/>
     </row>
     <row r="124" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="7">
-        <v>45944</v>
-      </c>
-      <c r="B124" s="9">
-        <v>-0.2</v>
-      </c>
-      <c r="C124" s="9">
-        <v>0.38</v>
+      <c r="A124" s="6">
+        <v>45945</v>
+      </c>
+      <c r="B124" s="10">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="C124" s="10">
+        <v>0.41</v>
       </c>
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
       <c r="F124" s="4"/>
       <c r="G124" s="2">
-        <v>3.78</v>
+        <v>3.24</v>
       </c>
       <c r="H124" s="4"/>
       <c r="I124" s="4"/>
@@ -5465,20 +5473,20 @@
       <c r="Y124" s="4"/>
     </row>
     <row r="125" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="6">
-        <v>45943</v>
-      </c>
-      <c r="B125" s="10">
-        <v>1</v>
-      </c>
-      <c r="C125" s="10">
-        <v>1</v>
+      <c r="A125" s="7">
+        <v>45944</v>
+      </c>
+      <c r="B125" s="9">
+        <v>-0.2</v>
+      </c>
+      <c r="C125" s="9">
+        <v>0.38</v>
       </c>
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
       <c r="F125" s="4"/>
       <c r="G125" s="2">
-        <v>4.04</v>
+        <v>3.78</v>
       </c>
       <c r="H125" s="4"/>
       <c r="I125" s="4"/>
@@ -5501,19 +5509,19 @@
     </row>
     <row r="126" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B126" s="10">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="C126" s="10">
-        <v>-1.22</v>
+        <v>1</v>
       </c>
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
       <c r="F126" s="4"/>
       <c r="G126" s="2">
-        <v>5.08</v>
+        <v>4.04</v>
       </c>
       <c r="H126" s="4"/>
       <c r="I126" s="4"/>
@@ -5535,20 +5543,20 @@
       <c r="Y126" s="4"/>
     </row>
     <row r="127" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="7">
-        <v>45939</v>
-      </c>
-      <c r="B127" s="9">
-        <v>0.75</v>
+      <c r="A127" s="6">
+        <v>45940</v>
+      </c>
+      <c r="B127" s="10">
+        <v>-2</v>
       </c>
       <c r="C127" s="10">
-        <v>0.75</v>
+        <v>-1.22</v>
       </c>
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
       <c r="F127" s="4"/>
       <c r="G127" s="2">
-        <v>-2.12</v>
+        <v>5.08</v>
       </c>
       <c r="H127" s="4"/>
       <c r="I127" s="4"/>
@@ -5570,20 +5578,20 @@
       <c r="Y127" s="4"/>
     </row>
     <row r="128" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="6">
-        <v>45938</v>
-      </c>
-      <c r="B128" s="10">
-        <v>-0.26</v>
-      </c>
-      <c r="C128" s="9">
-        <v>-0.26</v>
+      <c r="A128" s="7">
+        <v>45939</v>
+      </c>
+      <c r="B128" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="C128" s="10">
+        <v>0.75</v>
       </c>
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
       <c r="F128" s="4"/>
       <c r="G128" s="2">
-        <v>3.36</v>
+        <v>-2.12</v>
       </c>
       <c r="H128" s="4"/>
       <c r="I128" s="4"/>
@@ -5606,19 +5614,19 @@
     </row>
     <row r="129" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B129" s="10">
-        <v>-0.2</v>
-      </c>
-      <c r="C129" s="10">
-        <v>-0.2</v>
+        <v>-0.26</v>
+      </c>
+      <c r="C129" s="9">
+        <v>-0.26</v>
       </c>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
       <c r="F129" s="4"/>
       <c r="G129" s="2">
-        <v>2.94</v>
+        <v>3.36</v>
       </c>
       <c r="H129" s="4"/>
       <c r="I129" s="4"/>
@@ -5641,19 +5649,19 @@
     </row>
     <row r="130" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B130" s="10">
-        <v>-0.43</v>
+        <v>-0.2</v>
       </c>
       <c r="C130" s="10">
-        <v>-0.43</v>
+        <v>-0.2</v>
       </c>
       <c r="D130" s="4"/>
       <c r="E130" s="4"/>
       <c r="F130" s="4"/>
       <c r="G130" s="2">
-        <v>3.95</v>
+        <v>2.94</v>
       </c>
       <c r="H130" s="4"/>
       <c r="I130" s="4"/>
@@ -5675,20 +5683,20 @@
       <c r="Y130" s="4"/>
     </row>
     <row r="131" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="7">
-        <v>45933</v>
-      </c>
-      <c r="B131" s="9">
-        <v>0.4</v>
-      </c>
-      <c r="C131" s="9">
-        <v>0.4</v>
+      <c r="A131" s="6">
+        <v>45936</v>
+      </c>
+      <c r="B131" s="10">
+        <v>-0.43</v>
+      </c>
+      <c r="C131" s="10">
+        <v>-0.43</v>
       </c>
       <c r="D131" s="4"/>
       <c r="E131" s="4"/>
       <c r="F131" s="4"/>
       <c r="G131" s="2">
-        <v>2.7</v>
+        <v>3.95</v>
       </c>
       <c r="H131" s="4"/>
       <c r="I131" s="4"/>
@@ -5710,20 +5718,20 @@
       <c r="Y131" s="4"/>
     </row>
     <row r="132" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="6">
-        <v>45931</v>
-      </c>
-      <c r="B132" s="10">
-        <v>0.49</v>
-      </c>
-      <c r="C132" s="10">
-        <v>0.49</v>
+      <c r="A132" s="7">
+        <v>45933</v>
+      </c>
+      <c r="B132" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="C132" s="9">
+        <v>0.4</v>
       </c>
       <c r="D132" s="4"/>
       <c r="E132" s="4"/>
       <c r="F132" s="4"/>
       <c r="G132" s="2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="H132" s="4"/>
       <c r="I132" s="4"/>
@@ -5745,20 +5753,20 @@
       <c r="Y132" s="4"/>
     </row>
     <row r="133" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="7">
-        <v>45930</v>
-      </c>
-      <c r="B133" s="9">
-        <v>0.08</v>
+      <c r="A133" s="6">
+        <v>45931</v>
+      </c>
+      <c r="B133" s="10">
+        <v>0.49</v>
       </c>
       <c r="C133" s="10">
-        <v>0.08</v>
+        <v>0.49</v>
       </c>
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
       <c r="F133" s="4"/>
       <c r="G133" s="2">
-        <v>-4.63</v>
+        <v>0</v>
       </c>
       <c r="H133" s="4"/>
       <c r="I133" s="4"/>
@@ -5780,20 +5788,20 @@
       <c r="Y133" s="4"/>
     </row>
     <row r="134" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="6">
-        <v>45929</v>
-      </c>
-      <c r="B134" s="10">
-        <v>0.27</v>
+      <c r="A134" s="7">
+        <v>45930</v>
+      </c>
+      <c r="B134" s="9">
+        <v>0.08</v>
       </c>
       <c r="C134" s="10">
-        <v>0.27</v>
+        <v>0.08</v>
       </c>
       <c r="D134" s="4"/>
       <c r="E134" s="4"/>
       <c r="F134" s="4"/>
       <c r="G134" s="2">
-        <v>-3.45</v>
+        <v>-4.63</v>
       </c>
       <c r="H134" s="4"/>
       <c r="I134" s="4"/>
@@ -5816,19 +5824,19 @@
     </row>
     <row r="135" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B135" s="10">
-        <v>1.31</v>
+        <v>0.27</v>
       </c>
       <c r="C135" s="10">
-        <v>1.31</v>
+        <v>0.27</v>
       </c>
       <c r="D135" s="4"/>
       <c r="E135" s="4"/>
       <c r="F135" s="4"/>
       <c r="G135" s="2">
-        <v>3.83</v>
+        <v>-3.45</v>
       </c>
       <c r="H135" s="4"/>
       <c r="I135" s="4"/>
@@ -5851,19 +5859,19 @@
     </row>
     <row r="136" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B136" s="10">
-        <v>0.97</v>
-      </c>
-      <c r="C136" s="9">
-        <v>0.97</v>
+        <v>1.31</v>
+      </c>
+      <c r="C136" s="10">
+        <v>1.31</v>
       </c>
       <c r="D136" s="4"/>
       <c r="E136" s="4"/>
       <c r="F136" s="4"/>
       <c r="G136" s="2">
-        <v>2.1</v>
+        <v>3.83</v>
       </c>
       <c r="H136" s="4"/>
       <c r="I136" s="4"/>
@@ -5886,19 +5894,19 @@
     </row>
     <row r="137" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B137" s="10">
-        <v>0.96</v>
-      </c>
-      <c r="C137" s="10">
-        <v>0.96</v>
+        <v>0.97</v>
+      </c>
+      <c r="C137" s="9">
+        <v>0.97</v>
       </c>
       <c r="D137" s="4"/>
       <c r="E137" s="4"/>
       <c r="F137" s="4"/>
       <c r="G137" s="2">
-        <v>-6.91</v>
+        <v>2.1</v>
       </c>
       <c r="H137" s="4"/>
       <c r="I137" s="4"/>
@@ -5920,20 +5928,20 @@
       <c r="Y137" s="4"/>
     </row>
     <row r="138" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="7">
-        <v>45923</v>
-      </c>
-      <c r="B138" s="9">
-        <v>-0.08</v>
-      </c>
-      <c r="C138" s="9">
-        <v>-0.08</v>
+      <c r="A138" s="6">
+        <v>45924</v>
+      </c>
+      <c r="B138" s="10">
+        <v>0.96</v>
+      </c>
+      <c r="C138" s="10">
+        <v>0.96</v>
       </c>
       <c r="D138" s="4"/>
       <c r="E138" s="4"/>
       <c r="F138" s="4"/>
       <c r="G138" s="2">
-        <v>-0.22</v>
+        <v>-6.91</v>
       </c>
       <c r="H138" s="4"/>
       <c r="I138" s="4"/>
@@ -5955,20 +5963,20 @@
       <c r="Y138" s="4"/>
     </row>
     <row r="139" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="6">
-        <v>45922</v>
-      </c>
-      <c r="B139" s="10">
-        <v>0.96</v>
-      </c>
-      <c r="C139" s="10">
-        <v>0.96</v>
+      <c r="A139" s="7">
+        <v>45923</v>
+      </c>
+      <c r="B139" s="9">
+        <v>-0.08</v>
+      </c>
+      <c r="C139" s="9">
+        <v>-0.08</v>
       </c>
       <c r="D139" s="4"/>
       <c r="E139" s="4"/>
       <c r="F139" s="4"/>
       <c r="G139" s="2">
-        <v>4.5199999999999996</v>
+        <v>-0.22</v>
       </c>
       <c r="H139" s="4"/>
       <c r="I139" s="4"/>
@@ -5990,20 +5998,20 @@
       <c r="Y139" s="4"/>
     </row>
     <row r="140" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="7">
-        <v>45919</v>
-      </c>
-      <c r="B140" s="9">
-        <v>-0.53</v>
+      <c r="A140" s="6">
+        <v>45922</v>
+      </c>
+      <c r="B140" s="10">
+        <v>0.96</v>
       </c>
       <c r="C140" s="10">
-        <v>-0.53</v>
+        <v>0.96</v>
       </c>
       <c r="D140" s="4"/>
       <c r="E140" s="4"/>
       <c r="F140" s="4"/>
       <c r="G140" s="2">
-        <v>4.05</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="H140" s="4"/>
       <c r="I140" s="4"/>
@@ -6025,20 +6033,20 @@
       <c r="Y140" s="4"/>
     </row>
     <row r="141" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="6">
-        <v>45918</v>
-      </c>
-      <c r="B141" s="10">
-        <v>1.98</v>
+      <c r="A141" s="7">
+        <v>45919</v>
+      </c>
+      <c r="B141" s="9">
+        <v>-0.53</v>
       </c>
       <c r="C141" s="10">
-        <v>1.98</v>
+        <v>-0.53</v>
       </c>
       <c r="D141" s="4"/>
       <c r="E141" s="4"/>
       <c r="F141" s="4"/>
       <c r="G141" s="2">
-        <v>-2.5</v>
+        <v>4.05</v>
       </c>
       <c r="H141" s="4"/>
       <c r="I141" s="4"/>
@@ -6061,19 +6069,19 @@
     </row>
     <row r="142" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B142" s="10">
-        <v>0.28000000000000003</v>
+        <v>1.98</v>
       </c>
       <c r="C142" s="10">
-        <v>0.28000000000000003</v>
+        <v>1.98</v>
       </c>
       <c r="D142" s="4"/>
       <c r="E142" s="4"/>
       <c r="F142" s="4"/>
       <c r="G142" s="2">
-        <v>2.08</v>
+        <v>-2.5</v>
       </c>
       <c r="H142" s="4"/>
       <c r="I142" s="4"/>
@@ -6096,19 +6104,19 @@
     </row>
     <row r="143" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B143" s="10">
-        <v>-0.13</v>
-      </c>
-      <c r="C143" s="9">
-        <v>-0.13</v>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="C143" s="10">
+        <v>0.28000000000000003</v>
       </c>
       <c r="D143" s="4"/>
       <c r="E143" s="4"/>
       <c r="F143" s="4"/>
       <c r="G143" s="2">
-        <v>0.97</v>
+        <v>2.08</v>
       </c>
       <c r="H143" s="4"/>
       <c r="I143" s="4"/>
@@ -6131,19 +6139,19 @@
     </row>
     <row r="144" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B144" s="10">
-        <v>0.42</v>
-      </c>
-      <c r="C144" s="10">
-        <v>0.42</v>
+        <v>-0.13</v>
+      </c>
+      <c r="C144" s="9">
+        <v>-0.13</v>
       </c>
       <c r="D144" s="4"/>
       <c r="E144" s="4"/>
       <c r="F144" s="4"/>
       <c r="G144" s="2">
-        <v>2.02</v>
+        <v>0.97</v>
       </c>
       <c r="H144" s="4"/>
       <c r="I144" s="4"/>
@@ -6166,19 +6174,19 @@
     </row>
     <row r="145" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B145" s="10">
-        <v>-0.15</v>
+        <v>0.42</v>
       </c>
       <c r="C145" s="10">
-        <v>-0.15</v>
+        <v>0.42</v>
       </c>
       <c r="D145" s="4"/>
       <c r="E145" s="4"/>
       <c r="F145" s="4"/>
       <c r="G145" s="2">
-        <v>1.59</v>
+        <v>2.02</v>
       </c>
       <c r="H145" s="4"/>
       <c r="I145" s="4"/>
@@ -6201,19 +6209,19 @@
     </row>
     <row r="146" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B146" s="10">
-        <v>1.36</v>
-      </c>
-      <c r="C146" s="9">
-        <v>1.36</v>
+        <v>-0.15</v>
+      </c>
+      <c r="C146" s="10">
+        <v>-0.15</v>
       </c>
       <c r="D146" s="4"/>
       <c r="E146" s="4"/>
       <c r="F146" s="4"/>
       <c r="G146" s="2">
-        <v>-0.78</v>
+        <v>1.59</v>
       </c>
       <c r="H146" s="4"/>
       <c r="I146" s="4"/>
@@ -6236,19 +6244,19 @@
     </row>
     <row r="147" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B147" s="10">
-        <v>0.46</v>
-      </c>
-      <c r="C147" s="10">
-        <v>0.46</v>
+        <v>1.36</v>
+      </c>
+      <c r="C147" s="9">
+        <v>1.36</v>
       </c>
       <c r="D147" s="4"/>
       <c r="E147" s="4"/>
       <c r="F147" s="4"/>
       <c r="G147" s="2">
-        <v>-2.12</v>
+        <v>-0.78</v>
       </c>
       <c r="H147" s="4"/>
       <c r="I147" s="4"/>
@@ -6271,19 +6279,19 @@
     </row>
     <row r="148" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="B148" s="10">
-        <v>1.8</v>
+        <v>0.46</v>
       </c>
       <c r="C148" s="10">
-        <v>1.8</v>
+        <v>0.46</v>
       </c>
       <c r="D148" s="4"/>
       <c r="E148" s="4"/>
       <c r="F148" s="4"/>
       <c r="G148" s="2">
-        <v>-0.08</v>
+        <v>-2.12</v>
       </c>
       <c r="H148" s="4"/>
       <c r="I148" s="4"/>
@@ -6306,19 +6314,19 @@
     </row>
     <row r="149" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
-        <v>45908</v>
+        <v>45909</v>
       </c>
       <c r="B149" s="10">
-        <v>-0.11</v>
-      </c>
-      <c r="C149" s="9">
-        <v>-0.11</v>
+        <v>1.8</v>
+      </c>
+      <c r="C149" s="10">
+        <v>1.8</v>
       </c>
       <c r="D149" s="4"/>
       <c r="E149" s="4"/>
       <c r="F149" s="4"/>
       <c r="G149" s="2">
-        <v>2.41</v>
+        <v>-0.08</v>
       </c>
       <c r="H149" s="4"/>
       <c r="I149" s="4"/>
@@ -6341,19 +6349,19 @@
     </row>
     <row r="150" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
-        <v>45905</v>
+        <v>45908</v>
       </c>
       <c r="B150" s="10">
-        <v>-1.8</v>
-      </c>
-      <c r="C150" s="10">
-        <v>-2.4</v>
+        <v>-0.11</v>
+      </c>
+      <c r="C150" s="9">
+        <v>-0.11</v>
       </c>
       <c r="D150" s="4"/>
       <c r="E150" s="4"/>
       <c r="F150" s="4"/>
       <c r="G150" s="2">
-        <v>-3.45</v>
+        <v>2.41</v>
       </c>
       <c r="H150" s="4"/>
       <c r="I150" s="4"/>
@@ -6375,20 +6383,20 @@
       <c r="Y150" s="4"/>
     </row>
     <row r="151" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="7">
-        <v>45904</v>
-      </c>
-      <c r="B151" s="9">
-        <v>0.12</v>
+      <c r="A151" s="6">
+        <v>45905</v>
+      </c>
+      <c r="B151" s="10">
+        <v>-1.8</v>
       </c>
       <c r="C151" s="10">
-        <v>0.12</v>
+        <v>-2.4</v>
       </c>
       <c r="D151" s="4"/>
       <c r="E151" s="4"/>
       <c r="F151" s="4"/>
       <c r="G151" s="2">
-        <v>1.52</v>
+        <v>-3.45</v>
       </c>
       <c r="H151" s="4"/>
       <c r="I151" s="4"/>
@@ -6410,20 +6418,20 @@
       <c r="Y151" s="4"/>
     </row>
     <row r="152" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="6">
-        <v>45903</v>
-      </c>
-      <c r="B152" s="10">
-        <v>0.15</v>
-      </c>
-      <c r="C152" s="9">
-        <v>0.15</v>
+      <c r="A152" s="7">
+        <v>45904</v>
+      </c>
+      <c r="B152" s="9">
+        <v>0.12</v>
+      </c>
+      <c r="C152" s="10">
+        <v>0.12</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="4"/>
       <c r="F152" s="4"/>
       <c r="G152" s="2">
-        <v>1.1100000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="H152" s="4"/>
       <c r="I152" s="4"/>
@@ -6445,20 +6453,20 @@
       <c r="Y152" s="4"/>
     </row>
     <row r="153" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="7">
-        <v>45902</v>
-      </c>
-      <c r="B153" s="9">
-        <v>1.02</v>
-      </c>
-      <c r="C153" s="10">
-        <v>1.02</v>
+      <c r="A153" s="6">
+        <v>45903</v>
+      </c>
+      <c r="B153" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="C153" s="9">
+        <v>0.15</v>
       </c>
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
       <c r="F153" s="4"/>
       <c r="G153" s="2">
-        <v>4.0599999999999996</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="H153" s="4"/>
       <c r="I153" s="4"/>
@@ -6480,20 +6488,20 @@
       <c r="Y153" s="4"/>
     </row>
     <row r="154" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="6">
-        <v>45901</v>
-      </c>
-      <c r="B154" s="10">
-        <v>0.51</v>
-      </c>
-      <c r="C154" s="9">
-        <v>0.51</v>
+      <c r="A154" s="7">
+        <v>45902</v>
+      </c>
+      <c r="B154" s="9">
+        <v>1.02</v>
+      </c>
+      <c r="C154" s="10">
+        <v>1.02</v>
       </c>
       <c r="D154" s="4"/>
       <c r="E154" s="4"/>
       <c r="F154" s="4"/>
       <c r="G154" s="2">
-        <v>0.3</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="H154" s="4"/>
       <c r="I154" s="4"/>
@@ -6515,20 +6523,20 @@
       <c r="Y154" s="4"/>
     </row>
     <row r="155" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="7">
-        <v>45898</v>
-      </c>
-      <c r="B155" s="9">
-        <v>0.48</v>
-      </c>
-      <c r="C155" s="10">
-        <v>0.48</v>
+      <c r="A155" s="6">
+        <v>45901</v>
+      </c>
+      <c r="B155" s="10">
+        <v>0.51</v>
+      </c>
+      <c r="C155" s="9">
+        <v>0.51</v>
       </c>
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
       <c r="F155" s="4"/>
       <c r="G155" s="2">
-        <v>-4.5</v>
+        <v>0.3</v>
       </c>
       <c r="H155" s="4"/>
       <c r="I155" s="4"/>
@@ -6550,20 +6558,20 @@
       <c r="Y155" s="4"/>
     </row>
     <row r="156" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="6">
-        <v>45897</v>
-      </c>
-      <c r="B156" s="10">
-        <v>-1.49</v>
-      </c>
-      <c r="C156" s="9">
-        <v>-0.27</v>
+      <c r="A156" s="7">
+        <v>45898</v>
+      </c>
+      <c r="B156" s="9">
+        <v>0.48</v>
+      </c>
+      <c r="C156" s="10">
+        <v>0.48</v>
       </c>
       <c r="D156" s="4"/>
       <c r="E156" s="4"/>
       <c r="F156" s="4"/>
       <c r="G156" s="2">
-        <v>5.25</v>
+        <v>-4.5</v>
       </c>
       <c r="H156" s="4"/>
       <c r="I156" s="4"/>
@@ -6585,20 +6593,20 @@
       <c r="Y156" s="4"/>
     </row>
     <row r="157" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="7">
-        <v>45896</v>
-      </c>
-      <c r="B157" s="9">
-        <v>0</v>
-      </c>
-      <c r="C157" s="10">
-        <v>0</v>
+      <c r="A157" s="6">
+        <v>45897</v>
+      </c>
+      <c r="B157" s="10">
+        <v>-1.49</v>
+      </c>
+      <c r="C157" s="9">
+        <v>-0.27</v>
       </c>
       <c r="D157" s="4"/>
       <c r="E157" s="4"/>
       <c r="F157" s="4"/>
       <c r="G157" s="2">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="H157" s="4"/>
       <c r="I157" s="4"/>
@@ -6620,20 +6628,20 @@
       <c r="Y157" s="4"/>
     </row>
     <row r="158" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="6">
-        <v>45895</v>
-      </c>
-      <c r="B158" s="10">
-        <v>-0.36</v>
-      </c>
-      <c r="C158" s="9">
-        <v>-0.36</v>
+      <c r="A158" s="7">
+        <v>45896</v>
+      </c>
+      <c r="B158" s="9">
+        <v>0</v>
+      </c>
+      <c r="C158" s="10">
+        <v>0</v>
       </c>
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
       <c r="F158" s="4"/>
       <c r="G158" s="2">
-        <v>-2.52</v>
+        <v>0</v>
       </c>
       <c r="H158" s="4"/>
       <c r="I158" s="4"/>
@@ -6655,20 +6663,20 @@
       <c r="Y158" s="4"/>
     </row>
     <row r="159" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="7">
-        <v>45894</v>
-      </c>
-      <c r="B159" s="9">
-        <v>0.67</v>
-      </c>
-      <c r="C159" s="10">
-        <v>0.67</v>
+      <c r="A159" s="6">
+        <v>45895</v>
+      </c>
+      <c r="B159" s="10">
+        <v>-0.36</v>
+      </c>
+      <c r="C159" s="9">
+        <v>-0.36</v>
       </c>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
       <c r="F159" s="4"/>
       <c r="G159" s="2">
-        <v>1</v>
+        <v>-2.52</v>
       </c>
       <c r="H159" s="4"/>
       <c r="I159" s="4"/>
@@ -6690,20 +6698,20 @@
       <c r="Y159" s="4"/>
     </row>
     <row r="160" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="6">
-        <v>45891</v>
-      </c>
-      <c r="B160" s="10">
-        <v>0</v>
-      </c>
-      <c r="C160" s="9">
-        <v>0</v>
+      <c r="A160" s="7">
+        <v>45894</v>
+      </c>
+      <c r="B160" s="9">
+        <v>0.67</v>
+      </c>
+      <c r="C160" s="10">
+        <v>0.67</v>
       </c>
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
       <c r="F160" s="4"/>
       <c r="G160" s="2">
-        <v>5.01</v>
+        <v>1</v>
       </c>
       <c r="H160" s="4"/>
       <c r="I160" s="4"/>
@@ -6725,20 +6733,20 @@
       <c r="Y160" s="4"/>
     </row>
     <row r="161" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="7">
-        <v>45890</v>
-      </c>
-      <c r="B161" s="9">
-        <v>0.8</v>
-      </c>
-      <c r="C161" s="10">
-        <v>0.8</v>
+      <c r="A161" s="6">
+        <v>45891</v>
+      </c>
+      <c r="B161" s="10">
+        <v>0</v>
+      </c>
+      <c r="C161" s="9">
+        <v>0</v>
       </c>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
       <c r="F161" s="4"/>
       <c r="G161" s="2">
-        <v>-3.34</v>
+        <v>5.01</v>
       </c>
       <c r="H161" s="4"/>
       <c r="I161" s="4"/>
@@ -6760,20 +6768,20 @@
       <c r="Y161" s="4"/>
     </row>
     <row r="162" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="6">
-        <v>45889</v>
-      </c>
-      <c r="B162" s="10">
-        <v>0.7</v>
-      </c>
-      <c r="C162" s="9">
-        <v>0.7</v>
+      <c r="A162" s="7">
+        <v>45890</v>
+      </c>
+      <c r="B162" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="C162" s="10">
+        <v>0.8</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="4"/>
       <c r="F162" s="4"/>
       <c r="G162" s="2">
-        <v>0.39</v>
+        <v>-3.34</v>
       </c>
       <c r="H162" s="4"/>
       <c r="I162" s="4"/>
@@ -6795,20 +6803,20 @@
       <c r="Y162" s="4"/>
     </row>
     <row r="163" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="7">
-        <v>45888</v>
-      </c>
-      <c r="B163" s="9">
-        <v>1.07</v>
-      </c>
-      <c r="C163" s="10">
-        <v>1.07</v>
+      <c r="A163" s="6">
+        <v>45889</v>
+      </c>
+      <c r="B163" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="C163" s="9">
+        <v>0.7</v>
       </c>
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
       <c r="F163" s="4"/>
       <c r="G163" s="2">
-        <v>-2.65</v>
+        <v>0.39</v>
       </c>
       <c r="H163" s="4"/>
       <c r="I163" s="4"/>
@@ -6830,20 +6838,20 @@
       <c r="Y163" s="4"/>
     </row>
     <row r="164" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="6">
-        <v>45887</v>
-      </c>
-      <c r="B164" s="10">
-        <v>1.56</v>
+      <c r="A164" s="7">
+        <v>45888</v>
+      </c>
+      <c r="B164" s="9">
+        <v>1.07</v>
       </c>
       <c r="C164" s="10">
-        <v>1.56</v>
+        <v>1.07</v>
       </c>
       <c r="D164" s="4"/>
       <c r="E164" s="4"/>
       <c r="F164" s="4"/>
       <c r="G164" s="2">
-        <v>-8.58</v>
+        <v>-2.65</v>
       </c>
       <c r="H164" s="4"/>
       <c r="I164" s="4"/>
@@ -6866,19 +6874,19 @@
     </row>
     <row r="165" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
-        <v>45883</v>
+        <v>45887</v>
       </c>
       <c r="B165" s="10">
-        <v>1.82</v>
-      </c>
-      <c r="C165" s="9">
-        <v>1.82</v>
+        <v>1.56</v>
+      </c>
+      <c r="C165" s="10">
+        <v>1.56</v>
       </c>
       <c r="D165" s="4"/>
       <c r="E165" s="4"/>
       <c r="F165" s="4"/>
       <c r="G165" s="2">
-        <v>1.22</v>
+        <v>-8.58</v>
       </c>
       <c r="H165" s="4"/>
       <c r="I165" s="4"/>
@@ -6900,20 +6908,20 @@
       <c r="Y165" s="4"/>
     </row>
     <row r="166" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="7">
-        <v>45882</v>
-      </c>
-      <c r="B166" s="9">
-        <v>0.6</v>
-      </c>
-      <c r="C166" s="10">
-        <v>0.6</v>
+      <c r="A166" s="6">
+        <v>45883</v>
+      </c>
+      <c r="B166" s="10">
+        <v>1.82</v>
+      </c>
+      <c r="C166" s="9">
+        <v>1.82</v>
       </c>
       <c r="D166" s="4"/>
       <c r="E166" s="4"/>
       <c r="F166" s="4"/>
       <c r="G166" s="2">
-        <v>-2.5099999999999998</v>
+        <v>1.22</v>
       </c>
       <c r="H166" s="4"/>
       <c r="I166" s="4"/>
@@ -6935,20 +6943,20 @@
       <c r="Y166" s="4"/>
     </row>
     <row r="167" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="6">
-        <v>45881</v>
-      </c>
-      <c r="B167" s="10">
-        <v>-1.82</v>
+      <c r="A167" s="7">
+        <v>45882</v>
+      </c>
+      <c r="B167" s="9">
+        <v>0.6</v>
       </c>
       <c r="C167" s="10">
-        <v>-0.69</v>
+        <v>0.6</v>
       </c>
       <c r="D167" s="4"/>
       <c r="E167" s="4"/>
       <c r="F167" s="4"/>
       <c r="G167" s="2">
-        <v>4.42</v>
+        <v>-2.5099999999999998</v>
       </c>
       <c r="H167" s="4"/>
       <c r="I167" s="4"/>
@@ -6971,19 +6979,19 @@
     </row>
     <row r="168" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
-        <v>45880</v>
+        <v>45881</v>
       </c>
       <c r="B168" s="10">
-        <v>-0.68</v>
-      </c>
-      <c r="C168" s="9">
-        <v>-0.68</v>
+        <v>-1.82</v>
+      </c>
+      <c r="C168" s="10">
+        <v>-0.69</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="4"/>
       <c r="F168" s="4"/>
       <c r="G168" s="2">
-        <v>3.76</v>
+        <v>4.42</v>
       </c>
       <c r="H168" s="4"/>
       <c r="I168" s="4"/>
@@ -7005,20 +7013,20 @@
       <c r="Y168" s="4"/>
     </row>
     <row r="169" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="7">
-        <v>45877</v>
-      </c>
-      <c r="B169" s="9">
-        <v>0.17</v>
-      </c>
-      <c r="C169" s="10">
-        <v>0.17</v>
+      <c r="A169" s="6">
+        <v>45880</v>
+      </c>
+      <c r="B169" s="10">
+        <v>-0.68</v>
+      </c>
+      <c r="C169" s="9">
+        <v>-0.68</v>
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
       <c r="F169" s="4"/>
       <c r="G169" s="2">
-        <v>-6.62</v>
+        <v>3.76</v>
       </c>
       <c r="H169" s="4"/>
       <c r="I169" s="4"/>
@@ -7040,20 +7048,20 @@
       <c r="Y169" s="4"/>
     </row>
     <row r="170" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="6">
-        <v>45876</v>
-      </c>
-      <c r="B170" s="10">
-        <v>1.75</v>
+      <c r="A170" s="7">
+        <v>45877</v>
+      </c>
+      <c r="B170" s="9">
+        <v>0.17</v>
       </c>
       <c r="C170" s="10">
-        <v>1.75</v>
+        <v>0.17</v>
       </c>
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
       <c r="F170" s="4"/>
       <c r="G170" s="2">
-        <v>10.58</v>
+        <v>-6.62</v>
       </c>
       <c r="H170" s="4"/>
       <c r="I170" s="4"/>
@@ -7076,19 +7084,19 @@
     </row>
     <row r="171" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
-        <v>45875</v>
+        <v>45876</v>
       </c>
       <c r="B171" s="10">
-        <v>0.72</v>
-      </c>
-      <c r="C171" s="9">
-        <v>0.72</v>
+        <v>1.75</v>
+      </c>
+      <c r="C171" s="10">
+        <v>1.75</v>
       </c>
       <c r="D171" s="4"/>
       <c r="E171" s="4"/>
       <c r="F171" s="4"/>
       <c r="G171" s="2">
-        <v>-0.76</v>
+        <v>10.58</v>
       </c>
       <c r="H171" s="4"/>
       <c r="I171" s="4"/>
@@ -7110,20 +7118,20 @@
       <c r="Y171" s="4"/>
     </row>
     <row r="172" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="7">
-        <v>45874</v>
-      </c>
-      <c r="B172" s="9">
-        <v>1.81</v>
-      </c>
-      <c r="C172" s="10">
-        <v>1.81</v>
+      <c r="A172" s="6">
+        <v>45875</v>
+      </c>
+      <c r="B172" s="10">
+        <v>0.72</v>
+      </c>
+      <c r="C172" s="9">
+        <v>0.72</v>
       </c>
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
       <c r="F172" s="4"/>
       <c r="G172" s="2">
-        <v>-2.99</v>
+        <v>-0.76</v>
       </c>
       <c r="H172" s="4"/>
       <c r="I172" s="4"/>
@@ -7145,20 +7153,20 @@
       <c r="Y172" s="4"/>
     </row>
     <row r="173" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="6">
-        <v>45873</v>
-      </c>
-      <c r="B173" s="10">
-        <v>0</v>
-      </c>
-      <c r="C173" s="9">
-        <v>0</v>
+      <c r="A173" s="7">
+        <v>45874</v>
+      </c>
+      <c r="B173" s="9">
+        <v>1.81</v>
+      </c>
+      <c r="C173" s="10">
+        <v>1.81</v>
       </c>
       <c r="D173" s="4"/>
       <c r="E173" s="4"/>
       <c r="F173" s="4"/>
       <c r="G173" s="2">
-        <v>3.06</v>
+        <v>-2.99</v>
       </c>
       <c r="H173" s="4"/>
       <c r="I173" s="4"/>
@@ -7181,19 +7189,19 @@
     </row>
     <row r="174" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
-        <v>45870</v>
-      </c>
-      <c r="B174" s="9">
-        <v>0.01</v>
+        <v>45873</v>
+      </c>
+      <c r="B174" s="10">
+        <v>0</v>
       </c>
       <c r="C174" s="9">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D174" s="4"/>
       <c r="E174" s="4"/>
       <c r="F174" s="4"/>
       <c r="G174" s="2">
-        <v>4.2300000000000004</v>
+        <v>3.06</v>
       </c>
       <c r="H174" s="4"/>
       <c r="I174" s="4"/>
@@ -7216,19 +7224,19 @@
     </row>
     <row r="175" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
-        <v>45869</v>
-      </c>
-      <c r="B175" s="10">
-        <v>1.61</v>
-      </c>
-      <c r="C175" s="10">
-        <v>1.61</v>
+        <v>45870</v>
+      </c>
+      <c r="B175" s="9">
+        <v>0.01</v>
+      </c>
+      <c r="C175" s="9">
+        <v>0.01</v>
       </c>
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
       <c r="F175" s="4"/>
       <c r="G175" s="2">
-        <v>-6.24</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="H175" s="4"/>
       <c r="I175" s="4"/>
@@ -7251,19 +7259,19 @@
     </row>
     <row r="176" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
-        <v>45868</v>
-      </c>
-      <c r="B176" s="9">
-        <v>-0.65</v>
-      </c>
-      <c r="C176" s="9">
-        <v>-0.65</v>
+        <v>45869</v>
+      </c>
+      <c r="B176" s="10">
+        <v>1.61</v>
+      </c>
+      <c r="C176" s="10">
+        <v>1.61</v>
       </c>
       <c r="D176" s="4"/>
       <c r="E176" s="4"/>
       <c r="F176" s="4"/>
       <c r="G176" s="2">
-        <v>0.97</v>
+        <v>-6.24</v>
       </c>
       <c r="H176" s="4"/>
       <c r="I176" s="4"/>
@@ -7286,19 +7294,19 @@
     </row>
     <row r="177" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
-        <v>45867</v>
-      </c>
-      <c r="B177" s="10">
-        <v>1.41</v>
-      </c>
-      <c r="C177" s="10">
-        <v>2.42</v>
+        <v>45868</v>
+      </c>
+      <c r="B177" s="9">
+        <v>-0.65</v>
+      </c>
+      <c r="C177" s="9">
+        <v>-0.65</v>
       </c>
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
       <c r="F177" s="4"/>
       <c r="G177" s="2">
-        <v>10.029999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="H177" s="4"/>
       <c r="I177" s="4"/>
@@ -7321,19 +7329,19 @@
     </row>
     <row r="178" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
-        <v>45866</v>
-      </c>
-      <c r="B178" s="9">
-        <v>-0.05</v>
-      </c>
-      <c r="C178" s="9">
-        <v>-0.05</v>
+        <v>45867</v>
+      </c>
+      <c r="B178" s="10">
+        <v>1.41</v>
+      </c>
+      <c r="C178" s="10">
+        <v>2.42</v>
       </c>
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
       <c r="F178" s="4"/>
       <c r="G178" s="2">
-        <v>-4.24</v>
+        <v>10.029999999999999</v>
       </c>
       <c r="H178" s="4"/>
       <c r="I178" s="4"/>
@@ -7356,19 +7364,19 @@
     </row>
     <row r="179" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
-        <v>45863</v>
-      </c>
-      <c r="B179" s="10">
-        <v>0.12</v>
-      </c>
-      <c r="C179" s="10">
-        <v>0.12</v>
+        <v>45866</v>
+      </c>
+      <c r="B179" s="9">
+        <v>-0.05</v>
+      </c>
+      <c r="C179" s="9">
+        <v>-0.05</v>
       </c>
       <c r="D179" s="4"/>
       <c r="E179" s="4"/>
       <c r="F179" s="4"/>
       <c r="G179" s="2">
-        <v>3.54</v>
+        <v>-4.24</v>
       </c>
       <c r="H179" s="4"/>
       <c r="I179" s="4"/>
@@ -7391,19 +7399,19 @@
     </row>
     <row r="180" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
-        <v>45862</v>
-      </c>
-      <c r="B180" s="9">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C180" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>45863</v>
+      </c>
+      <c r="B180" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="C180" s="10">
+        <v>0.12</v>
       </c>
       <c r="D180" s="4"/>
       <c r="E180" s="4"/>
       <c r="F180" s="4"/>
       <c r="G180" s="2">
-        <v>1.27</v>
+        <v>3.54</v>
       </c>
       <c r="H180" s="4"/>
       <c r="I180" s="4"/>
@@ -7426,19 +7434,19 @@
     </row>
     <row r="181" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
-        <v>45861</v>
-      </c>
-      <c r="B181" s="10">
-        <v>0.91</v>
-      </c>
-      <c r="C181" s="10">
-        <v>0.91</v>
+        <v>45862</v>
+      </c>
+      <c r="B181" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C181" s="9">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
       <c r="F181" s="4"/>
       <c r="G181" s="2">
-        <v>3.51</v>
+        <v>1.27</v>
       </c>
       <c r="H181" s="4"/>
       <c r="I181" s="4"/>
@@ -7461,19 +7469,19 @@
     </row>
     <row r="182" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
-        <v>45860</v>
-      </c>
-      <c r="B182" s="9">
-        <v>1.37</v>
-      </c>
-      <c r="C182" s="9">
-        <v>1.37</v>
+        <v>45861</v>
+      </c>
+      <c r="B182" s="10">
+        <v>0.91</v>
+      </c>
+      <c r="C182" s="10">
+        <v>0.91</v>
       </c>
       <c r="D182" s="4"/>
       <c r="E182" s="4"/>
       <c r="F182" s="4"/>
       <c r="G182" s="2">
-        <v>1.17</v>
+        <v>3.51</v>
       </c>
       <c r="H182" s="4"/>
       <c r="I182" s="4"/>
@@ -7496,19 +7504,19 @@
     </row>
     <row r="183" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
-        <v>45859</v>
-      </c>
-      <c r="B183" s="10">
-        <v>1</v>
-      </c>
-      <c r="C183" s="10">
-        <v>1</v>
+        <v>45860</v>
+      </c>
+      <c r="B183" s="9">
+        <v>1.37</v>
+      </c>
+      <c r="C183" s="9">
+        <v>1.37</v>
       </c>
       <c r="D183" s="4"/>
       <c r="E183" s="4"/>
       <c r="F183" s="4"/>
       <c r="G183" s="2">
-        <v>4.28</v>
+        <v>1.17</v>
       </c>
       <c r="H183" s="4"/>
       <c r="I183" s="4"/>
@@ -7531,19 +7539,19 @@
     </row>
     <row r="184" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
-        <v>45856</v>
-      </c>
-      <c r="B184" s="9">
-        <v>-0.13</v>
-      </c>
-      <c r="C184" s="9">
-        <v>-0.13</v>
+        <v>45859</v>
+      </c>
+      <c r="B184" s="10">
+        <v>1</v>
+      </c>
+      <c r="C184" s="10">
+        <v>1</v>
       </c>
       <c r="D184" s="4"/>
       <c r="E184" s="4"/>
       <c r="F184" s="4"/>
       <c r="G184" s="2">
-        <v>3.67</v>
+        <v>4.28</v>
       </c>
       <c r="H184" s="4"/>
       <c r="I184" s="4"/>
@@ -7566,19 +7574,19 @@
     </row>
     <row r="185" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
-        <v>45855</v>
-      </c>
-      <c r="B185" s="10">
-        <v>1.77</v>
-      </c>
-      <c r="C185" s="10">
-        <v>1.77</v>
+        <v>45856</v>
+      </c>
+      <c r="B185" s="9">
+        <v>-0.13</v>
+      </c>
+      <c r="C185" s="9">
+        <v>-0.13</v>
       </c>
       <c r="D185" s="4"/>
       <c r="E185" s="4"/>
       <c r="F185" s="4"/>
       <c r="G185" s="2">
-        <v>-1.1299999999999999</v>
+        <v>3.67</v>
       </c>
       <c r="H185" s="4"/>
       <c r="I185" s="4"/>
@@ -7601,19 +7609,19 @@
     </row>
     <row r="186" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
-        <v>45854</v>
-      </c>
-      <c r="B186" s="9">
-        <v>0.34</v>
-      </c>
-      <c r="C186" s="9">
-        <v>0.34</v>
+        <v>45855</v>
+      </c>
+      <c r="B186" s="10">
+        <v>1.77</v>
+      </c>
+      <c r="C186" s="10">
+        <v>1.77</v>
       </c>
       <c r="D186" s="4"/>
       <c r="E186" s="4"/>
       <c r="F186" s="4"/>
       <c r="G186" s="2">
-        <v>-2.48</v>
+        <v>-1.1299999999999999</v>
       </c>
       <c r="H186" s="4"/>
       <c r="I186" s="4"/>
@@ -7636,19 +7644,19 @@
     </row>
     <row r="187" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
-        <v>45853</v>
-      </c>
-      <c r="B187" s="10">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C187" s="10">
-        <v>1.1000000000000001</v>
+        <v>45854</v>
+      </c>
+      <c r="B187" s="9">
+        <v>0.34</v>
+      </c>
+      <c r="C187" s="9">
+        <v>0.34</v>
       </c>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
       <c r="F187" s="4"/>
       <c r="G187" s="2">
-        <v>4.37</v>
+        <v>-2.48</v>
       </c>
       <c r="H187" s="4"/>
       <c r="I187" s="4"/>
@@ -7671,19 +7679,19 @@
     </row>
     <row r="188" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
-        <v>45852</v>
-      </c>
-      <c r="B188" s="9">
-        <v>-0.27</v>
-      </c>
-      <c r="C188" s="9">
-        <v>-0.27</v>
+        <v>45853</v>
+      </c>
+      <c r="B188" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C188" s="10">
+        <v>1.1000000000000001</v>
       </c>
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
       <c r="F188" s="4"/>
       <c r="G188" s="2">
-        <v>2.04</v>
+        <v>4.37</v>
       </c>
       <c r="H188" s="4"/>
       <c r="I188" s="4"/>
@@ -7706,15 +7714,19 @@
     </row>
     <row r="189" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
-        <v>45849</v>
-      </c>
-      <c r="B189" s="4"/>
-      <c r="C189" s="4"/>
+        <v>45852</v>
+      </c>
+      <c r="B189" s="9">
+        <v>-0.27</v>
+      </c>
+      <c r="C189" s="9">
+        <v>-0.27</v>
+      </c>
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
       <c r="F189" s="4"/>
-      <c r="G189" s="3">
-        <v>0</v>
+      <c r="G189" s="2">
+        <v>2.04</v>
       </c>
       <c r="H189" s="4"/>
       <c r="I189" s="4"/>
@@ -7737,7 +7749,7 @@
     </row>
     <row r="190" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
-        <v>45848</v>
+        <v>45849</v>
       </c>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -7745,7 +7757,7 @@
       <c r="E190" s="4"/>
       <c r="F190" s="4"/>
       <c r="G190" s="3">
-        <v>7.03</v>
+        <v>0</v>
       </c>
       <c r="H190" s="4"/>
       <c r="I190" s="4"/>
@@ -7768,7 +7780,7 @@
     </row>
     <row r="191" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
-        <v>45847</v>
+        <v>45848</v>
       </c>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -7776,7 +7788,7 @@
       <c r="E191" s="4"/>
       <c r="F191" s="4"/>
       <c r="G191" s="3">
-        <v>2.15</v>
+        <v>7.03</v>
       </c>
       <c r="H191" s="4"/>
       <c r="I191" s="4"/>
@@ -7799,7 +7811,7 @@
     </row>
     <row r="192" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
-        <v>45846</v>
+        <v>45847</v>
       </c>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -7807,7 +7819,7 @@
       <c r="E192" s="4"/>
       <c r="F192" s="4"/>
       <c r="G192" s="3">
-        <v>3.92</v>
+        <v>2.15</v>
       </c>
       <c r="H192" s="4"/>
       <c r="I192" s="4"/>
@@ -7830,7 +7842,7 @@
     </row>
     <row r="193" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -7838,7 +7850,7 @@
       <c r="E193" s="4"/>
       <c r="F193" s="4"/>
       <c r="G193" s="3">
-        <v>0.7</v>
+        <v>3.92</v>
       </c>
       <c r="H193" s="4"/>
       <c r="I193" s="4"/>
@@ -7861,7 +7873,7 @@
     </row>
     <row r="194" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
-        <v>45842</v>
+        <v>45845</v>
       </c>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -7869,7 +7881,7 @@
       <c r="E194" s="4"/>
       <c r="F194" s="4"/>
       <c r="G194" s="3">
-        <v>4.68</v>
+        <v>0.7</v>
       </c>
       <c r="H194" s="4"/>
       <c r="I194" s="4"/>
@@ -7892,7 +7904,7 @@
     </row>
     <row r="195" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
-        <v>45841</v>
+        <v>45842</v>
       </c>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -7900,7 +7912,7 @@
       <c r="E195" s="4"/>
       <c r="F195" s="4"/>
       <c r="G195" s="3">
-        <v>1.03</v>
+        <v>4.68</v>
       </c>
       <c r="H195" s="4"/>
       <c r="I195" s="4"/>
@@ -7923,7 +7935,7 @@
     </row>
     <row r="196" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
-        <v>45840</v>
+        <v>45841</v>
       </c>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -7931,7 +7943,7 @@
       <c r="E196" s="4"/>
       <c r="F196" s="4"/>
       <c r="G196" s="3">
-        <v>2.48</v>
+        <v>1.03</v>
       </c>
       <c r="H196" s="4"/>
       <c r="I196" s="4"/>
@@ -7954,7 +7966,7 @@
     </row>
     <row r="197" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
-        <v>45839</v>
+        <v>45840</v>
       </c>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
@@ -7962,7 +7974,7 @@
       <c r="E197" s="4"/>
       <c r="F197" s="4"/>
       <c r="G197" s="3">
-        <v>0.91</v>
+        <v>2.48</v>
       </c>
       <c r="H197" s="4"/>
       <c r="I197" s="4"/>
@@ -7985,15 +7997,15 @@
     </row>
     <row r="198" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
       <c r="D198" s="4"/>
       <c r="E198" s="4"/>
       <c r="F198" s="4"/>
-      <c r="G198" s="4">
-        <v>3.46</v>
+      <c r="G198" s="3">
+        <v>0.91</v>
       </c>
       <c r="H198" s="4"/>
       <c r="I198" s="4"/>
@@ -8016,7 +8028,7 @@
     </row>
     <row r="199" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
-        <v>45835</v>
+        <v>45838</v>
       </c>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
@@ -8024,7 +8036,7 @@
       <c r="E199" s="4"/>
       <c r="F199" s="4"/>
       <c r="G199" s="4">
-        <v>0.11</v>
+        <v>3.46</v>
       </c>
       <c r="H199" s="4"/>
       <c r="I199" s="4"/>
@@ -8047,7 +8059,7 @@
     </row>
     <row r="200" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -8055,7 +8067,7 @@
       <c r="E200" s="4"/>
       <c r="F200" s="4"/>
       <c r="G200" s="4">
-        <v>7.75</v>
+        <v>0.11</v>
       </c>
       <c r="H200" s="4"/>
       <c r="I200" s="4"/>
@@ -8078,7 +8090,7 @@
     </row>
     <row r="201" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
-        <v>45833</v>
+        <v>45834</v>
       </c>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
@@ -8086,7 +8098,7 @@
       <c r="E201" s="4"/>
       <c r="F201" s="4"/>
       <c r="G201" s="4">
-        <v>-3.52</v>
+        <v>7.75</v>
       </c>
       <c r="H201" s="4"/>
       <c r="I201" s="4"/>
@@ -8109,7 +8121,7 @@
     </row>
     <row r="202" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
-        <v>45832</v>
+        <v>45833</v>
       </c>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
@@ -8117,7 +8129,7 @@
       <c r="E202" s="4"/>
       <c r="F202" s="4"/>
       <c r="G202" s="4">
-        <v>1.65</v>
+        <v>-3.52</v>
       </c>
       <c r="H202" s="4"/>
       <c r="I202" s="4"/>
@@ -8140,7 +8152,7 @@
     </row>
     <row r="203" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
-        <v>45831</v>
+        <v>45832</v>
       </c>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -8148,7 +8160,7 @@
       <c r="E203" s="4"/>
       <c r="F203" s="4"/>
       <c r="G203" s="4">
-        <v>-6.06</v>
+        <v>1.65</v>
       </c>
       <c r="H203" s="4"/>
       <c r="I203" s="4"/>
@@ -8171,7 +8183,7 @@
     </row>
     <row r="204" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
-        <v>45828</v>
+        <v>45831</v>
       </c>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
@@ -8179,7 +8191,7 @@
       <c r="E204" s="4"/>
       <c r="F204" s="4"/>
       <c r="G204" s="4">
-        <v>4.43</v>
+        <v>-6.06</v>
       </c>
       <c r="H204" s="4"/>
       <c r="I204" s="4"/>
@@ -8202,7 +8214,7 @@
     </row>
     <row r="205" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
-        <v>45827</v>
+        <v>45828</v>
       </c>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
@@ -8210,7 +8222,7 @@
       <c r="E205" s="4"/>
       <c r="F205" s="4"/>
       <c r="G205" s="4">
-        <v>-3.19</v>
+        <v>4.43</v>
       </c>
       <c r="H205" s="4"/>
       <c r="I205" s="4"/>
@@ -8233,7 +8245,7 @@
     </row>
     <row r="206" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
@@ -8241,7 +8253,7 @@
       <c r="E206" s="4"/>
       <c r="F206" s="4"/>
       <c r="G206" s="4">
-        <v>1.71</v>
+        <v>-3.19</v>
       </c>
       <c r="H206" s="4"/>
       <c r="I206" s="4"/>
@@ -8264,7 +8276,7 @@
     </row>
     <row r="207" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>45825</v>
+        <v>45826</v>
       </c>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
@@ -8272,7 +8284,7 @@
       <c r="E207" s="4"/>
       <c r="F207" s="4"/>
       <c r="G207" s="4">
-        <v>1.49</v>
+        <v>1.71</v>
       </c>
       <c r="H207" s="4"/>
       <c r="I207" s="4"/>
@@ -8295,7 +8307,7 @@
     </row>
     <row r="208" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>45824</v>
+        <v>45825</v>
       </c>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
@@ -8303,7 +8315,7 @@
       <c r="E208" s="4"/>
       <c r="F208" s="4"/>
       <c r="G208" s="4">
-        <v>6.65</v>
+        <v>1.49</v>
       </c>
       <c r="H208" s="4"/>
       <c r="I208" s="4"/>
@@ -8326,7 +8338,7 @@
     </row>
     <row r="209" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>45821</v>
+        <v>45824</v>
       </c>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
@@ -8334,7 +8346,7 @@
       <c r="E209" s="4"/>
       <c r="F209" s="4"/>
       <c r="G209" s="4">
-        <v>-0.64</v>
+        <v>6.65</v>
       </c>
       <c r="H209" s="4"/>
       <c r="I209" s="4"/>
@@ -8357,7 +8369,7 @@
     </row>
     <row r="210" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>45820</v>
+        <v>45821</v>
       </c>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
@@ -8365,7 +8377,7 @@
       <c r="E210" s="4"/>
       <c r="F210" s="4"/>
       <c r="G210" s="4">
-        <v>4.74</v>
+        <v>-0.64</v>
       </c>
       <c r="H210" s="4"/>
       <c r="I210" s="4"/>
@@ -8388,7 +8400,7 @@
     </row>
     <row r="211" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>45819</v>
+        <v>45820</v>
       </c>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
@@ -8396,7 +8408,7 @@
       <c r="E211" s="4"/>
       <c r="F211" s="4"/>
       <c r="G211" s="4">
-        <v>-0.41</v>
+        <v>4.74</v>
       </c>
       <c r="H211" s="4"/>
       <c r="I211" s="4"/>
@@ -8419,7 +8431,7 @@
     </row>
     <row r="212" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>45818</v>
+        <v>45819</v>
       </c>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
@@ -8427,7 +8439,7 @@
       <c r="E212" s="4"/>
       <c r="F212" s="4"/>
       <c r="G212" s="4">
-        <v>2.75</v>
+        <v>-0.41</v>
       </c>
       <c r="H212" s="4"/>
       <c r="I212" s="4"/>
@@ -8450,7 +8462,7 @@
     </row>
     <row r="213" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>45817</v>
+        <v>45818</v>
       </c>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
@@ -8458,7 +8470,7 @@
       <c r="E213" s="4"/>
       <c r="F213" s="4"/>
       <c r="G213" s="4">
-        <v>1.89</v>
+        <v>2.75</v>
       </c>
       <c r="H213" s="4"/>
       <c r="I213" s="4"/>
@@ -8481,7 +8493,7 @@
     </row>
     <row r="214" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>45814</v>
+        <v>45817</v>
       </c>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
@@ -8489,7 +8501,7 @@
       <c r="E214" s="4"/>
       <c r="F214" s="4"/>
       <c r="G214" s="4">
-        <v>4.47</v>
+        <v>1.89</v>
       </c>
       <c r="H214" s="4"/>
       <c r="I214" s="4"/>
@@ -8512,7 +8524,7 @@
     </row>
     <row r="215" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>45813</v>
+        <v>45814</v>
       </c>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
@@ -8520,7 +8532,7 @@
       <c r="E215" s="4"/>
       <c r="F215" s="4"/>
       <c r="G215" s="4">
-        <v>8.7100000000000009</v>
+        <v>4.47</v>
       </c>
       <c r="H215" s="4"/>
       <c r="I215" s="4"/>
@@ -8543,7 +8555,7 @@
     </row>
     <row r="216" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>45812</v>
+        <v>45813</v>
       </c>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
@@ -8551,7 +8563,7 @@
       <c r="E216" s="4"/>
       <c r="F216" s="4"/>
       <c r="G216" s="4">
-        <v>2.27</v>
+        <v>8.7100000000000009</v>
       </c>
       <c r="H216" s="4"/>
       <c r="I216" s="4"/>
@@ -8574,7 +8586,7 @@
     </row>
     <row r="217" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>45811</v>
+        <v>45812</v>
       </c>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
@@ -8582,7 +8594,7 @@
       <c r="E217" s="4"/>
       <c r="F217" s="4"/>
       <c r="G217" s="4">
-        <v>5.05</v>
+        <v>2.27</v>
       </c>
       <c r="H217" s="4"/>
       <c r="I217" s="4"/>
@@ -8605,7 +8617,7 @@
     </row>
     <row r="218" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>45810</v>
+        <v>45811</v>
       </c>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
@@ -8613,7 +8625,7 @@
       <c r="E218" s="4"/>
       <c r="F218" s="4"/>
       <c r="G218" s="4">
-        <v>-1.1599999999999999</v>
+        <v>5.05</v>
       </c>
       <c r="H218" s="4"/>
       <c r="I218" s="4"/>
@@ -8636,7 +8648,7 @@
     </row>
     <row r="219" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>45807</v>
+        <v>45810</v>
       </c>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -8644,7 +8656,7 @@
       <c r="E219" s="4"/>
       <c r="F219" s="4"/>
       <c r="G219" s="4">
-        <v>-2.5</v>
+        <v>-1.1599999999999999</v>
       </c>
       <c r="H219" s="4"/>
       <c r="I219" s="4"/>
@@ -8667,7 +8679,7 @@
     </row>
     <row r="220" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>45806</v>
+        <v>45807</v>
       </c>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
@@ -8675,7 +8687,7 @@
       <c r="E220" s="4"/>
       <c r="F220" s="4"/>
       <c r="G220" s="4">
-        <v>-1.68</v>
+        <v>-2.5</v>
       </c>
       <c r="H220" s="4"/>
       <c r="I220" s="4"/>
@@ -8698,7 +8710,7 @@
     </row>
     <row r="221" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>45805</v>
+        <v>45806</v>
       </c>
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
@@ -8706,7 +8718,7 @@
       <c r="E221" s="4"/>
       <c r="F221" s="4"/>
       <c r="G221" s="4">
-        <v>4.78</v>
+        <v>-1.68</v>
       </c>
       <c r="H221" s="4"/>
       <c r="I221" s="4"/>
@@ -8729,7 +8741,7 @@
     </row>
     <row r="222" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>45804</v>
+        <v>45805</v>
       </c>
       <c r="B222" s="4"/>
       <c r="C222" s="4"/>
@@ -8737,7 +8749,7 @@
       <c r="E222" s="4"/>
       <c r="F222" s="4"/>
       <c r="G222" s="4">
-        <v>4.55</v>
+        <v>4.78</v>
       </c>
       <c r="H222" s="4"/>
       <c r="I222" s="4"/>
@@ -8760,7 +8772,7 @@
     </row>
     <row r="223" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>45803</v>
+        <v>45804</v>
       </c>
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
@@ -8768,7 +8780,7 @@
       <c r="E223" s="4"/>
       <c r="F223" s="4"/>
       <c r="G223" s="4">
-        <v>1.62</v>
+        <v>4.55</v>
       </c>
       <c r="H223" s="4"/>
       <c r="I223" s="4"/>
@@ -8791,7 +8803,7 @@
     </row>
     <row r="224" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>45800</v>
+        <v>45803</v>
       </c>
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
@@ -8799,7 +8811,7 @@
       <c r="E224" s="4"/>
       <c r="F224" s="4"/>
       <c r="G224" s="4">
-        <v>4.22</v>
+        <v>1.62</v>
       </c>
       <c r="H224" s="4"/>
       <c r="I224" s="4"/>
@@ -8822,7 +8834,7 @@
     </row>
     <row r="225" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>45799</v>
+        <v>45800</v>
       </c>
       <c r="B225" s="4"/>
       <c r="C225" s="4"/>
@@ -8830,7 +8842,7 @@
       <c r="E225" s="4"/>
       <c r="F225" s="4"/>
       <c r="G225" s="4">
-        <v>1.97</v>
+        <v>4.22</v>
       </c>
       <c r="H225" s="4"/>
       <c r="I225" s="4"/>
@@ -8853,7 +8865,7 @@
     </row>
     <row r="226" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>45798</v>
+        <v>45799</v>
       </c>
       <c r="B226" s="4"/>
       <c r="C226" s="4"/>
@@ -8861,7 +8873,7 @@
       <c r="E226" s="4"/>
       <c r="F226" s="4"/>
       <c r="G226" s="4">
-        <v>-8.26</v>
+        <v>1.97</v>
       </c>
       <c r="H226" s="4"/>
       <c r="I226" s="4"/>
@@ -8884,7 +8896,7 @@
     </row>
     <row r="227" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>45797</v>
+        <v>45798</v>
       </c>
       <c r="B227" s="4"/>
       <c r="C227" s="4"/>
@@ -8892,7 +8904,7 @@
       <c r="E227" s="4"/>
       <c r="F227" s="4"/>
       <c r="G227" s="4">
-        <v>4.9000000000000004</v>
+        <v>-8.26</v>
       </c>
       <c r="H227" s="4"/>
       <c r="I227" s="4"/>
@@ -8915,7 +8927,7 @@
     </row>
     <row r="228" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>45796</v>
+        <v>45797</v>
       </c>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
@@ -8923,7 +8935,7 @@
       <c r="E228" s="4"/>
       <c r="F228" s="4"/>
       <c r="G228" s="4">
-        <v>4.32</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H228" s="4"/>
       <c r="I228" s="4"/>
@@ -8946,7 +8958,7 @@
     </row>
     <row r="229" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>45793</v>
+        <v>45796</v>
       </c>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
@@ -8954,7 +8966,7 @@
       <c r="E229" s="4"/>
       <c r="F229" s="4"/>
       <c r="G229" s="4">
-        <v>1.48</v>
+        <v>4.32</v>
       </c>
       <c r="H229" s="4"/>
       <c r="I229" s="4"/>
@@ -8977,7 +8989,7 @@
     </row>
     <row r="230" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>45792</v>
+        <v>45793</v>
       </c>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
@@ -8985,7 +8997,7 @@
       <c r="E230" s="4"/>
       <c r="F230" s="4"/>
       <c r="G230" s="4">
-        <v>6.87</v>
+        <v>1.48</v>
       </c>
       <c r="H230" s="4"/>
       <c r="I230" s="4"/>
@@ -9008,7 +9020,7 @@
     </row>
     <row r="231" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>45791</v>
+        <v>45792</v>
       </c>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
@@ -9016,7 +9028,7 @@
       <c r="E231" s="4"/>
       <c r="F231" s="4"/>
       <c r="G231" s="4">
-        <v>1.1200000000000001</v>
+        <v>6.87</v>
       </c>
       <c r="H231" s="4"/>
       <c r="I231" s="4"/>
@@ -9039,7 +9051,7 @@
     </row>
     <row r="232" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>45790</v>
+        <v>45791</v>
       </c>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
@@ -9047,7 +9059,7 @@
       <c r="E232" s="4"/>
       <c r="F232" s="4"/>
       <c r="G232" s="4">
-        <v>2.5499999999999998</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="H232" s="4"/>
       <c r="I232" s="4"/>
@@ -9070,7 +9082,7 @@
     </row>
     <row r="233" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>45789</v>
+        <v>45790</v>
       </c>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
@@ -9078,7 +9090,7 @@
       <c r="E233" s="4"/>
       <c r="F233" s="4"/>
       <c r="G233" s="4">
-        <v>0.61</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="H233" s="4"/>
       <c r="I233" s="4"/>
@@ -9101,7 +9113,7 @@
     </row>
     <row r="234" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>45786</v>
+        <v>45789</v>
       </c>
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
@@ -9109,11 +9121,9 @@
       <c r="E234" s="4"/>
       <c r="F234" s="4"/>
       <c r="G234" s="4">
-        <v>3.28</v>
-      </c>
-      <c r="H234" s="4">
-        <v>4.6399999999999997</v>
-      </c>
+        <v>0.61</v>
+      </c>
+      <c r="H234" s="4"/>
       <c r="I234" s="4"/>
       <c r="J234" s="4"/>
       <c r="K234" s="4"/>
@@ -9134,7 +9144,7 @@
     </row>
     <row r="235" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>45785</v>
+        <v>45786</v>
       </c>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
@@ -9142,9 +9152,11 @@
       <c r="E235" s="4"/>
       <c r="F235" s="4"/>
       <c r="G235" s="4">
-        <v>2.63</v>
-      </c>
-      <c r="H235" s="4"/>
+        <v>3.28</v>
+      </c>
+      <c r="H235" s="4">
+        <v>4.6399999999999997</v>
+      </c>
       <c r="I235" s="4"/>
       <c r="J235" s="4"/>
       <c r="K235" s="4"/>
@@ -9165,7 +9177,7 @@
     </row>
     <row r="236" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>45784</v>
+        <v>45785</v>
       </c>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
@@ -9173,7 +9185,7 @@
       <c r="E236" s="4"/>
       <c r="F236" s="4"/>
       <c r="G236" s="4">
-        <v>0.98</v>
+        <v>2.63</v>
       </c>
       <c r="H236" s="4"/>
       <c r="I236" s="4"/>
@@ -9196,7 +9208,7 @@
     </row>
     <row r="237" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>45783</v>
+        <v>45784</v>
       </c>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
@@ -9204,7 +9216,7 @@
       <c r="E237" s="4"/>
       <c r="F237" s="4"/>
       <c r="G237" s="4">
-        <v>4.41</v>
+        <v>0.98</v>
       </c>
       <c r="H237" s="4"/>
       <c r="I237" s="4"/>
@@ -9227,7 +9239,7 @@
     </row>
     <row r="238" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>45782</v>
+        <v>45783</v>
       </c>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
@@ -9235,7 +9247,7 @@
       <c r="E238" s="4"/>
       <c r="F238" s="4"/>
       <c r="G238" s="4">
-        <v>-2.72</v>
+        <v>4.41</v>
       </c>
       <c r="H238" s="4"/>
       <c r="I238" s="4"/>
@@ -9258,7 +9270,7 @@
     </row>
     <row r="239" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>45779</v>
+        <v>45782</v>
       </c>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
@@ -9266,7 +9278,7 @@
       <c r="E239" s="4"/>
       <c r="F239" s="4"/>
       <c r="G239" s="4">
-        <v>-4.29</v>
+        <v>-2.72</v>
       </c>
       <c r="H239" s="4"/>
       <c r="I239" s="4"/>
@@ -9289,7 +9301,7 @@
     </row>
     <row r="240" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>45777</v>
+        <v>45779</v>
       </c>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
@@ -9297,7 +9309,7 @@
       <c r="E240" s="4"/>
       <c r="F240" s="4"/>
       <c r="G240" s="4">
-        <v>-1.38</v>
+        <v>-4.29</v>
       </c>
       <c r="H240" s="4"/>
       <c r="I240" s="4"/>
@@ -9320,7 +9332,7 @@
     </row>
     <row r="241" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>45776</v>
+        <v>45777</v>
       </c>
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
@@ -9328,7 +9340,7 @@
       <c r="E241" s="4"/>
       <c r="F241" s="4"/>
       <c r="G241" s="4">
-        <v>0.69</v>
+        <v>-1.38</v>
       </c>
       <c r="H241" s="4"/>
       <c r="I241" s="4"/>
@@ -9351,7 +9363,7 @@
     </row>
     <row r="242" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>45775</v>
+        <v>45776</v>
       </c>
       <c r="B242" s="4"/>
       <c r="C242" s="4"/>
@@ -9359,7 +9371,7 @@
       <c r="E242" s="4"/>
       <c r="F242" s="4"/>
       <c r="G242" s="4">
-        <v>7.09</v>
+        <v>0.69</v>
       </c>
       <c r="H242" s="4"/>
       <c r="I242" s="4"/>
@@ -9382,7 +9394,7 @@
     </row>
     <row r="243" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>45772</v>
+        <v>45775</v>
       </c>
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
@@ -9390,7 +9402,7 @@
       <c r="E243" s="4"/>
       <c r="F243" s="4"/>
       <c r="G243" s="4">
-        <v>0</v>
+        <v>7.09</v>
       </c>
       <c r="H243" s="4"/>
       <c r="I243" s="4"/>
@@ -9413,7 +9425,7 @@
     </row>
     <row r="244" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>45771</v>
+        <v>45772</v>
       </c>
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
@@ -9444,7 +9456,7 @@
     </row>
     <row r="245" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>45770</v>
+        <v>45771</v>
       </c>
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
@@ -9452,7 +9464,7 @@
       <c r="E245" s="4"/>
       <c r="F245" s="4"/>
       <c r="G245" s="4">
-        <v>-5.94</v>
+        <v>0</v>
       </c>
       <c r="H245" s="4"/>
       <c r="I245" s="4"/>
@@ -9475,7 +9487,7 @@
     </row>
     <row r="246" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>45769</v>
+        <v>45770</v>
       </c>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
@@ -9483,7 +9495,7 @@
       <c r="E246" s="4"/>
       <c r="F246" s="4"/>
       <c r="G246" s="4">
-        <v>-0.47</v>
+        <v>-5.94</v>
       </c>
       <c r="H246" s="4"/>
       <c r="I246" s="4"/>
@@ -9506,7 +9518,7 @@
     </row>
     <row r="247" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>45768</v>
+        <v>45769</v>
       </c>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
@@ -9514,7 +9526,7 @@
       <c r="E247" s="4"/>
       <c r="F247" s="4"/>
       <c r="G247" s="4">
-        <v>4.03</v>
+        <v>-0.47</v>
       </c>
       <c r="H247" s="4"/>
       <c r="I247" s="4"/>
@@ -9537,7 +9549,7 @@
     </row>
     <row r="248" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>45764</v>
+        <v>45768</v>
       </c>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
@@ -9545,7 +9557,7 @@
       <c r="E248" s="4"/>
       <c r="F248" s="4"/>
       <c r="G248" s="4">
-        <v>3.46</v>
+        <v>4.03</v>
       </c>
       <c r="H248" s="4"/>
       <c r="I248" s="4"/>
@@ -9568,7 +9580,7 @@
     </row>
     <row r="249" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>45763</v>
+        <v>45764</v>
       </c>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
@@ -9576,7 +9588,7 @@
       <c r="E249" s="4"/>
       <c r="F249" s="4"/>
       <c r="G249" s="4">
-        <v>-2.81</v>
+        <v>3.46</v>
       </c>
       <c r="H249" s="4"/>
       <c r="I249" s="4"/>
@@ -9599,7 +9611,7 @@
     </row>
     <row r="250" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>45762</v>
+        <v>45763</v>
       </c>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
@@ -9607,7 +9619,7 @@
       <c r="E250" s="4"/>
       <c r="F250" s="4"/>
       <c r="G250" s="4">
-        <v>7.81</v>
+        <v>-2.81</v>
       </c>
       <c r="H250" s="4"/>
       <c r="I250" s="4"/>
@@ -9630,7 +9642,7 @@
     </row>
     <row r="251" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>45758</v>
+        <v>45762</v>
       </c>
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
@@ -9638,7 +9650,7 @@
       <c r="E251" s="4"/>
       <c r="F251" s="4"/>
       <c r="G251" s="4">
-        <v>-5.82</v>
+        <v>7.81</v>
       </c>
       <c r="H251" s="4"/>
       <c r="I251" s="4"/>
@@ -9661,7 +9673,7 @@
     </row>
     <row r="252" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>45756</v>
+        <v>45758</v>
       </c>
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
@@ -9669,7 +9681,7 @@
       <c r="E252" s="4"/>
       <c r="F252" s="4"/>
       <c r="G252" s="4">
-        <v>-0.56000000000000005</v>
+        <v>-5.82</v>
       </c>
       <c r="H252" s="4"/>
       <c r="I252" s="4"/>
@@ -9692,7 +9704,7 @@
     </row>
     <row r="253" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>45755</v>
+        <v>45756</v>
       </c>
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
@@ -9700,7 +9712,7 @@
       <c r="E253" s="4"/>
       <c r="F253" s="4"/>
       <c r="G253" s="4">
-        <v>5.83</v>
+        <v>-0.56000000000000005</v>
       </c>
       <c r="H253" s="4"/>
       <c r="I253" s="4"/>
@@ -9723,7 +9735,7 @@
     </row>
     <row r="254" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>45754</v>
+        <v>45755</v>
       </c>
       <c r="B254" s="4"/>
       <c r="C254" s="4"/>
@@ -9731,7 +9743,7 @@
       <c r="E254" s="4"/>
       <c r="F254" s="4"/>
       <c r="G254" s="4">
-        <v>6.02</v>
+        <v>5.83</v>
       </c>
       <c r="H254" s="4"/>
       <c r="I254" s="4"/>
@@ -9754,7 +9766,7 @@
     </row>
     <row r="255" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="B255" s="4"/>
       <c r="C255" s="4"/>
@@ -9762,7 +9774,7 @@
       <c r="E255" s="4"/>
       <c r="F255" s="4"/>
       <c r="G255" s="4">
-        <v>7.17</v>
+        <v>6.02</v>
       </c>
       <c r="H255" s="4"/>
       <c r="I255" s="4"/>
@@ -9785,7 +9797,7 @@
     </row>
     <row r="256" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
@@ -9793,7 +9805,7 @@
       <c r="E256" s="4"/>
       <c r="F256" s="4"/>
       <c r="G256" s="4">
-        <v>-3.37</v>
+        <v>7.17</v>
       </c>
       <c r="H256" s="4"/>
       <c r="I256" s="4"/>
@@ -9816,7 +9828,7 @@
     </row>
     <row r="257" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>45749</v>
+        <v>45750</v>
       </c>
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
@@ -9824,7 +9836,7 @@
       <c r="E257" s="4"/>
       <c r="F257" s="4"/>
       <c r="G257" s="4">
-        <v>1.8</v>
+        <v>-3.37</v>
       </c>
       <c r="H257" s="4"/>
       <c r="I257" s="4"/>
@@ -9847,7 +9859,7 @@
     </row>
     <row r="258" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>45748</v>
+        <v>45749</v>
       </c>
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
@@ -9855,7 +9867,7 @@
       <c r="E258" s="4"/>
       <c r="F258" s="4"/>
       <c r="G258" s="4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="H258" s="4"/>
       <c r="I258" s="4"/>
@@ -9877,13 +9889,17 @@
       <c r="Y258" s="4"/>
     </row>
     <row r="259" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="4"/>
+      <c r="A259" s="6">
+        <v>45748</v>
+      </c>
       <c r="B259" s="4"/>
       <c r="C259" s="4"/>
       <c r="D259" s="4"/>
       <c r="E259" s="4"/>
       <c r="F259" s="4"/>
-      <c r="G259" s="4"/>
+      <c r="G259" s="4">
+        <v>0</v>
+      </c>
       <c r="H259" s="4"/>
       <c r="I259" s="4"/>
       <c r="J259" s="4"/>
@@ -28533,6 +28549,33 @@
       <c r="X949" s="4"/>
       <c r="Y949" s="4"/>
     </row>
+    <row r="950" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A950" s="4"/>
+      <c r="B950" s="4"/>
+      <c r="C950" s="4"/>
+      <c r="D950" s="4"/>
+      <c r="E950" s="4"/>
+      <c r="F950" s="4"/>
+      <c r="G950" s="4"/>
+      <c r="H950" s="4"/>
+      <c r="I950" s="4"/>
+      <c r="J950" s="4"/>
+      <c r="K950" s="4"/>
+      <c r="L950" s="4"/>
+      <c r="M950" s="4"/>
+      <c r="N950" s="4"/>
+      <c r="O950" s="4"/>
+      <c r="P950" s="4"/>
+      <c r="Q950" s="4"/>
+      <c r="R950" s="4"/>
+      <c r="S950" s="4"/>
+      <c r="T950" s="4"/>
+      <c r="U950" s="4"/>
+      <c r="V950" s="4"/>
+      <c r="W950" s="4"/>
+      <c r="X950" s="4"/>
+      <c r="Y950" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/dashboard/data/Elite.xlsx
+++ b/dashboard/data/Elite.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PCS\Desktop\Python\Practice\dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5A49A6-F70D-480C-8C22-00B95B6E4213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED252561-CEBD-4783-AA21-A9D9F0888219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C510DD15-1ECC-4C0C-BE9E-FD99F7348715}"/>
   </bookViews>
@@ -110,7 +110,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -206,22 +206,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -258,9 +247,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -626,7 +612,9 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13"/>
+      <c r="A2" s="6">
+        <v>46128</v>
+      </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
